--- a/Excel/Excercises/Textual.xlsx
+++ b/Excel/Excercises/Textual.xlsx
@@ -1,29 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8C1236-C435-47B3-811D-8E43B4DA93D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
     <sheet name="Practice" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3791,7 +3781,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -4309,20 +4299,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:L10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="3" max="3" width="150.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="150.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:12" ht="21" x14ac:dyDescent="0.35">
       <c r="B2" s="13" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
@@ -4337,7 +4327,7 @@
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -4350,7 +4340,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="2:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="14">
         <v>1</v>
       </c>
@@ -4367,7 +4357,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="2:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14">
         <v>2</v>
       </c>
@@ -4384,7 +4374,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
     </row>
-    <row r="8" spans="2:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14">
         <v>3</v>
       </c>
@@ -4401,7 +4391,7 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="2:12" ht="37" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B9" s="14">
         <v>4</v>
       </c>
@@ -4418,7 +4408,7 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="2:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14">
         <v>5</v>
       </c>
@@ -4441,26 +4431,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:M1003"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7265625" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" customWidth="1"/>
-    <col min="10" max="10" width="12.26953125" customWidth="1"/>
-    <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -4498,7 +4488,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
@@ -4526,7 +4516,7 @@
       <c r="L4" s="6"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -4554,7 +4544,7 @@
       <c r="L5" s="6"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
@@ -4582,7 +4572,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -4610,7 +4600,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -4638,7 +4628,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>2</v>
       </c>
@@ -4666,7 +4656,7 @@
       <c r="L9" s="6"/>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>2</v>
       </c>
@@ -4694,7 +4684,7 @@
       <c r="L10" s="6"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>5</v>
       </c>
@@ -4722,7 +4712,7 @@
       <c r="L11" s="6"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -4750,7 +4740,7 @@
       <c r="L12" s="6"/>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>2</v>
       </c>
@@ -4778,7 +4768,7 @@
       <c r="L13" s="6"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>5</v>
       </c>
@@ -4806,7 +4796,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>5</v>
       </c>
@@ -4834,7 +4824,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>2</v>
       </c>
@@ -4862,7 +4852,7 @@
       <c r="L16" s="6"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>5</v>
       </c>
@@ -4890,7 +4880,7 @@
       <c r="L17" s="6"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>2</v>
       </c>
@@ -4918,7 +4908,7 @@
       <c r="L18" s="6"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>2</v>
       </c>
@@ -4946,7 +4936,7 @@
       <c r="L19" s="6"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>5</v>
       </c>
@@ -4974,7 +4964,7 @@
       <c r="L20" s="6"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>2</v>
       </c>
@@ -5002,7 +4992,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>5</v>
       </c>
@@ -5030,7 +5020,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
@@ -5058,7 +5048,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="7"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>5</v>
       </c>
@@ -5086,7 +5076,7 @@
       <c r="L24" s="6"/>
       <c r="M24" s="7"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
@@ -5114,7 +5104,7 @@
       <c r="L25" s="6"/>
       <c r="M25" s="7"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>5</v>
       </c>
@@ -5142,7 +5132,7 @@
       <c r="L26" s="6"/>
       <c r="M26" s="7"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>2</v>
       </c>
@@ -5170,7 +5160,7 @@
       <c r="L27" s="6"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>5</v>
       </c>
@@ -5198,7 +5188,7 @@
       <c r="L28" s="6"/>
       <c r="M28" s="7"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
         <v>5</v>
       </c>
@@ -5226,7 +5216,7 @@
       <c r="L29" s="6"/>
       <c r="M29" s="7"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
         <v>5</v>
       </c>
@@ -5254,7 +5244,7 @@
       <c r="L30" s="6"/>
       <c r="M30" s="7"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
         <v>2</v>
       </c>
@@ -5282,7 +5272,7 @@
       <c r="L31" s="6"/>
       <c r="M31" s="7"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
         <v>5</v>
       </c>
@@ -5310,7 +5300,7 @@
       <c r="L32" s="6"/>
       <c r="M32" s="7"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
@@ -5338,7 +5328,7 @@
       <c r="L33" s="6"/>
       <c r="M33" s="7"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
@@ -5366,7 +5356,7 @@
       <c r="L34" s="6"/>
       <c r="M34" s="7"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
@@ -5394,7 +5384,7 @@
       <c r="L35" s="6"/>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
@@ -5422,7 +5412,7 @@
       <c r="L36" s="6"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
         <v>5</v>
       </c>
@@ -5450,7 +5440,7 @@
       <c r="L37" s="6"/>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
         <v>5</v>
       </c>
@@ -5478,7 +5468,7 @@
       <c r="L38" s="6"/>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
         <v>5</v>
       </c>
@@ -5506,7 +5496,7 @@
       <c r="L39" s="6"/>
       <c r="M39" s="7"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
@@ -5534,7 +5524,7 @@
       <c r="L40" s="6"/>
       <c r="M40" s="7"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
@@ -5562,7 +5552,7 @@
       <c r="L41" s="6"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
@@ -5590,7 +5580,7 @@
       <c r="L42" s="6"/>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="5" t="s">
         <v>5</v>
       </c>
@@ -5618,7 +5608,7 @@
       <c r="L43" s="6"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
         <v>5</v>
       </c>
@@ -5646,7 +5636,7 @@
       <c r="L44" s="6"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
@@ -5674,7 +5664,7 @@
       <c r="L45" s="6"/>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
@@ -5702,7 +5692,7 @@
       <c r="L46" s="6"/>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
         <v>5</v>
       </c>
@@ -5730,7 +5720,7 @@
       <c r="L47" s="6"/>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
@@ -5758,7 +5748,7 @@
       <c r="L48" s="6"/>
       <c r="M48" s="7"/>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B49" s="5" t="s">
         <v>5</v>
       </c>
@@ -5786,7 +5776,7 @@
       <c r="L49" s="6"/>
       <c r="M49" s="7"/>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="s">
         <v>2</v>
       </c>
@@ -5814,7 +5804,7 @@
       <c r="L50" s="6"/>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B51" s="5" t="s">
         <v>2</v>
       </c>
@@ -5842,7 +5832,7 @@
       <c r="L51" s="6"/>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
@@ -5870,7 +5860,7 @@
       <c r="L52" s="6"/>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B53" s="5" t="s">
         <v>5</v>
       </c>
@@ -5898,7 +5888,7 @@
       <c r="L53" s="6"/>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B54" s="5" t="s">
         <v>5</v>
       </c>
@@ -5926,7 +5916,7 @@
       <c r="L54" s="6"/>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55" s="5" t="s">
         <v>5</v>
       </c>
@@ -5954,7 +5944,7 @@
       <c r="L55" s="6"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56" s="5" t="s">
         <v>5</v>
       </c>
@@ -5982,7 +5972,7 @@
       <c r="L56" s="6"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57" s="5" t="s">
         <v>5</v>
       </c>
@@ -6010,7 +6000,7 @@
       <c r="L57" s="6"/>
       <c r="M57" s="7"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
@@ -6038,7 +6028,7 @@
       <c r="L58" s="6"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
@@ -6066,7 +6056,7 @@
       <c r="L59" s="6"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
@@ -6094,7 +6084,7 @@
       <c r="L60" s="6"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B61" s="5" t="s">
         <v>5</v>
       </c>
@@ -6122,7 +6112,7 @@
       <c r="L61" s="6"/>
       <c r="M61" s="7"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
         <v>5</v>
       </c>
@@ -6150,7 +6140,7 @@
       <c r="L62" s="6"/>
       <c r="M62" s="7"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63" s="5" t="s">
         <v>2</v>
       </c>
@@ -6178,7 +6168,7 @@
       <c r="L63" s="6"/>
       <c r="M63" s="7"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B64" s="5" t="s">
         <v>5</v>
       </c>
@@ -6206,7 +6196,7 @@
       <c r="L64" s="6"/>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B65" s="5" t="s">
         <v>5</v>
       </c>
@@ -6234,7 +6224,7 @@
       <c r="L65" s="6"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
         <v>5</v>
       </c>
@@ -6262,7 +6252,7 @@
       <c r="L66" s="6"/>
       <c r="M66" s="7"/>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B67" s="5" t="s">
         <v>2</v>
       </c>
@@ -6290,7 +6280,7 @@
       <c r="L67" s="6"/>
       <c r="M67" s="7"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B68" s="5" t="s">
         <v>2</v>
       </c>
@@ -6318,7 +6308,7 @@
       <c r="L68" s="6"/>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B69" s="5" t="s">
         <v>5</v>
       </c>
@@ -6346,7 +6336,7 @@
       <c r="L69" s="6"/>
       <c r="M69" s="7"/>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B70" s="5" t="s">
         <v>5</v>
       </c>
@@ -6374,7 +6364,7 @@
       <c r="L70" s="6"/>
       <c r="M70" s="7"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B71" s="5" t="s">
         <v>2</v>
       </c>
@@ -6402,7 +6392,7 @@
       <c r="L71" s="6"/>
       <c r="M71" s="7"/>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B72" s="5" t="s">
         <v>5</v>
       </c>
@@ -6430,7 +6420,7 @@
       <c r="L72" s="6"/>
       <c r="M72" s="7"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B73" s="5" t="s">
         <v>2</v>
       </c>
@@ -6458,7 +6448,7 @@
       <c r="L73" s="6"/>
       <c r="M73" s="7"/>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B74" s="5" t="s">
         <v>2</v>
       </c>
@@ -6486,7 +6476,7 @@
       <c r="L74" s="6"/>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B75" s="5" t="s">
         <v>5</v>
       </c>
@@ -6514,7 +6504,7 @@
       <c r="L75" s="6"/>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B76" s="5" t="s">
         <v>2</v>
       </c>
@@ -6542,7 +6532,7 @@
       <c r="L76" s="6"/>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
         <v>5</v>
       </c>
@@ -6570,7 +6560,7 @@
       <c r="L77" s="6"/>
       <c r="M77" s="7"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B78" s="5" t="s">
         <v>5</v>
       </c>
@@ -6598,7 +6588,7 @@
       <c r="L78" s="6"/>
       <c r="M78" s="7"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B79" s="5" t="s">
         <v>5</v>
       </c>
@@ -6626,7 +6616,7 @@
       <c r="L79" s="6"/>
       <c r="M79" s="7"/>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B80" s="5" t="s">
         <v>5</v>
       </c>
@@ -6654,7 +6644,7 @@
       <c r="L80" s="6"/>
       <c r="M80" s="7"/>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B81" s="5" t="s">
         <v>5</v>
       </c>
@@ -6682,7 +6672,7 @@
       <c r="L81" s="6"/>
       <c r="M81" s="7"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82" s="5" t="s">
         <v>2</v>
       </c>
@@ -6710,7 +6700,7 @@
       <c r="L82" s="6"/>
       <c r="M82" s="7"/>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
         <v>2</v>
       </c>
@@ -6738,7 +6728,7 @@
       <c r="L83" s="6"/>
       <c r="M83" s="7"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84" s="5" t="s">
         <v>2</v>
       </c>
@@ -6766,7 +6756,7 @@
       <c r="L84" s="6"/>
       <c r="M84" s="7"/>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B85" s="5" t="s">
         <v>5</v>
       </c>
@@ -6794,7 +6784,7 @@
       <c r="L85" s="6"/>
       <c r="M85" s="7"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86" s="5" t="s">
         <v>5</v>
       </c>
@@ -6822,7 +6812,7 @@
       <c r="L86" s="6"/>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B87" s="5" t="s">
         <v>5</v>
       </c>
@@ -6850,7 +6840,7 @@
       <c r="L87" s="6"/>
       <c r="M87" s="7"/>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B88" s="5" t="s">
         <v>5</v>
       </c>
@@ -6878,7 +6868,7 @@
       <c r="L88" s="6"/>
       <c r="M88" s="7"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B89" s="5" t="s">
         <v>2</v>
       </c>
@@ -6906,7 +6896,7 @@
       <c r="L89" s="6"/>
       <c r="M89" s="7"/>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B90" s="5" t="s">
         <v>2</v>
       </c>
@@ -6934,7 +6924,7 @@
       <c r="L90" s="6"/>
       <c r="M90" s="7"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B91" s="5" t="s">
         <v>2</v>
       </c>
@@ -6962,7 +6952,7 @@
       <c r="L91" s="6"/>
       <c r="M91" s="7"/>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
@@ -6990,7 +6980,7 @@
       <c r="L92" s="6"/>
       <c r="M92" s="7"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B93" s="5" t="s">
         <v>2</v>
       </c>
@@ -7018,7 +7008,7 @@
       <c r="L93" s="6"/>
       <c r="M93" s="7"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B94" s="5" t="s">
         <v>2</v>
       </c>
@@ -7046,7 +7036,7 @@
       <c r="L94" s="6"/>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B95" s="5" t="s">
         <v>5</v>
       </c>
@@ -7074,7 +7064,7 @@
       <c r="L95" s="6"/>
       <c r="M95" s="7"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B96" s="5" t="s">
         <v>5</v>
       </c>
@@ -7102,7 +7092,7 @@
       <c r="L96" s="6"/>
       <c r="M96" s="7"/>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B97" s="5" t="s">
         <v>5</v>
       </c>
@@ -7130,7 +7120,7 @@
       <c r="L97" s="6"/>
       <c r="M97" s="7"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B98" s="5" t="s">
         <v>2</v>
       </c>
@@ -7158,7 +7148,7 @@
       <c r="L98" s="6"/>
       <c r="M98" s="7"/>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B99" s="5" t="s">
         <v>5</v>
       </c>
@@ -7186,7 +7176,7 @@
       <c r="L99" s="6"/>
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B100" s="5" t="s">
         <v>5</v>
       </c>
@@ -7214,7 +7204,7 @@
       <c r="L100" s="6"/>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
@@ -7242,7 +7232,7 @@
       <c r="L101" s="6"/>
       <c r="M101" s="7"/>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B102" s="5" t="s">
         <v>2</v>
       </c>
@@ -7270,7 +7260,7 @@
       <c r="L102" s="6"/>
       <c r="M102" s="7"/>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B103" s="5" t="s">
         <v>2</v>
       </c>
@@ -7298,7 +7288,7 @@
       <c r="L103" s="6"/>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B104" s="5" t="s">
         <v>5</v>
       </c>
@@ -7326,7 +7316,7 @@
       <c r="L104" s="6"/>
       <c r="M104" s="7"/>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B105" s="5" t="s">
         <v>5</v>
       </c>
@@ -7354,7 +7344,7 @@
       <c r="L105" s="6"/>
       <c r="M105" s="7"/>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B106" s="5" t="s">
         <v>2</v>
       </c>
@@ -7382,7 +7372,7 @@
       <c r="L106" s="6"/>
       <c r="M106" s="7"/>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B107" s="5" t="s">
         <v>5</v>
       </c>
@@ -7410,7 +7400,7 @@
       <c r="L107" s="6"/>
       <c r="M107" s="7"/>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B108" s="5" t="s">
         <v>5</v>
       </c>
@@ -7438,7 +7428,7 @@
       <c r="L108" s="6"/>
       <c r="M108" s="7"/>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B109" s="5" t="s">
         <v>2</v>
       </c>
@@ -7466,7 +7456,7 @@
       <c r="L109" s="6"/>
       <c r="M109" s="7"/>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B110" s="5" t="s">
         <v>2</v>
       </c>
@@ -7494,7 +7484,7 @@
       <c r="L110" s="6"/>
       <c r="M110" s="7"/>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B111" s="5" t="s">
         <v>5</v>
       </c>
@@ -7522,7 +7512,7 @@
       <c r="L111" s="6"/>
       <c r="M111" s="7"/>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B112" s="5" t="s">
         <v>2</v>
       </c>
@@ -7550,7 +7540,7 @@
       <c r="L112" s="6"/>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B113" s="5" t="s">
         <v>2</v>
       </c>
@@ -7578,7 +7568,7 @@
       <c r="L113" s="6"/>
       <c r="M113" s="7"/>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
@@ -7606,7 +7596,7 @@
       <c r="L114" s="6"/>
       <c r="M114" s="7"/>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B115" s="5" t="s">
         <v>5</v>
       </c>
@@ -7634,7 +7624,7 @@
       <c r="L115" s="6"/>
       <c r="M115" s="7"/>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B116" s="5" t="s">
         <v>5</v>
       </c>
@@ -7662,7 +7652,7 @@
       <c r="L116" s="6"/>
       <c r="M116" s="7"/>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
@@ -7690,7 +7680,7 @@
       <c r="L117" s="6"/>
       <c r="M117" s="7"/>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
@@ -7718,7 +7708,7 @@
       <c r="L118" s="6"/>
       <c r="M118" s="7"/>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B119" s="5" t="s">
         <v>5</v>
       </c>
@@ -7746,7 +7736,7 @@
       <c r="L119" s="6"/>
       <c r="M119" s="7"/>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
@@ -7774,7 +7764,7 @@
       <c r="L120" s="6"/>
       <c r="M120" s="7"/>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
@@ -7802,7 +7792,7 @@
       <c r="L121" s="6"/>
       <c r="M121" s="7"/>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
@@ -7830,7 +7820,7 @@
       <c r="L122" s="6"/>
       <c r="M122" s="7"/>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B123" s="5" t="s">
         <v>2</v>
       </c>
@@ -7858,7 +7848,7 @@
       <c r="L123" s="6"/>
       <c r="M123" s="7"/>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B124" s="5" t="s">
         <v>2</v>
       </c>
@@ -7886,7 +7876,7 @@
       <c r="L124" s="6"/>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B125" s="5" t="s">
         <v>5</v>
       </c>
@@ -7914,7 +7904,7 @@
       <c r="L125" s="6"/>
       <c r="M125" s="7"/>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B126" s="5" t="s">
         <v>2</v>
       </c>
@@ -7942,7 +7932,7 @@
       <c r="L126" s="6"/>
       <c r="M126" s="7"/>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B127" s="5" t="s">
         <v>5</v>
       </c>
@@ -7970,7 +7960,7 @@
       <c r="L127" s="6"/>
       <c r="M127" s="7"/>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B128" s="5" t="s">
         <v>5</v>
       </c>
@@ -7998,7 +7988,7 @@
       <c r="L128" s="6"/>
       <c r="M128" s="7"/>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B129" s="5" t="s">
         <v>2</v>
       </c>
@@ -8026,7 +8016,7 @@
       <c r="L129" s="6"/>
       <c r="M129" s="7"/>
     </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B130" s="5" t="s">
         <v>5</v>
       </c>
@@ -8054,7 +8044,7 @@
       <c r="L130" s="6"/>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B131" s="5" t="s">
         <v>5</v>
       </c>
@@ -8082,7 +8072,7 @@
       <c r="L131" s="6"/>
       <c r="M131" s="7"/>
     </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B132" s="5" t="s">
         <v>5</v>
       </c>
@@ -8110,7 +8100,7 @@
       <c r="L132" s="6"/>
       <c r="M132" s="7"/>
     </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B133" s="5" t="s">
         <v>2</v>
       </c>
@@ -8138,7 +8128,7 @@
       <c r="L133" s="6"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B134" s="5" t="s">
         <v>5</v>
       </c>
@@ -8166,7 +8156,7 @@
       <c r="L134" s="6"/>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B135" s="5" t="s">
         <v>5</v>
       </c>
@@ -8194,7 +8184,7 @@
       <c r="L135" s="6"/>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B136" s="5" t="s">
         <v>5</v>
       </c>
@@ -8222,7 +8212,7 @@
       <c r="L136" s="6"/>
       <c r="M136" s="7"/>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B137" s="5" t="s">
         <v>2</v>
       </c>
@@ -8250,7 +8240,7 @@
       <c r="L137" s="6"/>
       <c r="M137" s="7"/>
     </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B138" s="5" t="s">
         <v>5</v>
       </c>
@@ -8278,7 +8268,7 @@
       <c r="L138" s="6"/>
       <c r="M138" s="7"/>
     </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B139" s="5" t="s">
         <v>5</v>
       </c>
@@ -8306,7 +8296,7 @@
       <c r="L139" s="6"/>
       <c r="M139" s="7"/>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B140" s="5" t="s">
         <v>5</v>
       </c>
@@ -8334,7 +8324,7 @@
       <c r="L140" s="6"/>
       <c r="M140" s="7"/>
     </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B141" s="5" t="s">
         <v>5</v>
       </c>
@@ -8362,7 +8352,7 @@
       <c r="L141" s="6"/>
       <c r="M141" s="7"/>
     </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B142" s="5" t="s">
         <v>2</v>
       </c>
@@ -8390,7 +8380,7 @@
       <c r="L142" s="6"/>
       <c r="M142" s="7"/>
     </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B143" s="5" t="s">
         <v>5</v>
       </c>
@@ -8418,7 +8408,7 @@
       <c r="L143" s="6"/>
       <c r="M143" s="7"/>
     </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B144" s="5" t="s">
         <v>2</v>
       </c>
@@ -8446,7 +8436,7 @@
       <c r="L144" s="6"/>
       <c r="M144" s="7"/>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B145" s="5" t="s">
         <v>2</v>
       </c>
@@ -8474,7 +8464,7 @@
       <c r="L145" s="6"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B146" s="5" t="s">
         <v>2</v>
       </c>
@@ -8502,7 +8492,7 @@
       <c r="L146" s="6"/>
       <c r="M146" s="7"/>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B147" s="5" t="s">
         <v>5</v>
       </c>
@@ -8530,7 +8520,7 @@
       <c r="L147" s="6"/>
       <c r="M147" s="7"/>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B148" s="5" t="s">
         <v>5</v>
       </c>
@@ -8558,7 +8548,7 @@
       <c r="L148" s="6"/>
       <c r="M148" s="7"/>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B149" s="5" t="s">
         <v>2</v>
       </c>
@@ -8586,7 +8576,7 @@
       <c r="L149" s="6"/>
       <c r="M149" s="7"/>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B150" s="5" t="s">
         <v>5</v>
       </c>
@@ -8614,7 +8604,7 @@
       <c r="L150" s="6"/>
       <c r="M150" s="7"/>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B151" s="5" t="s">
         <v>5</v>
       </c>
@@ -8642,7 +8632,7 @@
       <c r="L151" s="6"/>
       <c r="M151" s="7"/>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B152" s="5" t="s">
         <v>2</v>
       </c>
@@ -8670,7 +8660,7 @@
       <c r="L152" s="6"/>
       <c r="M152" s="7"/>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B153" s="5" t="s">
         <v>5</v>
       </c>
@@ -8698,7 +8688,7 @@
       <c r="L153" s="6"/>
       <c r="M153" s="7"/>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B154" s="5" t="s">
         <v>5</v>
       </c>
@@ -8726,7 +8716,7 @@
       <c r="L154" s="6"/>
       <c r="M154" s="7"/>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B155" s="5" t="s">
         <v>5</v>
       </c>
@@ -8754,7 +8744,7 @@
       <c r="L155" s="6"/>
       <c r="M155" s="7"/>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B156" s="5" t="s">
         <v>2</v>
       </c>
@@ -8782,7 +8772,7 @@
       <c r="L156" s="6"/>
       <c r="M156" s="7"/>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B157" s="5" t="s">
         <v>5</v>
       </c>
@@ -8810,7 +8800,7 @@
       <c r="L157" s="6"/>
       <c r="M157" s="7"/>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B158" s="5" t="s">
         <v>5</v>
       </c>
@@ -8838,7 +8828,7 @@
       <c r="L158" s="6"/>
       <c r="M158" s="7"/>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B159" s="5" t="s">
         <v>2</v>
       </c>
@@ -8866,7 +8856,7 @@
       <c r="L159" s="6"/>
       <c r="M159" s="7"/>
     </row>
-    <row r="160" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B160" s="5" t="s">
         <v>2</v>
       </c>
@@ -8894,7 +8884,7 @@
       <c r="L160" s="6"/>
       <c r="M160" s="7"/>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B161" s="5" t="s">
         <v>5</v>
       </c>
@@ -8922,7 +8912,7 @@
       <c r="L161" s="6"/>
       <c r="M161" s="7"/>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B162" s="5" t="s">
         <v>2</v>
       </c>
@@ -8950,7 +8940,7 @@
       <c r="L162" s="6"/>
       <c r="M162" s="7"/>
     </row>
-    <row r="163" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B163" s="5" t="s">
         <v>5</v>
       </c>
@@ -8978,7 +8968,7 @@
       <c r="L163" s="6"/>
       <c r="M163" s="7"/>
     </row>
-    <row r="164" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B164" s="5" t="s">
         <v>5</v>
       </c>
@@ -9006,7 +8996,7 @@
       <c r="L164" s="6"/>
       <c r="M164" s="7"/>
     </row>
-    <row r="165" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B165" s="5" t="s">
         <v>2</v>
       </c>
@@ -9034,7 +9024,7 @@
       <c r="L165" s="6"/>
       <c r="M165" s="7"/>
     </row>
-    <row r="166" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B166" s="5" t="s">
         <v>5</v>
       </c>
@@ -9062,7 +9052,7 @@
       <c r="L166" s="6"/>
       <c r="M166" s="7"/>
     </row>
-    <row r="167" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B167" s="5" t="s">
         <v>5</v>
       </c>
@@ -9090,7 +9080,7 @@
       <c r="L167" s="6"/>
       <c r="M167" s="7"/>
     </row>
-    <row r="168" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B168" s="5" t="s">
         <v>2</v>
       </c>
@@ -9118,7 +9108,7 @@
       <c r="L168" s="6"/>
       <c r="M168" s="7"/>
     </row>
-    <row r="169" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B169" s="5" t="s">
         <v>2</v>
       </c>
@@ -9146,7 +9136,7 @@
       <c r="L169" s="6"/>
       <c r="M169" s="7"/>
     </row>
-    <row r="170" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B170" s="5" t="s">
         <v>5</v>
       </c>
@@ -9174,7 +9164,7 @@
       <c r="L170" s="6"/>
       <c r="M170" s="7"/>
     </row>
-    <row r="171" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B171" s="5" t="s">
         <v>2</v>
       </c>
@@ -9202,7 +9192,7 @@
       <c r="L171" s="6"/>
       <c r="M171" s="7"/>
     </row>
-    <row r="172" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B172" s="5" t="s">
         <v>2</v>
       </c>
@@ -9230,7 +9220,7 @@
       <c r="L172" s="6"/>
       <c r="M172" s="7"/>
     </row>
-    <row r="173" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B173" s="5" t="s">
         <v>2</v>
       </c>
@@ -9258,7 +9248,7 @@
       <c r="L173" s="6"/>
       <c r="M173" s="7"/>
     </row>
-    <row r="174" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B174" s="5" t="s">
         <v>5</v>
       </c>
@@ -9286,7 +9276,7 @@
       <c r="L174" s="6"/>
       <c r="M174" s="7"/>
     </row>
-    <row r="175" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B175" s="5" t="s">
         <v>5</v>
       </c>
@@ -9314,7 +9304,7 @@
       <c r="L175" s="6"/>
       <c r="M175" s="7"/>
     </row>
-    <row r="176" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B176" s="5" t="s">
         <v>2</v>
       </c>
@@ -9342,7 +9332,7 @@
       <c r="L176" s="6"/>
       <c r="M176" s="7"/>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B177" s="5" t="s">
         <v>2</v>
       </c>
@@ -9370,7 +9360,7 @@
       <c r="L177" s="6"/>
       <c r="M177" s="7"/>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B178" s="5" t="s">
         <v>2</v>
       </c>
@@ -9398,7 +9388,7 @@
       <c r="L178" s="6"/>
       <c r="M178" s="7"/>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B179" s="5" t="s">
         <v>2</v>
       </c>
@@ -9426,7 +9416,7 @@
       <c r="L179" s="6"/>
       <c r="M179" s="7"/>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B180" s="5" t="s">
         <v>2</v>
       </c>
@@ -9454,7 +9444,7 @@
       <c r="L180" s="6"/>
       <c r="M180" s="7"/>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B181" s="5" t="s">
         <v>2</v>
       </c>
@@ -9482,7 +9472,7 @@
       <c r="L181" s="6"/>
       <c r="M181" s="7"/>
     </row>
-    <row r="182" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B182" s="5" t="s">
         <v>2</v>
       </c>
@@ -9510,7 +9500,7 @@
       <c r="L182" s="6"/>
       <c r="M182" s="7"/>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B183" s="5" t="s">
         <v>2</v>
       </c>
@@ -9538,7 +9528,7 @@
       <c r="L183" s="6"/>
       <c r="M183" s="7"/>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B184" s="5" t="s">
         <v>5</v>
       </c>
@@ -9566,7 +9556,7 @@
       <c r="L184" s="6"/>
       <c r="M184" s="7"/>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B185" s="5" t="s">
         <v>2</v>
       </c>
@@ -9594,7 +9584,7 @@
       <c r="L185" s="6"/>
       <c r="M185" s="7"/>
     </row>
-    <row r="186" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B186" s="5" t="s">
         <v>2</v>
       </c>
@@ -9622,7 +9612,7 @@
       <c r="L186" s="6"/>
       <c r="M186" s="7"/>
     </row>
-    <row r="187" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B187" s="5" t="s">
         <v>2</v>
       </c>
@@ -9650,7 +9640,7 @@
       <c r="L187" s="6"/>
       <c r="M187" s="7"/>
     </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B188" s="5" t="s">
         <v>5</v>
       </c>
@@ -9678,7 +9668,7 @@
       <c r="L188" s="6"/>
       <c r="M188" s="7"/>
     </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B189" s="5" t="s">
         <v>5</v>
       </c>
@@ -9706,7 +9696,7 @@
       <c r="L189" s="6"/>
       <c r="M189" s="7"/>
     </row>
-    <row r="190" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B190" s="5" t="s">
         <v>5</v>
       </c>
@@ -9734,7 +9724,7 @@
       <c r="L190" s="6"/>
       <c r="M190" s="7"/>
     </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B191" s="5" t="s">
         <v>5</v>
       </c>
@@ -9762,7 +9752,7 @@
       <c r="L191" s="6"/>
       <c r="M191" s="7"/>
     </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B192" s="5" t="s">
         <v>5</v>
       </c>
@@ -9790,7 +9780,7 @@
       <c r="L192" s="6"/>
       <c r="M192" s="7"/>
     </row>
-    <row r="193" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B193" s="5" t="s">
         <v>2</v>
       </c>
@@ -9818,7 +9808,7 @@
       <c r="L193" s="6"/>
       <c r="M193" s="7"/>
     </row>
-    <row r="194" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B194" s="5" t="s">
         <v>2</v>
       </c>
@@ -9846,7 +9836,7 @@
       <c r="L194" s="6"/>
       <c r="M194" s="7"/>
     </row>
-    <row r="195" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B195" s="5" t="s">
         <v>5</v>
       </c>
@@ -9874,7 +9864,7 @@
       <c r="L195" s="6"/>
       <c r="M195" s="7"/>
     </row>
-    <row r="196" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B196" s="5" t="s">
         <v>2</v>
       </c>
@@ -9902,7 +9892,7 @@
       <c r="L196" s="6"/>
       <c r="M196" s="7"/>
     </row>
-    <row r="197" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B197" s="5" t="s">
         <v>5</v>
       </c>
@@ -9930,7 +9920,7 @@
       <c r="L197" s="6"/>
       <c r="M197" s="7"/>
     </row>
-    <row r="198" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B198" s="5" t="s">
         <v>2</v>
       </c>
@@ -9958,7 +9948,7 @@
       <c r="L198" s="6"/>
       <c r="M198" s="7"/>
     </row>
-    <row r="199" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B199" s="5" t="s">
         <v>5</v>
       </c>
@@ -9986,7 +9976,7 @@
       <c r="L199" s="6"/>
       <c r="M199" s="7"/>
     </row>
-    <row r="200" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B200" s="5" t="s">
         <v>5</v>
       </c>
@@ -10014,7 +10004,7 @@
       <c r="L200" s="6"/>
       <c r="M200" s="7"/>
     </row>
-    <row r="201" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B201" s="5" t="s">
         <v>5</v>
       </c>
@@ -10042,7 +10032,7 @@
       <c r="L201" s="6"/>
       <c r="M201" s="7"/>
     </row>
-    <row r="202" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B202" s="5" t="s">
         <v>2</v>
       </c>
@@ -10070,7 +10060,7 @@
       <c r="L202" s="6"/>
       <c r="M202" s="7"/>
     </row>
-    <row r="203" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B203" s="5" t="s">
         <v>2</v>
       </c>
@@ -10098,7 +10088,7 @@
       <c r="L203" s="6"/>
       <c r="M203" s="7"/>
     </row>
-    <row r="204" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B204" s="5" t="s">
         <v>2</v>
       </c>
@@ -10126,7 +10116,7 @@
       <c r="L204" s="6"/>
       <c r="M204" s="7"/>
     </row>
-    <row r="205" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B205" s="5" t="s">
         <v>2</v>
       </c>
@@ -10154,7 +10144,7 @@
       <c r="L205" s="6"/>
       <c r="M205" s="7"/>
     </row>
-    <row r="206" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B206" s="5" t="s">
         <v>5</v>
       </c>
@@ -10182,7 +10172,7 @@
       <c r="L206" s="6"/>
       <c r="M206" s="7"/>
     </row>
-    <row r="207" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B207" s="5" t="s">
         <v>2</v>
       </c>
@@ -10210,7 +10200,7 @@
       <c r="L207" s="6"/>
       <c r="M207" s="7"/>
     </row>
-    <row r="208" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B208" s="5" t="s">
         <v>5</v>
       </c>
@@ -10238,7 +10228,7 @@
       <c r="L208" s="6"/>
       <c r="M208" s="7"/>
     </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B209" s="5" t="s">
         <v>5</v>
       </c>
@@ -10266,7 +10256,7 @@
       <c r="L209" s="6"/>
       <c r="M209" s="7"/>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B210" s="5" t="s">
         <v>5</v>
       </c>
@@ -10294,7 +10284,7 @@
       <c r="L210" s="6"/>
       <c r="M210" s="7"/>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B211" s="5" t="s">
         <v>5</v>
       </c>
@@ -10322,7 +10312,7 @@
       <c r="L211" s="6"/>
       <c r="M211" s="7"/>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B212" s="5" t="s">
         <v>2</v>
       </c>
@@ -10350,7 +10340,7 @@
       <c r="L212" s="6"/>
       <c r="M212" s="7"/>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B213" s="5" t="s">
         <v>2</v>
       </c>
@@ -10378,7 +10368,7 @@
       <c r="L213" s="6"/>
       <c r="M213" s="7"/>
     </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B214" s="5" t="s">
         <v>5</v>
       </c>
@@ -10406,7 +10396,7 @@
       <c r="L214" s="6"/>
       <c r="M214" s="7"/>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B215" s="5" t="s">
         <v>5</v>
       </c>
@@ -10434,7 +10424,7 @@
       <c r="L215" s="6"/>
       <c r="M215" s="7"/>
     </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B216" s="5" t="s">
         <v>2</v>
       </c>
@@ -10462,7 +10452,7 @@
       <c r="L216" s="6"/>
       <c r="M216" s="7"/>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B217" s="5" t="s">
         <v>5</v>
       </c>
@@ -10490,7 +10480,7 @@
       <c r="L217" s="6"/>
       <c r="M217" s="7"/>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B218" s="5" t="s">
         <v>5</v>
       </c>
@@ -10518,7 +10508,7 @@
       <c r="L218" s="6"/>
       <c r="M218" s="7"/>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B219" s="5" t="s">
         <v>5</v>
       </c>
@@ -10546,7 +10536,7 @@
       <c r="L219" s="6"/>
       <c r="M219" s="7"/>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B220" s="5" t="s">
         <v>2</v>
       </c>
@@ -10574,7 +10564,7 @@
       <c r="L220" s="6"/>
       <c r="M220" s="7"/>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B221" s="5" t="s">
         <v>2</v>
       </c>
@@ -10602,7 +10592,7 @@
       <c r="L221" s="6"/>
       <c r="M221" s="7"/>
     </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B222" s="5" t="s">
         <v>5</v>
       </c>
@@ -10630,7 +10620,7 @@
       <c r="L222" s="6"/>
       <c r="M222" s="7"/>
     </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B223" s="5" t="s">
         <v>5</v>
       </c>
@@ -10658,7 +10648,7 @@
       <c r="L223" s="6"/>
       <c r="M223" s="7"/>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B224" s="5" t="s">
         <v>2</v>
       </c>
@@ -10686,7 +10676,7 @@
       <c r="L224" s="6"/>
       <c r="M224" s="7"/>
     </row>
-    <row r="225" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B225" s="5" t="s">
         <v>5</v>
       </c>
@@ -10714,7 +10704,7 @@
       <c r="L225" s="6"/>
       <c r="M225" s="7"/>
     </row>
-    <row r="226" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B226" s="5" t="s">
         <v>2</v>
       </c>
@@ -10742,7 +10732,7 @@
       <c r="L226" s="6"/>
       <c r="M226" s="7"/>
     </row>
-    <row r="227" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B227" s="5" t="s">
         <v>5</v>
       </c>
@@ -10770,7 +10760,7 @@
       <c r="L227" s="6"/>
       <c r="M227" s="7"/>
     </row>
-    <row r="228" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B228" s="5" t="s">
         <v>2</v>
       </c>
@@ -10798,7 +10788,7 @@
       <c r="L228" s="6"/>
       <c r="M228" s="7"/>
     </row>
-    <row r="229" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B229" s="5" t="s">
         <v>2</v>
       </c>
@@ -10826,7 +10816,7 @@
       <c r="L229" s="6"/>
       <c r="M229" s="7"/>
     </row>
-    <row r="230" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B230" s="5" t="s">
         <v>2</v>
       </c>
@@ -10854,7 +10844,7 @@
       <c r="L230" s="6"/>
       <c r="M230" s="7"/>
     </row>
-    <row r="231" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B231" s="5" t="s">
         <v>5</v>
       </c>
@@ -10882,7 +10872,7 @@
       <c r="L231" s="6"/>
       <c r="M231" s="7"/>
     </row>
-    <row r="232" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B232" s="5" t="s">
         <v>5</v>
       </c>
@@ -10910,7 +10900,7 @@
       <c r="L232" s="6"/>
       <c r="M232" s="7"/>
     </row>
-    <row r="233" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B233" s="5" t="s">
         <v>2</v>
       </c>
@@ -10938,7 +10928,7 @@
       <c r="L233" s="6"/>
       <c r="M233" s="7"/>
     </row>
-    <row r="234" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B234" s="5" t="s">
         <v>5</v>
       </c>
@@ -10966,7 +10956,7 @@
       <c r="L234" s="6"/>
       <c r="M234" s="7"/>
     </row>
-    <row r="235" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B235" s="5" t="s">
         <v>5</v>
       </c>
@@ -10994,7 +10984,7 @@
       <c r="L235" s="6"/>
       <c r="M235" s="7"/>
     </row>
-    <row r="236" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B236" s="5" t="s">
         <v>2</v>
       </c>
@@ -11022,7 +11012,7 @@
       <c r="L236" s="6"/>
       <c r="M236" s="7"/>
     </row>
-    <row r="237" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B237" s="5" t="s">
         <v>5</v>
       </c>
@@ -11050,7 +11040,7 @@
       <c r="L237" s="6"/>
       <c r="M237" s="7"/>
     </row>
-    <row r="238" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B238" s="5" t="s">
         <v>5</v>
       </c>
@@ -11078,7 +11068,7 @@
       <c r="L238" s="6"/>
       <c r="M238" s="7"/>
     </row>
-    <row r="239" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B239" s="5" t="s">
         <v>5</v>
       </c>
@@ -11106,7 +11096,7 @@
       <c r="L239" s="6"/>
       <c r="M239" s="7"/>
     </row>
-    <row r="240" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B240" s="5" t="s">
         <v>5</v>
       </c>
@@ -11134,7 +11124,7 @@
       <c r="L240" s="6"/>
       <c r="M240" s="7"/>
     </row>
-    <row r="241" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B241" s="5" t="s">
         <v>2</v>
       </c>
@@ -11162,7 +11152,7 @@
       <c r="L241" s="6"/>
       <c r="M241" s="7"/>
     </row>
-    <row r="242" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B242" s="5" t="s">
         <v>5</v>
       </c>
@@ -11190,7 +11180,7 @@
       <c r="L242" s="6"/>
       <c r="M242" s="7"/>
     </row>
-    <row r="243" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B243" s="5" t="s">
         <v>5</v>
       </c>
@@ -11218,7 +11208,7 @@
       <c r="L243" s="6"/>
       <c r="M243" s="7"/>
     </row>
-    <row r="244" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B244" s="5" t="s">
         <v>5</v>
       </c>
@@ -11246,7 +11236,7 @@
       <c r="L244" s="6"/>
       <c r="M244" s="7"/>
     </row>
-    <row r="245" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B245" s="5" t="s">
         <v>2</v>
       </c>
@@ -11274,7 +11264,7 @@
       <c r="L245" s="6"/>
       <c r="M245" s="7"/>
     </row>
-    <row r="246" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B246" s="5" t="s">
         <v>2</v>
       </c>
@@ -11302,7 +11292,7 @@
       <c r="L246" s="6"/>
       <c r="M246" s="7"/>
     </row>
-    <row r="247" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B247" s="5" t="s">
         <v>5</v>
       </c>
@@ -11330,7 +11320,7 @@
       <c r="L247" s="6"/>
       <c r="M247" s="7"/>
     </row>
-    <row r="248" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B248" s="5" t="s">
         <v>5</v>
       </c>
@@ -11358,7 +11348,7 @@
       <c r="L248" s="6"/>
       <c r="M248" s="7"/>
     </row>
-    <row r="249" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B249" s="5" t="s">
         <v>5</v>
       </c>
@@ -11386,7 +11376,7 @@
       <c r="L249" s="6"/>
       <c r="M249" s="7"/>
     </row>
-    <row r="250" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B250" s="5" t="s">
         <v>5</v>
       </c>
@@ -11414,7 +11404,7 @@
       <c r="L250" s="6"/>
       <c r="M250" s="7"/>
     </row>
-    <row r="251" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B251" s="5" t="s">
         <v>2</v>
       </c>
@@ -11442,7 +11432,7 @@
       <c r="L251" s="6"/>
       <c r="M251" s="7"/>
     </row>
-    <row r="252" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B252" s="5" t="s">
         <v>2</v>
       </c>
@@ -11470,7 +11460,7 @@
       <c r="L252" s="6"/>
       <c r="M252" s="7"/>
     </row>
-    <row r="253" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B253" s="5" t="s">
         <v>5</v>
       </c>
@@ -11498,7 +11488,7 @@
       <c r="L253" s="6"/>
       <c r="M253" s="7"/>
     </row>
-    <row r="254" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B254" s="5" t="s">
         <v>5</v>
       </c>
@@ -11526,7 +11516,7 @@
       <c r="L254" s="6"/>
       <c r="M254" s="7"/>
     </row>
-    <row r="255" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B255" s="5" t="s">
         <v>2</v>
       </c>
@@ -11554,7 +11544,7 @@
       <c r="L255" s="6"/>
       <c r="M255" s="7"/>
     </row>
-    <row r="256" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B256" s="5" t="s">
         <v>2</v>
       </c>
@@ -11582,7 +11572,7 @@
       <c r="L256" s="6"/>
       <c r="M256" s="7"/>
     </row>
-    <row r="257" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B257" s="5" t="s">
         <v>5</v>
       </c>
@@ -11610,7 +11600,7 @@
       <c r="L257" s="6"/>
       <c r="M257" s="7"/>
     </row>
-    <row r="258" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B258" s="5" t="s">
         <v>5</v>
       </c>
@@ -11638,7 +11628,7 @@
       <c r="L258" s="6"/>
       <c r="M258" s="7"/>
     </row>
-    <row r="259" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B259" s="5" t="s">
         <v>2</v>
       </c>
@@ -11666,7 +11656,7 @@
       <c r="L259" s="6"/>
       <c r="M259" s="7"/>
     </row>
-    <row r="260" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B260" s="5" t="s">
         <v>2</v>
       </c>
@@ -11694,7 +11684,7 @@
       <c r="L260" s="6"/>
       <c r="M260" s="7"/>
     </row>
-    <row r="261" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B261" s="5" t="s">
         <v>5</v>
       </c>
@@ -11722,7 +11712,7 @@
       <c r="L261" s="6"/>
       <c r="M261" s="7"/>
     </row>
-    <row r="262" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B262" s="5" t="s">
         <v>2</v>
       </c>
@@ -11750,7 +11740,7 @@
       <c r="L262" s="6"/>
       <c r="M262" s="7"/>
     </row>
-    <row r="263" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B263" s="5" t="s">
         <v>2</v>
       </c>
@@ -11778,7 +11768,7 @@
       <c r="L263" s="6"/>
       <c r="M263" s="7"/>
     </row>
-    <row r="264" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B264" s="5" t="s">
         <v>2</v>
       </c>
@@ -11806,7 +11796,7 @@
       <c r="L264" s="6"/>
       <c r="M264" s="7"/>
     </row>
-    <row r="265" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B265" s="5" t="s">
         <v>5</v>
       </c>
@@ -11834,7 +11824,7 @@
       <c r="L265" s="6"/>
       <c r="M265" s="7"/>
     </row>
-    <row r="266" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B266" s="5" t="s">
         <v>2</v>
       </c>
@@ -11862,7 +11852,7 @@
       <c r="L266" s="6"/>
       <c r="M266" s="7"/>
     </row>
-    <row r="267" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B267" s="5" t="s">
         <v>2</v>
       </c>
@@ -11890,7 +11880,7 @@
       <c r="L267" s="6"/>
       <c r="M267" s="7"/>
     </row>
-    <row r="268" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B268" s="5" t="s">
         <v>5</v>
       </c>
@@ -11918,7 +11908,7 @@
       <c r="L268" s="6"/>
       <c r="M268" s="7"/>
     </row>
-    <row r="269" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B269" s="5" t="s">
         <v>5</v>
       </c>
@@ -11946,7 +11936,7 @@
       <c r="L269" s="6"/>
       <c r="M269" s="7"/>
     </row>
-    <row r="270" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B270" s="5" t="s">
         <v>2</v>
       </c>
@@ -11974,7 +11964,7 @@
       <c r="L270" s="6"/>
       <c r="M270" s="7"/>
     </row>
-    <row r="271" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B271" s="5" t="s">
         <v>2</v>
       </c>
@@ -12002,7 +11992,7 @@
       <c r="L271" s="6"/>
       <c r="M271" s="7"/>
     </row>
-    <row r="272" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B272" s="5" t="s">
         <v>2</v>
       </c>
@@ -12030,7 +12020,7 @@
       <c r="L272" s="6"/>
       <c r="M272" s="7"/>
     </row>
-    <row r="273" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B273" s="5" t="s">
         <v>2</v>
       </c>
@@ -12058,7 +12048,7 @@
       <c r="L273" s="6"/>
       <c r="M273" s="7"/>
     </row>
-    <row r="274" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B274" s="5" t="s">
         <v>5</v>
       </c>
@@ -12086,7 +12076,7 @@
       <c r="L274" s="6"/>
       <c r="M274" s="7"/>
     </row>
-    <row r="275" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B275" s="5" t="s">
         <v>5</v>
       </c>
@@ -12114,7 +12104,7 @@
       <c r="L275" s="6"/>
       <c r="M275" s="7"/>
     </row>
-    <row r="276" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B276" s="5" t="s">
         <v>2</v>
       </c>
@@ -12142,7 +12132,7 @@
       <c r="L276" s="6"/>
       <c r="M276" s="7"/>
     </row>
-    <row r="277" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B277" s="5" t="s">
         <v>2</v>
       </c>
@@ -12170,7 +12160,7 @@
       <c r="L277" s="6"/>
       <c r="M277" s="7"/>
     </row>
-    <row r="278" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B278" s="5" t="s">
         <v>5</v>
       </c>
@@ -12198,7 +12188,7 @@
       <c r="L278" s="6"/>
       <c r="M278" s="7"/>
     </row>
-    <row r="279" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B279" s="5" t="s">
         <v>5</v>
       </c>
@@ -12226,7 +12216,7 @@
       <c r="L279" s="6"/>
       <c r="M279" s="7"/>
     </row>
-    <row r="280" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B280" s="5" t="s">
         <v>2</v>
       </c>
@@ -12254,7 +12244,7 @@
       <c r="L280" s="6"/>
       <c r="M280" s="7"/>
     </row>
-    <row r="281" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B281" s="5" t="s">
         <v>2</v>
       </c>
@@ -12282,7 +12272,7 @@
       <c r="L281" s="6"/>
       <c r="M281" s="7"/>
     </row>
-    <row r="282" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B282" s="5" t="s">
         <v>2</v>
       </c>
@@ -12310,7 +12300,7 @@
       <c r="L282" s="6"/>
       <c r="M282" s="7"/>
     </row>
-    <row r="283" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B283" s="5" t="s">
         <v>5</v>
       </c>
@@ -12338,7 +12328,7 @@
       <c r="L283" s="6"/>
       <c r="M283" s="7"/>
     </row>
-    <row r="284" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B284" s="5" t="s">
         <v>5</v>
       </c>
@@ -12366,7 +12356,7 @@
       <c r="L284" s="6"/>
       <c r="M284" s="7"/>
     </row>
-    <row r="285" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B285" s="5" t="s">
         <v>5</v>
       </c>
@@ -12394,7 +12384,7 @@
       <c r="L285" s="6"/>
       <c r="M285" s="7"/>
     </row>
-    <row r="286" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B286" s="5" t="s">
         <v>2</v>
       </c>
@@ -12422,7 +12412,7 @@
       <c r="L286" s="6"/>
       <c r="M286" s="7"/>
     </row>
-    <row r="287" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B287" s="5" t="s">
         <v>2</v>
       </c>
@@ -12450,7 +12440,7 @@
       <c r="L287" s="6"/>
       <c r="M287" s="7"/>
     </row>
-    <row r="288" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B288" s="5" t="s">
         <v>2</v>
       </c>
@@ -12478,7 +12468,7 @@
       <c r="L288" s="6"/>
       <c r="M288" s="7"/>
     </row>
-    <row r="289" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B289" s="5" t="s">
         <v>5</v>
       </c>
@@ -12506,7 +12496,7 @@
       <c r="L289" s="6"/>
       <c r="M289" s="7"/>
     </row>
-    <row r="290" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B290" s="5" t="s">
         <v>5</v>
       </c>
@@ -12534,7 +12524,7 @@
       <c r="L290" s="6"/>
       <c r="M290" s="7"/>
     </row>
-    <row r="291" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B291" s="5" t="s">
         <v>2</v>
       </c>
@@ -12562,7 +12552,7 @@
       <c r="L291" s="6"/>
       <c r="M291" s="7"/>
     </row>
-    <row r="292" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B292" s="5" t="s">
         <v>5</v>
       </c>
@@ -12590,7 +12580,7 @@
       <c r="L292" s="6"/>
       <c r="M292" s="7"/>
     </row>
-    <row r="293" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B293" s="5" t="s">
         <v>5</v>
       </c>
@@ -12618,7 +12608,7 @@
       <c r="L293" s="6"/>
       <c r="M293" s="7"/>
     </row>
-    <row r="294" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B294" s="5" t="s">
         <v>5</v>
       </c>
@@ -12646,7 +12636,7 @@
       <c r="L294" s="6"/>
       <c r="M294" s="7"/>
     </row>
-    <row r="295" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B295" s="5" t="s">
         <v>5</v>
       </c>
@@ -12674,7 +12664,7 @@
       <c r="L295" s="6"/>
       <c r="M295" s="7"/>
     </row>
-    <row r="296" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B296" s="5" t="s">
         <v>5</v>
       </c>
@@ -12702,7 +12692,7 @@
       <c r="L296" s="6"/>
       <c r="M296" s="7"/>
     </row>
-    <row r="297" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B297" s="5" t="s">
         <v>2</v>
       </c>
@@ -12730,7 +12720,7 @@
       <c r="L297" s="6"/>
       <c r="M297" s="7"/>
     </row>
-    <row r="298" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B298" s="5" t="s">
         <v>5</v>
       </c>
@@ -12758,7 +12748,7 @@
       <c r="L298" s="6"/>
       <c r="M298" s="7"/>
     </row>
-    <row r="299" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B299" s="5" t="s">
         <v>5</v>
       </c>
@@ -12786,7 +12776,7 @@
       <c r="L299" s="6"/>
       <c r="M299" s="7"/>
     </row>
-    <row r="300" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B300" s="5" t="s">
         <v>5</v>
       </c>
@@ -12814,7 +12804,7 @@
       <c r="L300" s="6"/>
       <c r="M300" s="7"/>
     </row>
-    <row r="301" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B301" s="5" t="s">
         <v>5</v>
       </c>
@@ -12842,7 +12832,7 @@
       <c r="L301" s="6"/>
       <c r="M301" s="7"/>
     </row>
-    <row r="302" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B302" s="5" t="s">
         <v>5</v>
       </c>
@@ -12870,7 +12860,7 @@
       <c r="L302" s="6"/>
       <c r="M302" s="7"/>
     </row>
-    <row r="303" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B303" s="5" t="s">
         <v>5</v>
       </c>
@@ -12898,7 +12888,7 @@
       <c r="L303" s="6"/>
       <c r="M303" s="7"/>
     </row>
-    <row r="304" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B304" s="5" t="s">
         <v>5</v>
       </c>
@@ -12926,7 +12916,7 @@
       <c r="L304" s="6"/>
       <c r="M304" s="7"/>
     </row>
-    <row r="305" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B305" s="5" t="s">
         <v>5</v>
       </c>
@@ -12954,7 +12944,7 @@
       <c r="L305" s="6"/>
       <c r="M305" s="7"/>
     </row>
-    <row r="306" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B306" s="5" t="s">
         <v>2</v>
       </c>
@@ -12982,7 +12972,7 @@
       <c r="L306" s="6"/>
       <c r="M306" s="7"/>
     </row>
-    <row r="307" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B307" s="5" t="s">
         <v>5</v>
       </c>
@@ -13010,7 +13000,7 @@
       <c r="L307" s="6"/>
       <c r="M307" s="7"/>
     </row>
-    <row r="308" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B308" s="5" t="s">
         <v>2</v>
       </c>
@@ -13038,7 +13028,7 @@
       <c r="L308" s="6"/>
       <c r="M308" s="7"/>
     </row>
-    <row r="309" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B309" s="5" t="s">
         <v>5</v>
       </c>
@@ -13066,7 +13056,7 @@
       <c r="L309" s="6"/>
       <c r="M309" s="7"/>
     </row>
-    <row r="310" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B310" s="5" t="s">
         <v>5</v>
       </c>
@@ -13094,7 +13084,7 @@
       <c r="L310" s="6"/>
       <c r="M310" s="7"/>
     </row>
-    <row r="311" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B311" s="5" t="s">
         <v>5</v>
       </c>
@@ -13122,7 +13112,7 @@
       <c r="L311" s="6"/>
       <c r="M311" s="7"/>
     </row>
-    <row r="312" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B312" s="5" t="s">
         <v>2</v>
       </c>
@@ -13150,7 +13140,7 @@
       <c r="L312" s="6"/>
       <c r="M312" s="7"/>
     </row>
-    <row r="313" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B313" s="5" t="s">
         <v>2</v>
       </c>
@@ -13178,7 +13168,7 @@
       <c r="L313" s="6"/>
       <c r="M313" s="7"/>
     </row>
-    <row r="314" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B314" s="5" t="s">
         <v>2</v>
       </c>
@@ -13206,7 +13196,7 @@
       <c r="L314" s="6"/>
       <c r="M314" s="7"/>
     </row>
-    <row r="315" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B315" s="5" t="s">
         <v>5</v>
       </c>
@@ -13234,7 +13224,7 @@
       <c r="L315" s="6"/>
       <c r="M315" s="7"/>
     </row>
-    <row r="316" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B316" s="5" t="s">
         <v>5</v>
       </c>
@@ -13262,7 +13252,7 @@
       <c r="L316" s="6"/>
       <c r="M316" s="7"/>
     </row>
-    <row r="317" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B317" s="5" t="s">
         <v>2</v>
       </c>
@@ -13290,7 +13280,7 @@
       <c r="L317" s="6"/>
       <c r="M317" s="7"/>
     </row>
-    <row r="318" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B318" s="5" t="s">
         <v>2</v>
       </c>
@@ -13318,7 +13308,7 @@
       <c r="L318" s="6"/>
       <c r="M318" s="7"/>
     </row>
-    <row r="319" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B319" s="5" t="s">
         <v>5</v>
       </c>
@@ -13346,7 +13336,7 @@
       <c r="L319" s="6"/>
       <c r="M319" s="7"/>
     </row>
-    <row r="320" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B320" s="5" t="s">
         <v>2</v>
       </c>
@@ -13374,7 +13364,7 @@
       <c r="L320" s="6"/>
       <c r="M320" s="7"/>
     </row>
-    <row r="321" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B321" s="5" t="s">
         <v>5</v>
       </c>
@@ -13402,7 +13392,7 @@
       <c r="L321" s="6"/>
       <c r="M321" s="7"/>
     </row>
-    <row r="322" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B322" s="5" t="s">
         <v>5</v>
       </c>
@@ -13430,7 +13420,7 @@
       <c r="L322" s="6"/>
       <c r="M322" s="7"/>
     </row>
-    <row r="323" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B323" s="5" t="s">
         <v>2</v>
       </c>
@@ -13458,7 +13448,7 @@
       <c r="L323" s="6"/>
       <c r="M323" s="7"/>
     </row>
-    <row r="324" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B324" s="5" t="s">
         <v>2</v>
       </c>
@@ -13486,7 +13476,7 @@
       <c r="L324" s="6"/>
       <c r="M324" s="7"/>
     </row>
-    <row r="325" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B325" s="5" t="s">
         <v>2</v>
       </c>
@@ -13514,7 +13504,7 @@
       <c r="L325" s="6"/>
       <c r="M325" s="7"/>
     </row>
-    <row r="326" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B326" s="5" t="s">
         <v>2</v>
       </c>
@@ -13542,7 +13532,7 @@
       <c r="L326" s="6"/>
       <c r="M326" s="7"/>
     </row>
-    <row r="327" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B327" s="5" t="s">
         <v>2</v>
       </c>
@@ -13570,7 +13560,7 @@
       <c r="L327" s="6"/>
       <c r="M327" s="7"/>
     </row>
-    <row r="328" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B328" s="5" t="s">
         <v>2</v>
       </c>
@@ -13598,7 +13588,7 @@
       <c r="L328" s="6"/>
       <c r="M328" s="7"/>
     </row>
-    <row r="329" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B329" s="5" t="s">
         <v>2</v>
       </c>
@@ -13626,7 +13616,7 @@
       <c r="L329" s="6"/>
       <c r="M329" s="7"/>
     </row>
-    <row r="330" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B330" s="5" t="s">
         <v>5</v>
       </c>
@@ -13654,7 +13644,7 @@
       <c r="L330" s="6"/>
       <c r="M330" s="7"/>
     </row>
-    <row r="331" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B331" s="5" t="s">
         <v>5</v>
       </c>
@@ -13682,7 +13672,7 @@
       <c r="L331" s="6"/>
       <c r="M331" s="7"/>
     </row>
-    <row r="332" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B332" s="5" t="s">
         <v>5</v>
       </c>
@@ -13710,7 +13700,7 @@
       <c r="L332" s="6"/>
       <c r="M332" s="7"/>
     </row>
-    <row r="333" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B333" s="5" t="s">
         <v>2</v>
       </c>
@@ -13738,7 +13728,7 @@
       <c r="L333" s="6"/>
       <c r="M333" s="7"/>
     </row>
-    <row r="334" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B334" s="5" t="s">
         <v>5</v>
       </c>
@@ -13766,7 +13756,7 @@
       <c r="L334" s="6"/>
       <c r="M334" s="7"/>
     </row>
-    <row r="335" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B335" s="5" t="s">
         <v>5</v>
       </c>
@@ -13794,7 +13784,7 @@
       <c r="L335" s="6"/>
       <c r="M335" s="7"/>
     </row>
-    <row r="336" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B336" s="5" t="s">
         <v>5</v>
       </c>
@@ -13822,7 +13812,7 @@
       <c r="L336" s="6"/>
       <c r="M336" s="7"/>
     </row>
-    <row r="337" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B337" s="5" t="s">
         <v>5</v>
       </c>
@@ -13850,7 +13840,7 @@
       <c r="L337" s="6"/>
       <c r="M337" s="7"/>
     </row>
-    <row r="338" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B338" s="5" t="s">
         <v>2</v>
       </c>
@@ -13878,7 +13868,7 @@
       <c r="L338" s="6"/>
       <c r="M338" s="7"/>
     </row>
-    <row r="339" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B339" s="5" t="s">
         <v>2</v>
       </c>
@@ -13906,7 +13896,7 @@
       <c r="L339" s="6"/>
       <c r="M339" s="7"/>
     </row>
-    <row r="340" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B340" s="5" t="s">
         <v>5</v>
       </c>
@@ -13934,7 +13924,7 @@
       <c r="L340" s="6"/>
       <c r="M340" s="7"/>
     </row>
-    <row r="341" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="341" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B341" s="5" t="s">
         <v>5</v>
       </c>
@@ -13962,7 +13952,7 @@
       <c r="L341" s="6"/>
       <c r="M341" s="7"/>
     </row>
-    <row r="342" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="342" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B342" s="5" t="s">
         <v>2</v>
       </c>
@@ -13990,7 +13980,7 @@
       <c r="L342" s="6"/>
       <c r="M342" s="7"/>
     </row>
-    <row r="343" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="343" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B343" s="5" t="s">
         <v>2</v>
       </c>
@@ -14018,7 +14008,7 @@
       <c r="L343" s="6"/>
       <c r="M343" s="7"/>
     </row>
-    <row r="344" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="344" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B344" s="5" t="s">
         <v>5</v>
       </c>
@@ -14046,7 +14036,7 @@
       <c r="L344" s="6"/>
       <c r="M344" s="7"/>
     </row>
-    <row r="345" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="345" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B345" s="5" t="s">
         <v>2</v>
       </c>
@@ -14074,7 +14064,7 @@
       <c r="L345" s="6"/>
       <c r="M345" s="7"/>
     </row>
-    <row r="346" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="346" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B346" s="5" t="s">
         <v>2</v>
       </c>
@@ -14102,7 +14092,7 @@
       <c r="L346" s="6"/>
       <c r="M346" s="7"/>
     </row>
-    <row r="347" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="347" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B347" s="5" t="s">
         <v>5</v>
       </c>
@@ -14130,7 +14120,7 @@
       <c r="L347" s="6"/>
       <c r="M347" s="7"/>
     </row>
-    <row r="348" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="348" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B348" s="5" t="s">
         <v>5</v>
       </c>
@@ -14158,7 +14148,7 @@
       <c r="L348" s="6"/>
       <c r="M348" s="7"/>
     </row>
-    <row r="349" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="349" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B349" s="5" t="s">
         <v>2</v>
       </c>
@@ -14186,7 +14176,7 @@
       <c r="L349" s="6"/>
       <c r="M349" s="7"/>
     </row>
-    <row r="350" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="350" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B350" s="5" t="s">
         <v>5</v>
       </c>
@@ -14214,7 +14204,7 @@
       <c r="L350" s="6"/>
       <c r="M350" s="7"/>
     </row>
-    <row r="351" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="351" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B351" s="5" t="s">
         <v>2</v>
       </c>
@@ -14242,7 +14232,7 @@
       <c r="L351" s="6"/>
       <c r="M351" s="7"/>
     </row>
-    <row r="352" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="352" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B352" s="5" t="s">
         <v>5</v>
       </c>
@@ -14270,7 +14260,7 @@
       <c r="L352" s="6"/>
       <c r="M352" s="7"/>
     </row>
-    <row r="353" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="353" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B353" s="5" t="s">
         <v>5</v>
       </c>
@@ -14298,7 +14288,7 @@
       <c r="L353" s="6"/>
       <c r="M353" s="7"/>
     </row>
-    <row r="354" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B354" s="5" t="s">
         <v>2</v>
       </c>
@@ -14326,7 +14316,7 @@
       <c r="L354" s="6"/>
       <c r="M354" s="7"/>
     </row>
-    <row r="355" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B355" s="5" t="s">
         <v>5</v>
       </c>
@@ -14354,7 +14344,7 @@
       <c r="L355" s="6"/>
       <c r="M355" s="7"/>
     </row>
-    <row r="356" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="356" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B356" s="5" t="s">
         <v>2</v>
       </c>
@@ -14382,7 +14372,7 @@
       <c r="L356" s="6"/>
       <c r="M356" s="7"/>
     </row>
-    <row r="357" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="357" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B357" s="5" t="s">
         <v>2</v>
       </c>
@@ -14410,7 +14400,7 @@
       <c r="L357" s="6"/>
       <c r="M357" s="7"/>
     </row>
-    <row r="358" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="358" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B358" s="5" t="s">
         <v>2</v>
       </c>
@@ -14438,7 +14428,7 @@
       <c r="L358" s="6"/>
       <c r="M358" s="7"/>
     </row>
-    <row r="359" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="359" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B359" s="5" t="s">
         <v>2</v>
       </c>
@@ -14466,7 +14456,7 @@
       <c r="L359" s="6"/>
       <c r="M359" s="7"/>
     </row>
-    <row r="360" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="360" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B360" s="5" t="s">
         <v>5</v>
       </c>
@@ -14494,7 +14484,7 @@
       <c r="L360" s="6"/>
       <c r="M360" s="7"/>
     </row>
-    <row r="361" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="361" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B361" s="5" t="s">
         <v>2</v>
       </c>
@@ -14522,7 +14512,7 @@
       <c r="L361" s="6"/>
       <c r="M361" s="7"/>
     </row>
-    <row r="362" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="362" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B362" s="5" t="s">
         <v>5</v>
       </c>
@@ -14550,7 +14540,7 @@
       <c r="L362" s="6"/>
       <c r="M362" s="7"/>
     </row>
-    <row r="363" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="363" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B363" s="5" t="s">
         <v>2</v>
       </c>
@@ -14578,7 +14568,7 @@
       <c r="L363" s="6"/>
       <c r="M363" s="7"/>
     </row>
-    <row r="364" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="364" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B364" s="5" t="s">
         <v>2</v>
       </c>
@@ -14606,7 +14596,7 @@
       <c r="L364" s="6"/>
       <c r="M364" s="7"/>
     </row>
-    <row r="365" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="365" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B365" s="5" t="s">
         <v>5</v>
       </c>
@@ -14634,7 +14624,7 @@
       <c r="L365" s="6"/>
       <c r="M365" s="7"/>
     </row>
-    <row r="366" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="366" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B366" s="5" t="s">
         <v>2</v>
       </c>
@@ -14662,7 +14652,7 @@
       <c r="L366" s="6"/>
       <c r="M366" s="7"/>
     </row>
-    <row r="367" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="367" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B367" s="5" t="s">
         <v>2</v>
       </c>
@@ -14690,7 +14680,7 @@
       <c r="L367" s="6"/>
       <c r="M367" s="7"/>
     </row>
-    <row r="368" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="368" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B368" s="5" t="s">
         <v>5</v>
       </c>
@@ -14718,7 +14708,7 @@
       <c r="L368" s="6"/>
       <c r="M368" s="7"/>
     </row>
-    <row r="369" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="369" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B369" s="5" t="s">
         <v>5</v>
       </c>
@@ -14746,7 +14736,7 @@
       <c r="L369" s="6"/>
       <c r="M369" s="7"/>
     </row>
-    <row r="370" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="370" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B370" s="5" t="s">
         <v>5</v>
       </c>
@@ -14774,7 +14764,7 @@
       <c r="L370" s="6"/>
       <c r="M370" s="7"/>
     </row>
-    <row r="371" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="371" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B371" s="5" t="s">
         <v>5</v>
       </c>
@@ -14802,7 +14792,7 @@
       <c r="L371" s="6"/>
       <c r="M371" s="7"/>
     </row>
-    <row r="372" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="372" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B372" s="5" t="s">
         <v>2</v>
       </c>
@@ -14830,7 +14820,7 @@
       <c r="L372" s="6"/>
       <c r="M372" s="7"/>
     </row>
-    <row r="373" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="373" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B373" s="5" t="s">
         <v>2</v>
       </c>
@@ -14858,7 +14848,7 @@
       <c r="L373" s="6"/>
       <c r="M373" s="7"/>
     </row>
-    <row r="374" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="374" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B374" s="5" t="s">
         <v>5</v>
       </c>
@@ -14886,7 +14876,7 @@
       <c r="L374" s="6"/>
       <c r="M374" s="7"/>
     </row>
-    <row r="375" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="375" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B375" s="5" t="s">
         <v>2</v>
       </c>
@@ -14914,7 +14904,7 @@
       <c r="L375" s="6"/>
       <c r="M375" s="7"/>
     </row>
-    <row r="376" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B376" s="5" t="s">
         <v>5</v>
       </c>
@@ -14942,7 +14932,7 @@
       <c r="L376" s="6"/>
       <c r="M376" s="7"/>
     </row>
-    <row r="377" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B377" s="5" t="s">
         <v>2</v>
       </c>
@@ -14970,7 +14960,7 @@
       <c r="L377" s="6"/>
       <c r="M377" s="7"/>
     </row>
-    <row r="378" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="378" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B378" s="5" t="s">
         <v>2</v>
       </c>
@@ -14998,7 +14988,7 @@
       <c r="L378" s="6"/>
       <c r="M378" s="7"/>
     </row>
-    <row r="379" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="379" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B379" s="5" t="s">
         <v>5</v>
       </c>
@@ -15026,7 +15016,7 @@
       <c r="L379" s="6"/>
       <c r="M379" s="7"/>
     </row>
-    <row r="380" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="380" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B380" s="5" t="s">
         <v>2</v>
       </c>
@@ -15054,7 +15044,7 @@
       <c r="L380" s="6"/>
       <c r="M380" s="7"/>
     </row>
-    <row r="381" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B381" s="5" t="s">
         <v>2</v>
       </c>
@@ -15082,7 +15072,7 @@
       <c r="L381" s="6"/>
       <c r="M381" s="7"/>
     </row>
-    <row r="382" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B382" s="5" t="s">
         <v>2</v>
       </c>
@@ -15110,7 +15100,7 @@
       <c r="L382" s="6"/>
       <c r="M382" s="7"/>
     </row>
-    <row r="383" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="383" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B383" s="5" t="s">
         <v>5</v>
       </c>
@@ -15138,7 +15128,7 @@
       <c r="L383" s="6"/>
       <c r="M383" s="7"/>
     </row>
-    <row r="384" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="384" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B384" s="5" t="s">
         <v>2</v>
       </c>
@@ -15166,7 +15156,7 @@
       <c r="L384" s="6"/>
       <c r="M384" s="7"/>
     </row>
-    <row r="385" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="385" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B385" s="5" t="s">
         <v>5</v>
       </c>
@@ -15194,7 +15184,7 @@
       <c r="L385" s="6"/>
       <c r="M385" s="7"/>
     </row>
-    <row r="386" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="386" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B386" s="5" t="s">
         <v>5</v>
       </c>
@@ -15222,7 +15212,7 @@
       <c r="L386" s="6"/>
       <c r="M386" s="7"/>
     </row>
-    <row r="387" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="387" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B387" s="5" t="s">
         <v>2</v>
       </c>
@@ -15250,7 +15240,7 @@
       <c r="L387" s="6"/>
       <c r="M387" s="7"/>
     </row>
-    <row r="388" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="388" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B388" s="5" t="s">
         <v>2</v>
       </c>
@@ -15278,7 +15268,7 @@
       <c r="L388" s="6"/>
       <c r="M388" s="7"/>
     </row>
-    <row r="389" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="389" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B389" s="5" t="s">
         <v>2</v>
       </c>
@@ -15306,7 +15296,7 @@
       <c r="L389" s="6"/>
       <c r="M389" s="7"/>
     </row>
-    <row r="390" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="390" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B390" s="5" t="s">
         <v>2</v>
       </c>
@@ -15334,7 +15324,7 @@
       <c r="L390" s="6"/>
       <c r="M390" s="7"/>
     </row>
-    <row r="391" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="391" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B391" s="5" t="s">
         <v>2</v>
       </c>
@@ -15362,7 +15352,7 @@
       <c r="L391" s="6"/>
       <c r="M391" s="7"/>
     </row>
-    <row r="392" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="392" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B392" s="5" t="s">
         <v>2</v>
       </c>
@@ -15390,7 +15380,7 @@
       <c r="L392" s="6"/>
       <c r="M392" s="7"/>
     </row>
-    <row r="393" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="393" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B393" s="5" t="s">
         <v>5</v>
       </c>
@@ -15418,7 +15408,7 @@
       <c r="L393" s="6"/>
       <c r="M393" s="7"/>
     </row>
-    <row r="394" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="394" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B394" s="5" t="s">
         <v>5</v>
       </c>
@@ -15446,7 +15436,7 @@
       <c r="L394" s="6"/>
       <c r="M394" s="7"/>
     </row>
-    <row r="395" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="395" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B395" s="5" t="s">
         <v>2</v>
       </c>
@@ -15474,7 +15464,7 @@
       <c r="L395" s="6"/>
       <c r="M395" s="7"/>
     </row>
-    <row r="396" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="396" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B396" s="5" t="s">
         <v>5</v>
       </c>
@@ -15502,7 +15492,7 @@
       <c r="L396" s="6"/>
       <c r="M396" s="7"/>
     </row>
-    <row r="397" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="397" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B397" s="5" t="s">
         <v>5</v>
       </c>
@@ -15530,7 +15520,7 @@
       <c r="L397" s="6"/>
       <c r="M397" s="7"/>
     </row>
-    <row r="398" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="398" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B398" s="5" t="s">
         <v>2</v>
       </c>
@@ -15558,7 +15548,7 @@
       <c r="L398" s="6"/>
       <c r="M398" s="7"/>
     </row>
-    <row r="399" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="399" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B399" s="5" t="s">
         <v>5</v>
       </c>
@@ -15586,7 +15576,7 @@
       <c r="L399" s="6"/>
       <c r="M399" s="7"/>
     </row>
-    <row r="400" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="400" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B400" s="5" t="s">
         <v>2</v>
       </c>
@@ -15614,7 +15604,7 @@
       <c r="L400" s="6"/>
       <c r="M400" s="7"/>
     </row>
-    <row r="401" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="401" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B401" s="5" t="s">
         <v>2</v>
       </c>
@@ -15642,7 +15632,7 @@
       <c r="L401" s="6"/>
       <c r="M401" s="7"/>
     </row>
-    <row r="402" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="402" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B402" s="5" t="s">
         <v>5</v>
       </c>
@@ -15670,7 +15660,7 @@
       <c r="L402" s="6"/>
       <c r="M402" s="7"/>
     </row>
-    <row r="403" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B403" s="5" t="s">
         <v>5</v>
       </c>
@@ -15698,7 +15688,7 @@
       <c r="L403" s="6"/>
       <c r="M403" s="7"/>
     </row>
-    <row r="404" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B404" s="5" t="s">
         <v>2</v>
       </c>
@@ -15726,7 +15716,7 @@
       <c r="L404" s="6"/>
       <c r="M404" s="7"/>
     </row>
-    <row r="405" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="405" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B405" s="5" t="s">
         <v>5</v>
       </c>
@@ -15754,7 +15744,7 @@
       <c r="L405" s="6"/>
       <c r="M405" s="7"/>
     </row>
-    <row r="406" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="406" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B406" s="5" t="s">
         <v>2</v>
       </c>
@@ -15782,7 +15772,7 @@
       <c r="L406" s="6"/>
       <c r="M406" s="7"/>
     </row>
-    <row r="407" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="407" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B407" s="5" t="s">
         <v>2</v>
       </c>
@@ -15810,7 +15800,7 @@
       <c r="L407" s="6"/>
       <c r="M407" s="7"/>
     </row>
-    <row r="408" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="408" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B408" s="5" t="s">
         <v>2</v>
       </c>
@@ -15838,7 +15828,7 @@
       <c r="L408" s="6"/>
       <c r="M408" s="7"/>
     </row>
-    <row r="409" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="409" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B409" s="5" t="s">
         <v>2</v>
       </c>
@@ -15866,7 +15856,7 @@
       <c r="L409" s="6"/>
       <c r="M409" s="7"/>
     </row>
-    <row r="410" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="410" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B410" s="5" t="s">
         <v>5</v>
       </c>
@@ -15894,7 +15884,7 @@
       <c r="L410" s="6"/>
       <c r="M410" s="7"/>
     </row>
-    <row r="411" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="411" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B411" s="5" t="s">
         <v>2</v>
       </c>
@@ -15922,7 +15912,7 @@
       <c r="L411" s="6"/>
       <c r="M411" s="7"/>
     </row>
-    <row r="412" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="412" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B412" s="5" t="s">
         <v>2</v>
       </c>
@@ -15950,7 +15940,7 @@
       <c r="L412" s="6"/>
       <c r="M412" s="7"/>
     </row>
-    <row r="413" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="413" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B413" s="5" t="s">
         <v>5</v>
       </c>
@@ -15978,7 +15968,7 @@
       <c r="L413" s="6"/>
       <c r="M413" s="7"/>
     </row>
-    <row r="414" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="414" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B414" s="5" t="s">
         <v>2</v>
       </c>
@@ -16006,7 +15996,7 @@
       <c r="L414" s="6"/>
       <c r="M414" s="7"/>
     </row>
-    <row r="415" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="415" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B415" s="5" t="s">
         <v>5</v>
       </c>
@@ -16034,7 +16024,7 @@
       <c r="L415" s="6"/>
       <c r="M415" s="7"/>
     </row>
-    <row r="416" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="416" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B416" s="5" t="s">
         <v>5</v>
       </c>
@@ -16062,7 +16052,7 @@
       <c r="L416" s="6"/>
       <c r="M416" s="7"/>
     </row>
-    <row r="417" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="417" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B417" s="5" t="s">
         <v>5</v>
       </c>
@@ -16090,7 +16080,7 @@
       <c r="L417" s="6"/>
       <c r="M417" s="7"/>
     </row>
-    <row r="418" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="418" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B418" s="5" t="s">
         <v>2</v>
       </c>
@@ -16118,7 +16108,7 @@
       <c r="L418" s="6"/>
       <c r="M418" s="7"/>
     </row>
-    <row r="419" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="419" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B419" s="5" t="s">
         <v>5</v>
       </c>
@@ -16146,7 +16136,7 @@
       <c r="L419" s="6"/>
       <c r="M419" s="7"/>
     </row>
-    <row r="420" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="420" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B420" s="5" t="s">
         <v>5</v>
       </c>
@@ -16174,7 +16164,7 @@
       <c r="L420" s="6"/>
       <c r="M420" s="7"/>
     </row>
-    <row r="421" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="421" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B421" s="5" t="s">
         <v>5</v>
       </c>
@@ -16202,7 +16192,7 @@
       <c r="L421" s="6"/>
       <c r="M421" s="7"/>
     </row>
-    <row r="422" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="422" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B422" s="5" t="s">
         <v>5</v>
       </c>
@@ -16230,7 +16220,7 @@
       <c r="L422" s="6"/>
       <c r="M422" s="7"/>
     </row>
-    <row r="423" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="423" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B423" s="5" t="s">
         <v>5</v>
       </c>
@@ -16258,7 +16248,7 @@
       <c r="L423" s="6"/>
       <c r="M423" s="7"/>
     </row>
-    <row r="424" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="424" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B424" s="5" t="s">
         <v>2</v>
       </c>
@@ -16286,7 +16276,7 @@
       <c r="L424" s="6"/>
       <c r="M424" s="7"/>
     </row>
-    <row r="425" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="425" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B425" s="5" t="s">
         <v>2</v>
       </c>
@@ -16314,7 +16304,7 @@
       <c r="L425" s="6"/>
       <c r="M425" s="7"/>
     </row>
-    <row r="426" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="426" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B426" s="5" t="s">
         <v>2</v>
       </c>
@@ -16342,7 +16332,7 @@
       <c r="L426" s="6"/>
       <c r="M426" s="7"/>
     </row>
-    <row r="427" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="427" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B427" s="5" t="s">
         <v>2</v>
       </c>
@@ -16370,7 +16360,7 @@
       <c r="L427" s="6"/>
       <c r="M427" s="7"/>
     </row>
-    <row r="428" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="428" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B428" s="5" t="s">
         <v>5</v>
       </c>
@@ -16398,7 +16388,7 @@
       <c r="L428" s="6"/>
       <c r="M428" s="7"/>
     </row>
-    <row r="429" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="429" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B429" s="5" t="s">
         <v>2</v>
       </c>
@@ -16426,7 +16416,7 @@
       <c r="L429" s="6"/>
       <c r="M429" s="7"/>
     </row>
-    <row r="430" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="430" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B430" s="5" t="s">
         <v>5</v>
       </c>
@@ -16454,7 +16444,7 @@
       <c r="L430" s="6"/>
       <c r="M430" s="7"/>
     </row>
-    <row r="431" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="431" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B431" s="5" t="s">
         <v>5</v>
       </c>
@@ -16482,7 +16472,7 @@
       <c r="L431" s="6"/>
       <c r="M431" s="7"/>
     </row>
-    <row r="432" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="432" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B432" s="5" t="s">
         <v>5</v>
       </c>
@@ -16510,7 +16500,7 @@
       <c r="L432" s="6"/>
       <c r="M432" s="7"/>
     </row>
-    <row r="433" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="433" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B433" s="5" t="s">
         <v>5</v>
       </c>
@@ -16538,7 +16528,7 @@
       <c r="L433" s="6"/>
       <c r="M433" s="7"/>
     </row>
-    <row r="434" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="434" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B434" s="5" t="s">
         <v>5</v>
       </c>
@@ -16566,7 +16556,7 @@
       <c r="L434" s="6"/>
       <c r="M434" s="7"/>
     </row>
-    <row r="435" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="435" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B435" s="5" t="s">
         <v>2</v>
       </c>
@@ -16594,7 +16584,7 @@
       <c r="L435" s="6"/>
       <c r="M435" s="7"/>
     </row>
-    <row r="436" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="436" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B436" s="5" t="s">
         <v>5</v>
       </c>
@@ -16622,7 +16612,7 @@
       <c r="L436" s="6"/>
       <c r="M436" s="7"/>
     </row>
-    <row r="437" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="437" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B437" s="5" t="s">
         <v>2</v>
       </c>
@@ -16650,7 +16640,7 @@
       <c r="L437" s="6"/>
       <c r="M437" s="7"/>
     </row>
-    <row r="438" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="438" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B438" s="5" t="s">
         <v>5</v>
       </c>
@@ -16678,7 +16668,7 @@
       <c r="L438" s="6"/>
       <c r="M438" s="7"/>
     </row>
-    <row r="439" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="439" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B439" s="5" t="s">
         <v>5</v>
       </c>
@@ -16706,7 +16696,7 @@
       <c r="L439" s="6"/>
       <c r="M439" s="7"/>
     </row>
-    <row r="440" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="440" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B440" s="5" t="s">
         <v>5</v>
       </c>
@@ -16734,7 +16724,7 @@
       <c r="L440" s="6"/>
       <c r="M440" s="7"/>
     </row>
-    <row r="441" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="441" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B441" s="5" t="s">
         <v>5</v>
       </c>
@@ -16762,7 +16752,7 @@
       <c r="L441" s="6"/>
       <c r="M441" s="7"/>
     </row>
-    <row r="442" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="442" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B442" s="5" t="s">
         <v>5</v>
       </c>
@@ -16790,7 +16780,7 @@
       <c r="L442" s="6"/>
       <c r="M442" s="7"/>
     </row>
-    <row r="443" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="443" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B443" s="5" t="s">
         <v>5</v>
       </c>
@@ -16818,7 +16808,7 @@
       <c r="L443" s="6"/>
       <c r="M443" s="7"/>
     </row>
-    <row r="444" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="444" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B444" s="5" t="s">
         <v>2</v>
       </c>
@@ -16846,7 +16836,7 @@
       <c r="L444" s="6"/>
       <c r="M444" s="7"/>
     </row>
-    <row r="445" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="445" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B445" s="5" t="s">
         <v>2</v>
       </c>
@@ -16874,7 +16864,7 @@
       <c r="L445" s="6"/>
       <c r="M445" s="7"/>
     </row>
-    <row r="446" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="446" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B446" s="5" t="s">
         <v>2</v>
       </c>
@@ -16902,7 +16892,7 @@
       <c r="L446" s="6"/>
       <c r="M446" s="7"/>
     </row>
-    <row r="447" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="447" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B447" s="5" t="s">
         <v>2</v>
       </c>
@@ -16930,7 +16920,7 @@
       <c r="L447" s="6"/>
       <c r="M447" s="7"/>
     </row>
-    <row r="448" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="448" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B448" s="5" t="s">
         <v>5</v>
       </c>
@@ -16958,7 +16948,7 @@
       <c r="L448" s="6"/>
       <c r="M448" s="7"/>
     </row>
-    <row r="449" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="449" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B449" s="5" t="s">
         <v>2</v>
       </c>
@@ -16986,7 +16976,7 @@
       <c r="L449" s="6"/>
       <c r="M449" s="7"/>
     </row>
-    <row r="450" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B450" s="5" t="s">
         <v>5</v>
       </c>
@@ -17014,7 +17004,7 @@
       <c r="L450" s="6"/>
       <c r="M450" s="7"/>
     </row>
-    <row r="451" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B451" s="5" t="s">
         <v>5</v>
       </c>
@@ -17042,7 +17032,7 @@
       <c r="L451" s="6"/>
       <c r="M451" s="7"/>
     </row>
-    <row r="452" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B452" s="5" t="s">
         <v>5</v>
       </c>
@@ -17070,7 +17060,7 @@
       <c r="L452" s="6"/>
       <c r="M452" s="7"/>
     </row>
-    <row r="453" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B453" s="5" t="s">
         <v>5</v>
       </c>
@@ -17098,7 +17088,7 @@
       <c r="L453" s="6"/>
       <c r="M453" s="7"/>
     </row>
-    <row r="454" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B454" s="5" t="s">
         <v>2</v>
       </c>
@@ -17126,7 +17116,7 @@
       <c r="L454" s="6"/>
       <c r="M454" s="7"/>
     </row>
-    <row r="455" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B455" s="5" t="s">
         <v>2</v>
       </c>
@@ -17154,7 +17144,7 @@
       <c r="L455" s="6"/>
       <c r="M455" s="7"/>
     </row>
-    <row r="456" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B456" s="5" t="s">
         <v>2</v>
       </c>
@@ -17182,7 +17172,7 @@
       <c r="L456" s="6"/>
       <c r="M456" s="7"/>
     </row>
-    <row r="457" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B457" s="5" t="s">
         <v>5</v>
       </c>
@@ -17210,7 +17200,7 @@
       <c r="L457" s="6"/>
       <c r="M457" s="7"/>
     </row>
-    <row r="458" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B458" s="5" t="s">
         <v>2</v>
       </c>
@@ -17238,7 +17228,7 @@
       <c r="L458" s="6"/>
       <c r="M458" s="7"/>
     </row>
-    <row r="459" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B459" s="5" t="s">
         <v>5</v>
       </c>
@@ -17266,7 +17256,7 @@
       <c r="L459" s="6"/>
       <c r="M459" s="7"/>
     </row>
-    <row r="460" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B460" s="5" t="s">
         <v>2</v>
       </c>
@@ -17294,7 +17284,7 @@
       <c r="L460" s="6"/>
       <c r="M460" s="7"/>
     </row>
-    <row r="461" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B461" s="5" t="s">
         <v>5</v>
       </c>
@@ -17322,7 +17312,7 @@
       <c r="L461" s="6"/>
       <c r="M461" s="7"/>
     </row>
-    <row r="462" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B462" s="5" t="s">
         <v>2</v>
       </c>
@@ -17350,7 +17340,7 @@
       <c r="L462" s="6"/>
       <c r="M462" s="7"/>
     </row>
-    <row r="463" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B463" s="5" t="s">
         <v>5</v>
       </c>
@@ -17378,7 +17368,7 @@
       <c r="L463" s="6"/>
       <c r="M463" s="7"/>
     </row>
-    <row r="464" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B464" s="5" t="s">
         <v>5</v>
       </c>
@@ -17406,7 +17396,7 @@
       <c r="L464" s="6"/>
       <c r="M464" s="7"/>
     </row>
-    <row r="465" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="465" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B465" s="5" t="s">
         <v>5</v>
       </c>
@@ -17434,7 +17424,7 @@
       <c r="L465" s="6"/>
       <c r="M465" s="7"/>
     </row>
-    <row r="466" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="466" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B466" s="5" t="s">
         <v>2</v>
       </c>
@@ -17462,7 +17452,7 @@
       <c r="L466" s="6"/>
       <c r="M466" s="7"/>
     </row>
-    <row r="467" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="467" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B467" s="5" t="s">
         <v>2</v>
       </c>
@@ -17490,7 +17480,7 @@
       <c r="L467" s="6"/>
       <c r="M467" s="7"/>
     </row>
-    <row r="468" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="468" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B468" s="5" t="s">
         <v>5</v>
       </c>
@@ -17518,7 +17508,7 @@
       <c r="L468" s="6"/>
       <c r="M468" s="7"/>
     </row>
-    <row r="469" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="469" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B469" s="5" t="s">
         <v>2</v>
       </c>
@@ -17546,7 +17536,7 @@
       <c r="L469" s="6"/>
       <c r="M469" s="7"/>
     </row>
-    <row r="470" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="470" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B470" s="5" t="s">
         <v>2</v>
       </c>
@@ -17574,7 +17564,7 @@
       <c r="L470" s="6"/>
       <c r="M470" s="7"/>
     </row>
-    <row r="471" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="471" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B471" s="5" t="s">
         <v>5</v>
       </c>
@@ -17602,7 +17592,7 @@
       <c r="L471" s="6"/>
       <c r="M471" s="7"/>
     </row>
-    <row r="472" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="472" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B472" s="5" t="s">
         <v>2</v>
       </c>
@@ -17630,7 +17620,7 @@
       <c r="L472" s="6"/>
       <c r="M472" s="7"/>
     </row>
-    <row r="473" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="473" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B473" s="5" t="s">
         <v>5</v>
       </c>
@@ -17658,7 +17648,7 @@
       <c r="L473" s="6"/>
       <c r="M473" s="7"/>
     </row>
-    <row r="474" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="474" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B474" s="5" t="s">
         <v>2</v>
       </c>
@@ -17686,7 +17676,7 @@
       <c r="L474" s="6"/>
       <c r="M474" s="7"/>
     </row>
-    <row r="475" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="475" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B475" s="5" t="s">
         <v>2</v>
       </c>
@@ -17714,7 +17704,7 @@
       <c r="L475" s="6"/>
       <c r="M475" s="7"/>
     </row>
-    <row r="476" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="476" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B476" s="5" t="s">
         <v>2</v>
       </c>
@@ -17742,7 +17732,7 @@
       <c r="L476" s="6"/>
       <c r="M476" s="7"/>
     </row>
-    <row r="477" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="477" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B477" s="5" t="s">
         <v>2</v>
       </c>
@@ -17770,7 +17760,7 @@
       <c r="L477" s="6"/>
       <c r="M477" s="7"/>
     </row>
-    <row r="478" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="478" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B478" s="5" t="s">
         <v>2</v>
       </c>
@@ -17798,7 +17788,7 @@
       <c r="L478" s="6"/>
       <c r="M478" s="7"/>
     </row>
-    <row r="479" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="479" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B479" s="5" t="s">
         <v>2</v>
       </c>
@@ -17826,7 +17816,7 @@
       <c r="L479" s="6"/>
       <c r="M479" s="7"/>
     </row>
-    <row r="480" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="480" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B480" s="5" t="s">
         <v>5</v>
       </c>
@@ -17854,7 +17844,7 @@
       <c r="L480" s="6"/>
       <c r="M480" s="7"/>
     </row>
-    <row r="481" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="481" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B481" s="5" t="s">
         <v>5</v>
       </c>
@@ -17882,7 +17872,7 @@
       <c r="L481" s="6"/>
       <c r="M481" s="7"/>
     </row>
-    <row r="482" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="482" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B482" s="5" t="s">
         <v>2</v>
       </c>
@@ -17910,7 +17900,7 @@
       <c r="L482" s="6"/>
       <c r="M482" s="7"/>
     </row>
-    <row r="483" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="483" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B483" s="5" t="s">
         <v>5</v>
       </c>
@@ -17938,7 +17928,7 @@
       <c r="L483" s="6"/>
       <c r="M483" s="7"/>
     </row>
-    <row r="484" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="484" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B484" s="5" t="s">
         <v>5</v>
       </c>
@@ -17966,7 +17956,7 @@
       <c r="L484" s="6"/>
       <c r="M484" s="7"/>
     </row>
-    <row r="485" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="485" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B485" s="5" t="s">
         <v>2</v>
       </c>
@@ -17994,7 +17984,7 @@
       <c r="L485" s="6"/>
       <c r="M485" s="7"/>
     </row>
-    <row r="486" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="486" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B486" s="5" t="s">
         <v>5</v>
       </c>
@@ -18022,7 +18012,7 @@
       <c r="L486" s="6"/>
       <c r="M486" s="7"/>
     </row>
-    <row r="487" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="487" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B487" s="5" t="s">
         <v>5</v>
       </c>
@@ -18050,7 +18040,7 @@
       <c r="L487" s="6"/>
       <c r="M487" s="7"/>
     </row>
-    <row r="488" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="488" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B488" s="5" t="s">
         <v>2</v>
       </c>
@@ -18078,7 +18068,7 @@
       <c r="L488" s="6"/>
       <c r="M488" s="7"/>
     </row>
-    <row r="489" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="489" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B489" s="5" t="s">
         <v>5</v>
       </c>
@@ -18106,7 +18096,7 @@
       <c r="L489" s="6"/>
       <c r="M489" s="7"/>
     </row>
-    <row r="490" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="490" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B490" s="5" t="s">
         <v>5</v>
       </c>
@@ -18134,7 +18124,7 @@
       <c r="L490" s="6"/>
       <c r="M490" s="7"/>
     </row>
-    <row r="491" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="491" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B491" s="5" t="s">
         <v>2</v>
       </c>
@@ -18162,7 +18152,7 @@
       <c r="L491" s="6"/>
       <c r="M491" s="7"/>
     </row>
-    <row r="492" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="492" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B492" s="5" t="s">
         <v>5</v>
       </c>
@@ -18190,7 +18180,7 @@
       <c r="L492" s="6"/>
       <c r="M492" s="7"/>
     </row>
-    <row r="493" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="493" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B493" s="5" t="s">
         <v>5</v>
       </c>
@@ -18218,7 +18208,7 @@
       <c r="L493" s="6"/>
       <c r="M493" s="7"/>
     </row>
-    <row r="494" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="494" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B494" s="5" t="s">
         <v>2</v>
       </c>
@@ -18246,7 +18236,7 @@
       <c r="L494" s="6"/>
       <c r="M494" s="7"/>
     </row>
-    <row r="495" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="495" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B495" s="5" t="s">
         <v>2</v>
       </c>
@@ -18274,7 +18264,7 @@
       <c r="L495" s="6"/>
       <c r="M495" s="7"/>
     </row>
-    <row r="496" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="496" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B496" s="5" t="s">
         <v>2</v>
       </c>
@@ -18302,7 +18292,7 @@
       <c r="L496" s="6"/>
       <c r="M496" s="7"/>
     </row>
-    <row r="497" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="497" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B497" s="5" t="s">
         <v>2</v>
       </c>
@@ -18330,7 +18320,7 @@
       <c r="L497" s="6"/>
       <c r="M497" s="7"/>
     </row>
-    <row r="498" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="498" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B498" s="5" t="s">
         <v>2</v>
       </c>
@@ -18358,7 +18348,7 @@
       <c r="L498" s="6"/>
       <c r="M498" s="7"/>
     </row>
-    <row r="499" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="499" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B499" s="5" t="s">
         <v>5</v>
       </c>
@@ -18386,7 +18376,7 @@
       <c r="L499" s="6"/>
       <c r="M499" s="7"/>
     </row>
-    <row r="500" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="500" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B500" s="5" t="s">
         <v>2</v>
       </c>
@@ -18414,7 +18404,7 @@
       <c r="L500" s="6"/>
       <c r="M500" s="7"/>
     </row>
-    <row r="501" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="501" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B501" s="5" t="s">
         <v>2</v>
       </c>
@@ -18442,7 +18432,7 @@
       <c r="L501" s="6"/>
       <c r="M501" s="7"/>
     </row>
-    <row r="502" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="502" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B502" s="5" t="s">
         <v>2</v>
       </c>
@@ -18470,7 +18460,7 @@
       <c r="L502" s="6"/>
       <c r="M502" s="7"/>
     </row>
-    <row r="503" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="503" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B503" s="5" t="s">
         <v>5</v>
       </c>
@@ -18498,7 +18488,7 @@
       <c r="L503" s="6"/>
       <c r="M503" s="7"/>
     </row>
-    <row r="504" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="504" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B504" s="5" t="s">
         <v>2</v>
       </c>
@@ -18526,7 +18516,7 @@
       <c r="L504" s="6"/>
       <c r="M504" s="7"/>
     </row>
-    <row r="505" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="505" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B505" s="5" t="s">
         <v>2</v>
       </c>
@@ -18554,7 +18544,7 @@
       <c r="L505" s="6"/>
       <c r="M505" s="7"/>
     </row>
-    <row r="506" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="506" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B506" s="5" t="s">
         <v>5</v>
       </c>
@@ -18582,7 +18572,7 @@
       <c r="L506" s="6"/>
       <c r="M506" s="7"/>
     </row>
-    <row r="507" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="507" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B507" s="5" t="s">
         <v>2</v>
       </c>
@@ -18610,7 +18600,7 @@
       <c r="L507" s="6"/>
       <c r="M507" s="7"/>
     </row>
-    <row r="508" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="508" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B508" s="5" t="s">
         <v>2</v>
       </c>
@@ -18638,7 +18628,7 @@
       <c r="L508" s="6"/>
       <c r="M508" s="7"/>
     </row>
-    <row r="509" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="509" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B509" s="5" t="s">
         <v>2</v>
       </c>
@@ -18666,7 +18656,7 @@
       <c r="L509" s="6"/>
       <c r="M509" s="7"/>
     </row>
-    <row r="510" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="510" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B510" s="5" t="s">
         <v>5</v>
       </c>
@@ -18694,7 +18684,7 @@
       <c r="L510" s="6"/>
       <c r="M510" s="7"/>
     </row>
-    <row r="511" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="511" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B511" s="5" t="s">
         <v>5</v>
       </c>
@@ -18722,7 +18712,7 @@
       <c r="L511" s="6"/>
       <c r="M511" s="7"/>
     </row>
-    <row r="512" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="512" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B512" s="5" t="s">
         <v>5</v>
       </c>
@@ -18750,7 +18740,7 @@
       <c r="L512" s="6"/>
       <c r="M512" s="7"/>
     </row>
-    <row r="513" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="513" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B513" s="5" t="s">
         <v>2</v>
       </c>
@@ -18778,7 +18768,7 @@
       <c r="L513" s="6"/>
       <c r="M513" s="7"/>
     </row>
-    <row r="514" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="514" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B514" s="5" t="s">
         <v>5</v>
       </c>
@@ -18806,7 +18796,7 @@
       <c r="L514" s="6"/>
       <c r="M514" s="7"/>
     </row>
-    <row r="515" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="515" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B515" s="5" t="s">
         <v>5</v>
       </c>
@@ -18834,7 +18824,7 @@
       <c r="L515" s="6"/>
       <c r="M515" s="7"/>
     </row>
-    <row r="516" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="516" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B516" s="5" t="s">
         <v>5</v>
       </c>
@@ -18862,7 +18852,7 @@
       <c r="L516" s="6"/>
       <c r="M516" s="7"/>
     </row>
-    <row r="517" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="517" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B517" s="5" t="s">
         <v>2</v>
       </c>
@@ -18890,7 +18880,7 @@
       <c r="L517" s="6"/>
       <c r="M517" s="7"/>
     </row>
-    <row r="518" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="518" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B518" s="5" t="s">
         <v>2</v>
       </c>
@@ -18918,7 +18908,7 @@
       <c r="L518" s="6"/>
       <c r="M518" s="7"/>
     </row>
-    <row r="519" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="519" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B519" s="5" t="s">
         <v>2</v>
       </c>
@@ -18946,7 +18936,7 @@
       <c r="L519" s="6"/>
       <c r="M519" s="7"/>
     </row>
-    <row r="520" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="520" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B520" s="5" t="s">
         <v>2</v>
       </c>
@@ -18974,7 +18964,7 @@
       <c r="L520" s="6"/>
       <c r="M520" s="7"/>
     </row>
-    <row r="521" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="521" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B521" s="5" t="s">
         <v>2</v>
       </c>
@@ -19002,7 +18992,7 @@
       <c r="L521" s="6"/>
       <c r="M521" s="7"/>
     </row>
-    <row r="522" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="522" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B522" s="5" t="s">
         <v>2</v>
       </c>
@@ -19030,7 +19020,7 @@
       <c r="L522" s="6"/>
       <c r="M522" s="7"/>
     </row>
-    <row r="523" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="523" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B523" s="5" t="s">
         <v>2</v>
       </c>
@@ -19058,7 +19048,7 @@
       <c r="L523" s="6"/>
       <c r="M523" s="7"/>
     </row>
-    <row r="524" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="524" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B524" s="5" t="s">
         <v>5</v>
       </c>
@@ -19086,7 +19076,7 @@
       <c r="L524" s="6"/>
       <c r="M524" s="7"/>
     </row>
-    <row r="525" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="525" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B525" s="5" t="s">
         <v>2</v>
       </c>
@@ -19114,7 +19104,7 @@
       <c r="L525" s="6"/>
       <c r="M525" s="7"/>
     </row>
-    <row r="526" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="526" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B526" s="5" t="s">
         <v>5</v>
       </c>
@@ -19142,7 +19132,7 @@
       <c r="L526" s="6"/>
       <c r="M526" s="7"/>
     </row>
-    <row r="527" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="527" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B527" s="5" t="s">
         <v>5</v>
       </c>
@@ -19170,7 +19160,7 @@
       <c r="L527" s="6"/>
       <c r="M527" s="7"/>
     </row>
-    <row r="528" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="528" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B528" s="5" t="s">
         <v>5</v>
       </c>
@@ -19198,7 +19188,7 @@
       <c r="L528" s="6"/>
       <c r="M528" s="7"/>
     </row>
-    <row r="529" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="529" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B529" s="5" t="s">
         <v>5</v>
       </c>
@@ -19226,7 +19216,7 @@
       <c r="L529" s="6"/>
       <c r="M529" s="7"/>
     </row>
-    <row r="530" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="530" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B530" s="5" t="s">
         <v>5</v>
       </c>
@@ -19254,7 +19244,7 @@
       <c r="L530" s="6"/>
       <c r="M530" s="7"/>
     </row>
-    <row r="531" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="531" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B531" s="5" t="s">
         <v>2</v>
       </c>
@@ -19282,7 +19272,7 @@
       <c r="L531" s="6"/>
       <c r="M531" s="7"/>
     </row>
-    <row r="532" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="532" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B532" s="5" t="s">
         <v>2</v>
       </c>
@@ -19310,7 +19300,7 @@
       <c r="L532" s="6"/>
       <c r="M532" s="7"/>
     </row>
-    <row r="533" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="533" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B533" s="5" t="s">
         <v>2</v>
       </c>
@@ -19338,7 +19328,7 @@
       <c r="L533" s="6"/>
       <c r="M533" s="7"/>
     </row>
-    <row r="534" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="534" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B534" s="5" t="s">
         <v>2</v>
       </c>
@@ -19366,7 +19356,7 @@
       <c r="L534" s="6"/>
       <c r="M534" s="7"/>
     </row>
-    <row r="535" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="535" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B535" s="5" t="s">
         <v>2</v>
       </c>
@@ -19394,7 +19384,7 @@
       <c r="L535" s="6"/>
       <c r="M535" s="7"/>
     </row>
-    <row r="536" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="536" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B536" s="5" t="s">
         <v>5</v>
       </c>
@@ -19422,7 +19412,7 @@
       <c r="L536" s="6"/>
       <c r="M536" s="7"/>
     </row>
-    <row r="537" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="537" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B537" s="5" t="s">
         <v>2</v>
       </c>
@@ -19450,7 +19440,7 @@
       <c r="L537" s="6"/>
       <c r="M537" s="7"/>
     </row>
-    <row r="538" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="538" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B538" s="5" t="s">
         <v>5</v>
       </c>
@@ -19478,7 +19468,7 @@
       <c r="L538" s="6"/>
       <c r="M538" s="7"/>
     </row>
-    <row r="539" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="539" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B539" s="5" t="s">
         <v>2</v>
       </c>
@@ -19506,7 +19496,7 @@
       <c r="L539" s="6"/>
       <c r="M539" s="7"/>
     </row>
-    <row r="540" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="540" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B540" s="5" t="s">
         <v>5</v>
       </c>
@@ -19534,7 +19524,7 @@
       <c r="L540" s="6"/>
       <c r="M540" s="7"/>
     </row>
-    <row r="541" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="541" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B541" s="5" t="s">
         <v>2</v>
       </c>
@@ -19562,7 +19552,7 @@
       <c r="L541" s="6"/>
       <c r="M541" s="7"/>
     </row>
-    <row r="542" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="542" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B542" s="5" t="s">
         <v>5</v>
       </c>
@@ -19590,7 +19580,7 @@
       <c r="L542" s="6"/>
       <c r="M542" s="7"/>
     </row>
-    <row r="543" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="543" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B543" s="5" t="s">
         <v>5</v>
       </c>
@@ -19618,7 +19608,7 @@
       <c r="L543" s="6"/>
       <c r="M543" s="7"/>
     </row>
-    <row r="544" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="544" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B544" s="5" t="s">
         <v>5</v>
       </c>
@@ -19646,7 +19636,7 @@
       <c r="L544" s="6"/>
       <c r="M544" s="7"/>
     </row>
-    <row r="545" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="545" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B545" s="5" t="s">
         <v>5</v>
       </c>
@@ -19674,7 +19664,7 @@
       <c r="L545" s="6"/>
       <c r="M545" s="7"/>
     </row>
-    <row r="546" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="546" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B546" s="5" t="s">
         <v>2</v>
       </c>
@@ -19702,7 +19692,7 @@
       <c r="L546" s="6"/>
       <c r="M546" s="7"/>
     </row>
-    <row r="547" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="547" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B547" s="5" t="s">
         <v>2</v>
       </c>
@@ -19730,7 +19720,7 @@
       <c r="L547" s="6"/>
       <c r="M547" s="7"/>
     </row>
-    <row r="548" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="548" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B548" s="5" t="s">
         <v>2</v>
       </c>
@@ -19758,7 +19748,7 @@
       <c r="L548" s="6"/>
       <c r="M548" s="7"/>
     </row>
-    <row r="549" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="549" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B549" s="5" t="s">
         <v>5</v>
       </c>
@@ -19786,7 +19776,7 @@
       <c r="L549" s="6"/>
       <c r="M549" s="7"/>
     </row>
-    <row r="550" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="550" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B550" s="5" t="s">
         <v>2</v>
       </c>
@@ -19814,7 +19804,7 @@
       <c r="L550" s="6"/>
       <c r="M550" s="7"/>
     </row>
-    <row r="551" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="551" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B551" s="5" t="s">
         <v>5</v>
       </c>
@@ -19842,7 +19832,7 @@
       <c r="L551" s="6"/>
       <c r="M551" s="7"/>
     </row>
-    <row r="552" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="552" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B552" s="5" t="s">
         <v>2</v>
       </c>
@@ -19870,7 +19860,7 @@
       <c r="L552" s="6"/>
       <c r="M552" s="7"/>
     </row>
-    <row r="553" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="553" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B553" s="5" t="s">
         <v>5</v>
       </c>
@@ -19898,7 +19888,7 @@
       <c r="L553" s="6"/>
       <c r="M553" s="7"/>
     </row>
-    <row r="554" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="554" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B554" s="5" t="s">
         <v>5</v>
       </c>
@@ -19926,7 +19916,7 @@
       <c r="L554" s="6"/>
       <c r="M554" s="7"/>
     </row>
-    <row r="555" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="555" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B555" s="5" t="s">
         <v>5</v>
       </c>
@@ -19954,7 +19944,7 @@
       <c r="L555" s="6"/>
       <c r="M555" s="7"/>
     </row>
-    <row r="556" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="556" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B556" s="5" t="s">
         <v>2</v>
       </c>
@@ -19982,7 +19972,7 @@
       <c r="L556" s="6"/>
       <c r="M556" s="7"/>
     </row>
-    <row r="557" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="557" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B557" s="5" t="s">
         <v>5</v>
       </c>
@@ -20010,7 +20000,7 @@
       <c r="L557" s="6"/>
       <c r="M557" s="7"/>
     </row>
-    <row r="558" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="558" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B558" s="5" t="s">
         <v>5</v>
       </c>
@@ -20038,7 +20028,7 @@
       <c r="L558" s="6"/>
       <c r="M558" s="7"/>
     </row>
-    <row r="559" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="559" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B559" s="5" t="s">
         <v>2</v>
       </c>
@@ -20066,7 +20056,7 @@
       <c r="L559" s="6"/>
       <c r="M559" s="7"/>
     </row>
-    <row r="560" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="560" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B560" s="5" t="s">
         <v>2</v>
       </c>
@@ -20094,7 +20084,7 @@
       <c r="L560" s="6"/>
       <c r="M560" s="7"/>
     </row>
-    <row r="561" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="561" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B561" s="5" t="s">
         <v>5</v>
       </c>
@@ -20122,7 +20112,7 @@
       <c r="L561" s="6"/>
       <c r="M561" s="7"/>
     </row>
-    <row r="562" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="562" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B562" s="5" t="s">
         <v>2</v>
       </c>
@@ -20150,7 +20140,7 @@
       <c r="L562" s="6"/>
       <c r="M562" s="7"/>
     </row>
-    <row r="563" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="563" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B563" s="5" t="s">
         <v>5</v>
       </c>
@@ -20178,7 +20168,7 @@
       <c r="L563" s="6"/>
       <c r="M563" s="7"/>
     </row>
-    <row r="564" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="564" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B564" s="5" t="s">
         <v>2</v>
       </c>
@@ -20206,7 +20196,7 @@
       <c r="L564" s="6"/>
       <c r="M564" s="7"/>
     </row>
-    <row r="565" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="565" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B565" s="5" t="s">
         <v>2</v>
       </c>
@@ -20234,7 +20224,7 @@
       <c r="L565" s="6"/>
       <c r="M565" s="7"/>
     </row>
-    <row r="566" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="566" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B566" s="5" t="s">
         <v>5</v>
       </c>
@@ -20262,7 +20252,7 @@
       <c r="L566" s="6"/>
       <c r="M566" s="7"/>
     </row>
-    <row r="567" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="567" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B567" s="5" t="s">
         <v>2</v>
       </c>
@@ -20290,7 +20280,7 @@
       <c r="L567" s="6"/>
       <c r="M567" s="7"/>
     </row>
-    <row r="568" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="568" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B568" s="5" t="s">
         <v>5</v>
       </c>
@@ -20318,7 +20308,7 @@
       <c r="L568" s="6"/>
       <c r="M568" s="7"/>
     </row>
-    <row r="569" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="569" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B569" s="5" t="s">
         <v>5</v>
       </c>
@@ -20346,7 +20336,7 @@
       <c r="L569" s="6"/>
       <c r="M569" s="7"/>
     </row>
-    <row r="570" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="570" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B570" s="5" t="s">
         <v>2</v>
       </c>
@@ -20374,7 +20364,7 @@
       <c r="L570" s="6"/>
       <c r="M570" s="7"/>
     </row>
-    <row r="571" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="571" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B571" s="5" t="s">
         <v>2</v>
       </c>
@@ -20402,7 +20392,7 @@
       <c r="L571" s="6"/>
       <c r="M571" s="7"/>
     </row>
-    <row r="572" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="572" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B572" s="5" t="s">
         <v>5</v>
       </c>
@@ -20430,7 +20420,7 @@
       <c r="L572" s="6"/>
       <c r="M572" s="7"/>
     </row>
-    <row r="573" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="573" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B573" s="5" t="s">
         <v>5</v>
       </c>
@@ -20458,7 +20448,7 @@
       <c r="L573" s="6"/>
       <c r="M573" s="7"/>
     </row>
-    <row r="574" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="574" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B574" s="5" t="s">
         <v>5</v>
       </c>
@@ -20486,7 +20476,7 @@
       <c r="L574" s="6"/>
       <c r="M574" s="7"/>
     </row>
-    <row r="575" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="575" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B575" s="5" t="s">
         <v>5</v>
       </c>
@@ -20514,7 +20504,7 @@
       <c r="L575" s="6"/>
       <c r="M575" s="7"/>
     </row>
-    <row r="576" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="576" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B576" s="5" t="s">
         <v>2</v>
       </c>
@@ -20542,7 +20532,7 @@
       <c r="L576" s="6"/>
       <c r="M576" s="7"/>
     </row>
-    <row r="577" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="577" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B577" s="5" t="s">
         <v>2</v>
       </c>
@@ -20570,7 +20560,7 @@
       <c r="L577" s="6"/>
       <c r="M577" s="7"/>
     </row>
-    <row r="578" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="578" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B578" s="5" t="s">
         <v>2</v>
       </c>
@@ -20598,7 +20588,7 @@
       <c r="L578" s="6"/>
       <c r="M578" s="7"/>
     </row>
-    <row r="579" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="579" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B579" s="5" t="s">
         <v>5</v>
       </c>
@@ -20626,7 +20616,7 @@
       <c r="L579" s="6"/>
       <c r="M579" s="7"/>
     </row>
-    <row r="580" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="580" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B580" s="5" t="s">
         <v>5</v>
       </c>
@@ -20654,7 +20644,7 @@
       <c r="L580" s="6"/>
       <c r="M580" s="7"/>
     </row>
-    <row r="581" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="581" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B581" s="5" t="s">
         <v>2</v>
       </c>
@@ -20682,7 +20672,7 @@
       <c r="L581" s="6"/>
       <c r="M581" s="7"/>
     </row>
-    <row r="582" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="582" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B582" s="5" t="s">
         <v>2</v>
       </c>
@@ -20710,7 +20700,7 @@
       <c r="L582" s="6"/>
       <c r="M582" s="7"/>
     </row>
-    <row r="583" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="583" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B583" s="5" t="s">
         <v>2</v>
       </c>
@@ -20738,7 +20728,7 @@
       <c r="L583" s="6"/>
       <c r="M583" s="7"/>
     </row>
-    <row r="584" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="584" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B584" s="5" t="s">
         <v>2</v>
       </c>
@@ -20766,7 +20756,7 @@
       <c r="L584" s="6"/>
       <c r="M584" s="7"/>
     </row>
-    <row r="585" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="585" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B585" s="5" t="s">
         <v>2</v>
       </c>
@@ -20794,7 +20784,7 @@
       <c r="L585" s="6"/>
       <c r="M585" s="7"/>
     </row>
-    <row r="586" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="586" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B586" s="5" t="s">
         <v>2</v>
       </c>
@@ -20822,7 +20812,7 @@
       <c r="L586" s="6"/>
       <c r="M586" s="7"/>
     </row>
-    <row r="587" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="587" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B587" s="5" t="s">
         <v>2</v>
       </c>
@@ -20850,7 +20840,7 @@
       <c r="L587" s="6"/>
       <c r="M587" s="7"/>
     </row>
-    <row r="588" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="588" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B588" s="5" t="s">
         <v>2</v>
       </c>
@@ -20878,7 +20868,7 @@
       <c r="L588" s="6"/>
       <c r="M588" s="7"/>
     </row>
-    <row r="589" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="589" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B589" s="5" t="s">
         <v>2</v>
       </c>
@@ -20906,7 +20896,7 @@
       <c r="L589" s="6"/>
       <c r="M589" s="7"/>
     </row>
-    <row r="590" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="590" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B590" s="5" t="s">
         <v>2</v>
       </c>
@@ -20934,7 +20924,7 @@
       <c r="L590" s="6"/>
       <c r="M590" s="7"/>
     </row>
-    <row r="591" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="591" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B591" s="5" t="s">
         <v>2</v>
       </c>
@@ -20962,7 +20952,7 @@
       <c r="L591" s="6"/>
       <c r="M591" s="7"/>
     </row>
-    <row r="592" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="592" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B592" s="5" t="s">
         <v>2</v>
       </c>
@@ -20990,7 +20980,7 @@
       <c r="L592" s="6"/>
       <c r="M592" s="7"/>
     </row>
-    <row r="593" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="593" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B593" s="5" t="s">
         <v>2</v>
       </c>
@@ -21018,7 +21008,7 @@
       <c r="L593" s="6"/>
       <c r="M593" s="7"/>
     </row>
-    <row r="594" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="594" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B594" s="5" t="s">
         <v>5</v>
       </c>
@@ -21046,7 +21036,7 @@
       <c r="L594" s="6"/>
       <c r="M594" s="7"/>
     </row>
-    <row r="595" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="595" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B595" s="5" t="s">
         <v>5</v>
       </c>
@@ -21074,7 +21064,7 @@
       <c r="L595" s="6"/>
       <c r="M595" s="7"/>
     </row>
-    <row r="596" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="596" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B596" s="5" t="s">
         <v>5</v>
       </c>
@@ -21102,7 +21092,7 @@
       <c r="L596" s="6"/>
       <c r="M596" s="7"/>
     </row>
-    <row r="597" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="597" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B597" s="5" t="s">
         <v>2</v>
       </c>
@@ -21130,7 +21120,7 @@
       <c r="L597" s="6"/>
       <c r="M597" s="7"/>
     </row>
-    <row r="598" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="598" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B598" s="5" t="s">
         <v>2</v>
       </c>
@@ -21158,7 +21148,7 @@
       <c r="L598" s="6"/>
       <c r="M598" s="7"/>
     </row>
-    <row r="599" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="599" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B599" s="5" t="s">
         <v>2</v>
       </c>
@@ -21186,7 +21176,7 @@
       <c r="L599" s="6"/>
       <c r="M599" s="7"/>
     </row>
-    <row r="600" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="600" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B600" s="5" t="s">
         <v>5</v>
       </c>
@@ -21214,7 +21204,7 @@
       <c r="L600" s="6"/>
       <c r="M600" s="7"/>
     </row>
-    <row r="601" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="601" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B601" s="5" t="s">
         <v>5</v>
       </c>
@@ -21242,7 +21232,7 @@
       <c r="L601" s="6"/>
       <c r="M601" s="7"/>
     </row>
-    <row r="602" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="602" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B602" s="5" t="s">
         <v>2</v>
       </c>
@@ -21270,7 +21260,7 @@
       <c r="L602" s="6"/>
       <c r="M602" s="7"/>
     </row>
-    <row r="603" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="603" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B603" s="5" t="s">
         <v>2</v>
       </c>
@@ -21298,7 +21288,7 @@
       <c r="L603" s="6"/>
       <c r="M603" s="7"/>
     </row>
-    <row r="604" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="604" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B604" s="5" t="s">
         <v>2</v>
       </c>
@@ -21326,7 +21316,7 @@
       <c r="L604" s="6"/>
       <c r="M604" s="7"/>
     </row>
-    <row r="605" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="605" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B605" s="5" t="s">
         <v>2</v>
       </c>
@@ -21354,7 +21344,7 @@
       <c r="L605" s="6"/>
       <c r="M605" s="7"/>
     </row>
-    <row r="606" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="606" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B606" s="5" t="s">
         <v>2</v>
       </c>
@@ -21382,7 +21372,7 @@
       <c r="L606" s="6"/>
       <c r="M606" s="7"/>
     </row>
-    <row r="607" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="607" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B607" s="5" t="s">
         <v>5</v>
       </c>
@@ -21410,7 +21400,7 @@
       <c r="L607" s="6"/>
       <c r="M607" s="7"/>
     </row>
-    <row r="608" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="608" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B608" s="5" t="s">
         <v>5</v>
       </c>
@@ -21438,7 +21428,7 @@
       <c r="L608" s="6"/>
       <c r="M608" s="7"/>
     </row>
-    <row r="609" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="609" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B609" s="5" t="s">
         <v>5</v>
       </c>
@@ -21466,7 +21456,7 @@
       <c r="L609" s="6"/>
       <c r="M609" s="7"/>
     </row>
-    <row r="610" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="610" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B610" s="5" t="s">
         <v>2</v>
       </c>
@@ -21494,7 +21484,7 @@
       <c r="L610" s="6"/>
       <c r="M610" s="7"/>
     </row>
-    <row r="611" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="611" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B611" s="5" t="s">
         <v>2</v>
       </c>
@@ -21522,7 +21512,7 @@
       <c r="L611" s="6"/>
       <c r="M611" s="7"/>
     </row>
-    <row r="612" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="612" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B612" s="5" t="s">
         <v>2</v>
       </c>
@@ -21550,7 +21540,7 @@
       <c r="L612" s="6"/>
       <c r="M612" s="7"/>
     </row>
-    <row r="613" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="613" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B613" s="5" t="s">
         <v>2</v>
       </c>
@@ -21578,7 +21568,7 @@
       <c r="L613" s="6"/>
       <c r="M613" s="7"/>
     </row>
-    <row r="614" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="614" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B614" s="5" t="s">
         <v>5</v>
       </c>
@@ -21606,7 +21596,7 @@
       <c r="L614" s="6"/>
       <c r="M614" s="7"/>
     </row>
-    <row r="615" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="615" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B615" s="5" t="s">
         <v>2</v>
       </c>
@@ -21634,7 +21624,7 @@
       <c r="L615" s="6"/>
       <c r="M615" s="7"/>
     </row>
-    <row r="616" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="616" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B616" s="5" t="s">
         <v>5</v>
       </c>
@@ -21662,7 +21652,7 @@
       <c r="L616" s="6"/>
       <c r="M616" s="7"/>
     </row>
-    <row r="617" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="617" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B617" s="5" t="s">
         <v>2</v>
       </c>
@@ -21690,7 +21680,7 @@
       <c r="L617" s="6"/>
       <c r="M617" s="7"/>
     </row>
-    <row r="618" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="618" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B618" s="5" t="s">
         <v>2</v>
       </c>
@@ -21718,7 +21708,7 @@
       <c r="L618" s="6"/>
       <c r="M618" s="7"/>
     </row>
-    <row r="619" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="619" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B619" s="5" t="s">
         <v>2</v>
       </c>
@@ -21746,7 +21736,7 @@
       <c r="L619" s="6"/>
       <c r="M619" s="7"/>
     </row>
-    <row r="620" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="620" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B620" s="5" t="s">
         <v>2</v>
       </c>
@@ -21774,7 +21764,7 @@
       <c r="L620" s="6"/>
       <c r="M620" s="7"/>
     </row>
-    <row r="621" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="621" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B621" s="5" t="s">
         <v>5</v>
       </c>
@@ -21802,7 +21792,7 @@
       <c r="L621" s="6"/>
       <c r="M621" s="7"/>
     </row>
-    <row r="622" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="622" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B622" s="5" t="s">
         <v>5</v>
       </c>
@@ -21830,7 +21820,7 @@
       <c r="L622" s="6"/>
       <c r="M622" s="7"/>
     </row>
-    <row r="623" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="623" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B623" s="5" t="s">
         <v>5</v>
       </c>
@@ -21858,7 +21848,7 @@
       <c r="L623" s="6"/>
       <c r="M623" s="7"/>
     </row>
-    <row r="624" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="624" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B624" s="5" t="s">
         <v>2</v>
       </c>
@@ -21886,7 +21876,7 @@
       <c r="L624" s="6"/>
       <c r="M624" s="7"/>
     </row>
-    <row r="625" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="625" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B625" s="5" t="s">
         <v>5</v>
       </c>
@@ -21914,7 +21904,7 @@
       <c r="L625" s="6"/>
       <c r="M625" s="7"/>
     </row>
-    <row r="626" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="626" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B626" s="5" t="s">
         <v>5</v>
       </c>
@@ -21942,7 +21932,7 @@
       <c r="L626" s="6"/>
       <c r="M626" s="7"/>
     </row>
-    <row r="627" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="627" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B627" s="5" t="s">
         <v>5</v>
       </c>
@@ -21970,7 +21960,7 @@
       <c r="L627" s="6"/>
       <c r="M627" s="7"/>
     </row>
-    <row r="628" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="628" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B628" s="5" t="s">
         <v>2</v>
       </c>
@@ -21998,7 +21988,7 @@
       <c r="L628" s="6"/>
       <c r="M628" s="7"/>
     </row>
-    <row r="629" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="629" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B629" s="5" t="s">
         <v>5</v>
       </c>
@@ -22026,7 +22016,7 @@
       <c r="L629" s="6"/>
       <c r="M629" s="7"/>
     </row>
-    <row r="630" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="630" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B630" s="5" t="s">
         <v>5</v>
       </c>
@@ -22054,7 +22044,7 @@
       <c r="L630" s="6"/>
       <c r="M630" s="7"/>
     </row>
-    <row r="631" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="631" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B631" s="5" t="s">
         <v>5</v>
       </c>
@@ -22082,7 +22072,7 @@
       <c r="L631" s="6"/>
       <c r="M631" s="7"/>
     </row>
-    <row r="632" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="632" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B632" s="5" t="s">
         <v>5</v>
       </c>
@@ -22110,7 +22100,7 @@
       <c r="L632" s="6"/>
       <c r="M632" s="7"/>
     </row>
-    <row r="633" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="633" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B633" s="5" t="s">
         <v>2</v>
       </c>
@@ -22138,7 +22128,7 @@
       <c r="L633" s="6"/>
       <c r="M633" s="7"/>
     </row>
-    <row r="634" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="634" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B634" s="5" t="s">
         <v>5</v>
       </c>
@@ -22166,7 +22156,7 @@
       <c r="L634" s="6"/>
       <c r="M634" s="7"/>
     </row>
-    <row r="635" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="635" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B635" s="5" t="s">
         <v>5</v>
       </c>
@@ -22194,7 +22184,7 @@
       <c r="L635" s="6"/>
       <c r="M635" s="7"/>
     </row>
-    <row r="636" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="636" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B636" s="5" t="s">
         <v>2</v>
       </c>
@@ -22222,7 +22212,7 @@
       <c r="L636" s="6"/>
       <c r="M636" s="7"/>
     </row>
-    <row r="637" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="637" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B637" s="5" t="s">
         <v>2</v>
       </c>
@@ -22250,7 +22240,7 @@
       <c r="L637" s="6"/>
       <c r="M637" s="7"/>
     </row>
-    <row r="638" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="638" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B638" s="5" t="s">
         <v>5</v>
       </c>
@@ -22278,7 +22268,7 @@
       <c r="L638" s="6"/>
       <c r="M638" s="7"/>
     </row>
-    <row r="639" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="639" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B639" s="5" t="s">
         <v>5</v>
       </c>
@@ -22306,7 +22296,7 @@
       <c r="L639" s="6"/>
       <c r="M639" s="7"/>
     </row>
-    <row r="640" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="640" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B640" s="5" t="s">
         <v>2</v>
       </c>
@@ -22334,7 +22324,7 @@
       <c r="L640" s="6"/>
       <c r="M640" s="7"/>
     </row>
-    <row r="641" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="641" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B641" s="5" t="s">
         <v>2</v>
       </c>
@@ -22362,7 +22352,7 @@
       <c r="L641" s="6"/>
       <c r="M641" s="7"/>
     </row>
-    <row r="642" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="642" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B642" s="5" t="s">
         <v>5</v>
       </c>
@@ -22390,7 +22380,7 @@
       <c r="L642" s="6"/>
       <c r="M642" s="7"/>
     </row>
-    <row r="643" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="643" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B643" s="5" t="s">
         <v>2</v>
       </c>
@@ -22418,7 +22408,7 @@
       <c r="L643" s="6"/>
       <c r="M643" s="7"/>
     </row>
-    <row r="644" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="644" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B644" s="5" t="s">
         <v>5</v>
       </c>
@@ -22446,7 +22436,7 @@
       <c r="L644" s="6"/>
       <c r="M644" s="7"/>
     </row>
-    <row r="645" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="645" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B645" s="5" t="s">
         <v>2</v>
       </c>
@@ -22474,7 +22464,7 @@
       <c r="L645" s="6"/>
       <c r="M645" s="7"/>
     </row>
-    <row r="646" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="646" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B646" s="5" t="s">
         <v>2</v>
       </c>
@@ -22502,7 +22492,7 @@
       <c r="L646" s="6"/>
       <c r="M646" s="7"/>
     </row>
-    <row r="647" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="647" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B647" s="5" t="s">
         <v>2</v>
       </c>
@@ -22530,7 +22520,7 @@
       <c r="L647" s="6"/>
       <c r="M647" s="7"/>
     </row>
-    <row r="648" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="648" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B648" s="5" t="s">
         <v>5</v>
       </c>
@@ -22558,7 +22548,7 @@
       <c r="L648" s="6"/>
       <c r="M648" s="7"/>
     </row>
-    <row r="649" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="649" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B649" s="5" t="s">
         <v>2</v>
       </c>
@@ -22586,7 +22576,7 @@
       <c r="L649" s="6"/>
       <c r="M649" s="7"/>
     </row>
-    <row r="650" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="650" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B650" s="5" t="s">
         <v>2</v>
       </c>
@@ -22614,7 +22604,7 @@
       <c r="L650" s="6"/>
       <c r="M650" s="7"/>
     </row>
-    <row r="651" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="651" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B651" s="5" t="s">
         <v>2</v>
       </c>
@@ -22642,7 +22632,7 @@
       <c r="L651" s="6"/>
       <c r="M651" s="7"/>
     </row>
-    <row r="652" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="652" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B652" s="5" t="s">
         <v>2</v>
       </c>
@@ -22670,7 +22660,7 @@
       <c r="L652" s="6"/>
       <c r="M652" s="7"/>
     </row>
-    <row r="653" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="653" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B653" s="5" t="s">
         <v>2</v>
       </c>
@@ -22698,7 +22688,7 @@
       <c r="L653" s="6"/>
       <c r="M653" s="7"/>
     </row>
-    <row r="654" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="654" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B654" s="5" t="s">
         <v>5</v>
       </c>
@@ -22726,7 +22716,7 @@
       <c r="L654" s="6"/>
       <c r="M654" s="7"/>
     </row>
-    <row r="655" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="655" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B655" s="5" t="s">
         <v>2</v>
       </c>
@@ -22754,7 +22744,7 @@
       <c r="L655" s="6"/>
       <c r="M655" s="7"/>
     </row>
-    <row r="656" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="656" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B656" s="5" t="s">
         <v>2</v>
       </c>
@@ -22782,7 +22772,7 @@
       <c r="L656" s="6"/>
       <c r="M656" s="7"/>
     </row>
-    <row r="657" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="657" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B657" s="5" t="s">
         <v>2</v>
       </c>
@@ -22810,7 +22800,7 @@
       <c r="L657" s="6"/>
       <c r="M657" s="7"/>
     </row>
-    <row r="658" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="658" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B658" s="5" t="s">
         <v>2</v>
       </c>
@@ -22838,7 +22828,7 @@
       <c r="L658" s="6"/>
       <c r="M658" s="7"/>
     </row>
-    <row r="659" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="659" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B659" s="5" t="s">
         <v>2</v>
       </c>
@@ -22866,7 +22856,7 @@
       <c r="L659" s="6"/>
       <c r="M659" s="7"/>
     </row>
-    <row r="660" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="660" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B660" s="5" t="s">
         <v>5</v>
       </c>
@@ -22894,7 +22884,7 @@
       <c r="L660" s="6"/>
       <c r="M660" s="7"/>
     </row>
-    <row r="661" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="661" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B661" s="5" t="s">
         <v>5</v>
       </c>
@@ -22922,7 +22912,7 @@
       <c r="L661" s="6"/>
       <c r="M661" s="7"/>
     </row>
-    <row r="662" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="662" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B662" s="5" t="s">
         <v>2</v>
       </c>
@@ -22950,7 +22940,7 @@
       <c r="L662" s="6"/>
       <c r="M662" s="7"/>
     </row>
-    <row r="663" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="663" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B663" s="5" t="s">
         <v>5</v>
       </c>
@@ -22978,7 +22968,7 @@
       <c r="L663" s="6"/>
       <c r="M663" s="7"/>
     </row>
-    <row r="664" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="664" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B664" s="5" t="s">
         <v>5</v>
       </c>
@@ -23006,7 +22996,7 @@
       <c r="L664" s="6"/>
       <c r="M664" s="7"/>
     </row>
-    <row r="665" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="665" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B665" s="5" t="s">
         <v>5</v>
       </c>
@@ -23034,7 +23024,7 @@
       <c r="L665" s="6"/>
       <c r="M665" s="7"/>
     </row>
-    <row r="666" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="666" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B666" s="5" t="s">
         <v>2</v>
       </c>
@@ -23062,7 +23052,7 @@
       <c r="L666" s="6"/>
       <c r="M666" s="7"/>
     </row>
-    <row r="667" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="667" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B667" s="5" t="s">
         <v>2</v>
       </c>
@@ -23090,7 +23080,7 @@
       <c r="L667" s="6"/>
       <c r="M667" s="7"/>
     </row>
-    <row r="668" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="668" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B668" s="5" t="s">
         <v>5</v>
       </c>
@@ -23118,7 +23108,7 @@
       <c r="L668" s="6"/>
       <c r="M668" s="7"/>
     </row>
-    <row r="669" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="669" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B669" s="5" t="s">
         <v>2</v>
       </c>
@@ -23146,7 +23136,7 @@
       <c r="L669" s="6"/>
       <c r="M669" s="7"/>
     </row>
-    <row r="670" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="670" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B670" s="5" t="s">
         <v>2</v>
       </c>
@@ -23174,7 +23164,7 @@
       <c r="L670" s="6"/>
       <c r="M670" s="7"/>
     </row>
-    <row r="671" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="671" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B671" s="5" t="s">
         <v>2</v>
       </c>
@@ -23202,7 +23192,7 @@
       <c r="L671" s="6"/>
       <c r="M671" s="7"/>
     </row>
-    <row r="672" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="672" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B672" s="5" t="s">
         <v>5</v>
       </c>
@@ -23230,7 +23220,7 @@
       <c r="L672" s="6"/>
       <c r="M672" s="7"/>
     </row>
-    <row r="673" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="673" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B673" s="5" t="s">
         <v>5</v>
       </c>
@@ -23258,7 +23248,7 @@
       <c r="L673" s="6"/>
       <c r="M673" s="7"/>
     </row>
-    <row r="674" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="674" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B674" s="5" t="s">
         <v>2</v>
       </c>
@@ -23286,7 +23276,7 @@
       <c r="L674" s="6"/>
       <c r="M674" s="7"/>
     </row>
-    <row r="675" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="675" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B675" s="5" t="s">
         <v>5</v>
       </c>
@@ -23314,7 +23304,7 @@
       <c r="L675" s="6"/>
       <c r="M675" s="7"/>
     </row>
-    <row r="676" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="676" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B676" s="5" t="s">
         <v>2</v>
       </c>
@@ -23342,7 +23332,7 @@
       <c r="L676" s="6"/>
       <c r="M676" s="7"/>
     </row>
-    <row r="677" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="677" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B677" s="5" t="s">
         <v>2</v>
       </c>
@@ -23370,7 +23360,7 @@
       <c r="L677" s="6"/>
       <c r="M677" s="7"/>
     </row>
-    <row r="678" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="678" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B678" s="5" t="s">
         <v>2</v>
       </c>
@@ -23398,7 +23388,7 @@
       <c r="L678" s="6"/>
       <c r="M678" s="7"/>
     </row>
-    <row r="679" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="679" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B679" s="5" t="s">
         <v>2</v>
       </c>
@@ -23426,7 +23416,7 @@
       <c r="L679" s="6"/>
       <c r="M679" s="7"/>
     </row>
-    <row r="680" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="680" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B680" s="5" t="s">
         <v>2</v>
       </c>
@@ -23454,7 +23444,7 @@
       <c r="L680" s="6"/>
       <c r="M680" s="7"/>
     </row>
-    <row r="681" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="681" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B681" s="5" t="s">
         <v>2</v>
       </c>
@@ -23482,7 +23472,7 @@
       <c r="L681" s="6"/>
       <c r="M681" s="7"/>
     </row>
-    <row r="682" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="682" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B682" s="5" t="s">
         <v>5</v>
       </c>
@@ -23510,7 +23500,7 @@
       <c r="L682" s="6"/>
       <c r="M682" s="7"/>
     </row>
-    <row r="683" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="683" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B683" s="5" t="s">
         <v>5</v>
       </c>
@@ -23538,7 +23528,7 @@
       <c r="L683" s="6"/>
       <c r="M683" s="7"/>
     </row>
-    <row r="684" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="684" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B684" s="5" t="s">
         <v>2</v>
       </c>
@@ -23566,7 +23556,7 @@
       <c r="L684" s="6"/>
       <c r="M684" s="7"/>
     </row>
-    <row r="685" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="685" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B685" s="5" t="s">
         <v>5</v>
       </c>
@@ -23594,7 +23584,7 @@
       <c r="L685" s="6"/>
       <c r="M685" s="7"/>
     </row>
-    <row r="686" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="686" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B686" s="5" t="s">
         <v>5</v>
       </c>
@@ -23622,7 +23612,7 @@
       <c r="L686" s="6"/>
       <c r="M686" s="7"/>
     </row>
-    <row r="687" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="687" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B687" s="5" t="s">
         <v>2</v>
       </c>
@@ -23650,7 +23640,7 @@
       <c r="L687" s="6"/>
       <c r="M687" s="7"/>
     </row>
-    <row r="688" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="688" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B688" s="5" t="s">
         <v>5</v>
       </c>
@@ -23678,7 +23668,7 @@
       <c r="L688" s="6"/>
       <c r="M688" s="7"/>
     </row>
-    <row r="689" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="689" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B689" s="5" t="s">
         <v>2</v>
       </c>
@@ -23706,7 +23696,7 @@
       <c r="L689" s="6"/>
       <c r="M689" s="7"/>
     </row>
-    <row r="690" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="690" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B690" s="5" t="s">
         <v>5</v>
       </c>
@@ -23734,7 +23724,7 @@
       <c r="L690" s="6"/>
       <c r="M690" s="7"/>
     </row>
-    <row r="691" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="691" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B691" s="5" t="s">
         <v>5</v>
       </c>
@@ -23762,7 +23752,7 @@
       <c r="L691" s="6"/>
       <c r="M691" s="7"/>
     </row>
-    <row r="692" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="692" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B692" s="5" t="s">
         <v>5</v>
       </c>
@@ -23790,7 +23780,7 @@
       <c r="L692" s="6"/>
       <c r="M692" s="7"/>
     </row>
-    <row r="693" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="693" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B693" s="5" t="s">
         <v>5</v>
       </c>
@@ -23818,7 +23808,7 @@
       <c r="L693" s="6"/>
       <c r="M693" s="7"/>
     </row>
-    <row r="694" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="694" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B694" s="5" t="s">
         <v>2</v>
       </c>
@@ -23846,7 +23836,7 @@
       <c r="L694" s="6"/>
       <c r="M694" s="7"/>
     </row>
-    <row r="695" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="695" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B695" s="5" t="s">
         <v>2</v>
       </c>
@@ -23874,7 +23864,7 @@
       <c r="L695" s="6"/>
       <c r="M695" s="7"/>
     </row>
-    <row r="696" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="696" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B696" s="5" t="s">
         <v>2</v>
       </c>
@@ -23902,7 +23892,7 @@
       <c r="L696" s="6"/>
       <c r="M696" s="7"/>
     </row>
-    <row r="697" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="697" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B697" s="5" t="s">
         <v>2</v>
       </c>
@@ -23930,7 +23920,7 @@
       <c r="L697" s="6"/>
       <c r="M697" s="7"/>
     </row>
-    <row r="698" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="698" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B698" s="5" t="s">
         <v>2</v>
       </c>
@@ -23958,7 +23948,7 @@
       <c r="L698" s="6"/>
       <c r="M698" s="7"/>
     </row>
-    <row r="699" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="699" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B699" s="5" t="s">
         <v>2</v>
       </c>
@@ -23986,7 +23976,7 @@
       <c r="L699" s="6"/>
       <c r="M699" s="7"/>
     </row>
-    <row r="700" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="700" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B700" s="5" t="s">
         <v>2</v>
       </c>
@@ -24014,7 +24004,7 @@
       <c r="L700" s="6"/>
       <c r="M700" s="7"/>
     </row>
-    <row r="701" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="701" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B701" s="5" t="s">
         <v>2</v>
       </c>
@@ -24042,7 +24032,7 @@
       <c r="L701" s="6"/>
       <c r="M701" s="7"/>
     </row>
-    <row r="702" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="702" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B702" s="5" t="s">
         <v>2</v>
       </c>
@@ -24070,7 +24060,7 @@
       <c r="L702" s="6"/>
       <c r="M702" s="7"/>
     </row>
-    <row r="703" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="703" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B703" s="5" t="s">
         <v>5</v>
       </c>
@@ -24098,7 +24088,7 @@
       <c r="L703" s="6"/>
       <c r="M703" s="7"/>
     </row>
-    <row r="704" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="704" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B704" s="5" t="s">
         <v>2</v>
       </c>
@@ -24126,7 +24116,7 @@
       <c r="L704" s="6"/>
       <c r="M704" s="7"/>
     </row>
-    <row r="705" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="705" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B705" s="5" t="s">
         <v>2</v>
       </c>
@@ -24154,7 +24144,7 @@
       <c r="L705" s="6"/>
       <c r="M705" s="7"/>
     </row>
-    <row r="706" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="706" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B706" s="5" t="s">
         <v>5</v>
       </c>
@@ -24182,7 +24172,7 @@
       <c r="L706" s="6"/>
       <c r="M706" s="7"/>
     </row>
-    <row r="707" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="707" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B707" s="5" t="s">
         <v>2</v>
       </c>
@@ -24210,7 +24200,7 @@
       <c r="L707" s="6"/>
       <c r="M707" s="7"/>
     </row>
-    <row r="708" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="708" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B708" s="5" t="s">
         <v>2</v>
       </c>
@@ -24238,7 +24228,7 @@
       <c r="L708" s="6"/>
       <c r="M708" s="7"/>
     </row>
-    <row r="709" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="709" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B709" s="5" t="s">
         <v>5</v>
       </c>
@@ -24266,7 +24256,7 @@
       <c r="L709" s="6"/>
       <c r="M709" s="7"/>
     </row>
-    <row r="710" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="710" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B710" s="5" t="s">
         <v>5</v>
       </c>
@@ -24294,7 +24284,7 @@
       <c r="L710" s="6"/>
       <c r="M710" s="7"/>
     </row>
-    <row r="711" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="711" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B711" s="5" t="s">
         <v>5</v>
       </c>
@@ -24322,7 +24312,7 @@
       <c r="L711" s="6"/>
       <c r="M711" s="7"/>
     </row>
-    <row r="712" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="712" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B712" s="5" t="s">
         <v>5</v>
       </c>
@@ -24350,7 +24340,7 @@
       <c r="L712" s="6"/>
       <c r="M712" s="7"/>
     </row>
-    <row r="713" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="713" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B713" s="5" t="s">
         <v>2</v>
       </c>
@@ -24378,7 +24368,7 @@
       <c r="L713" s="6"/>
       <c r="M713" s="7"/>
     </row>
-    <row r="714" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="714" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B714" s="5" t="s">
         <v>5</v>
       </c>
@@ -24406,7 +24396,7 @@
       <c r="L714" s="6"/>
       <c r="M714" s="7"/>
     </row>
-    <row r="715" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="715" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B715" s="5" t="s">
         <v>2</v>
       </c>
@@ -24434,7 +24424,7 @@
       <c r="L715" s="6"/>
       <c r="M715" s="7"/>
     </row>
-    <row r="716" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="716" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B716" s="5" t="s">
         <v>2</v>
       </c>
@@ -24462,7 +24452,7 @@
       <c r="L716" s="6"/>
       <c r="M716" s="7"/>
     </row>
-    <row r="717" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="717" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B717" s="5" t="s">
         <v>5</v>
       </c>
@@ -24490,7 +24480,7 @@
       <c r="L717" s="6"/>
       <c r="M717" s="7"/>
     </row>
-    <row r="718" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="718" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B718" s="5" t="s">
         <v>2</v>
       </c>
@@ -24518,7 +24508,7 @@
       <c r="L718" s="6"/>
       <c r="M718" s="7"/>
     </row>
-    <row r="719" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="719" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B719" s="5" t="s">
         <v>2</v>
       </c>
@@ -24546,7 +24536,7 @@
       <c r="L719" s="6"/>
       <c r="M719" s="7"/>
     </row>
-    <row r="720" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="720" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B720" s="5" t="s">
         <v>5</v>
       </c>
@@ -24574,7 +24564,7 @@
       <c r="L720" s="6"/>
       <c r="M720" s="7"/>
     </row>
-    <row r="721" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="721" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B721" s="5" t="s">
         <v>2</v>
       </c>
@@ -24602,7 +24592,7 @@
       <c r="L721" s="6"/>
       <c r="M721" s="7"/>
     </row>
-    <row r="722" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="722" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B722" s="5" t="s">
         <v>2</v>
       </c>
@@ -24630,7 +24620,7 @@
       <c r="L722" s="6"/>
       <c r="M722" s="7"/>
     </row>
-    <row r="723" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="723" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B723" s="5" t="s">
         <v>5</v>
       </c>
@@ -24658,7 +24648,7 @@
       <c r="L723" s="6"/>
       <c r="M723" s="7"/>
     </row>
-    <row r="724" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="724" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B724" s="5" t="s">
         <v>2</v>
       </c>
@@ -24686,7 +24676,7 @@
       <c r="L724" s="6"/>
       <c r="M724" s="7"/>
     </row>
-    <row r="725" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="725" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B725" s="5" t="s">
         <v>5</v>
       </c>
@@ -24714,7 +24704,7 @@
       <c r="L725" s="6"/>
       <c r="M725" s="7"/>
     </row>
-    <row r="726" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="726" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B726" s="5" t="s">
         <v>2</v>
       </c>
@@ -24742,7 +24732,7 @@
       <c r="L726" s="6"/>
       <c r="M726" s="7"/>
     </row>
-    <row r="727" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="727" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B727" s="5" t="s">
         <v>5</v>
       </c>
@@ -24770,7 +24760,7 @@
       <c r="L727" s="6"/>
       <c r="M727" s="7"/>
     </row>
-    <row r="728" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="728" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B728" s="5" t="s">
         <v>5</v>
       </c>
@@ -24798,7 +24788,7 @@
       <c r="L728" s="6"/>
       <c r="M728" s="7"/>
     </row>
-    <row r="729" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="729" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B729" s="5" t="s">
         <v>5</v>
       </c>
@@ -24826,7 +24816,7 @@
       <c r="L729" s="6"/>
       <c r="M729" s="7"/>
     </row>
-    <row r="730" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="730" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B730" s="5" t="s">
         <v>2</v>
       </c>
@@ -24854,7 +24844,7 @@
       <c r="L730" s="6"/>
       <c r="M730" s="7"/>
     </row>
-    <row r="731" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="731" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B731" s="5" t="s">
         <v>5</v>
       </c>
@@ -24882,7 +24872,7 @@
       <c r="L731" s="6"/>
       <c r="M731" s="7"/>
     </row>
-    <row r="732" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="732" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B732" s="5" t="s">
         <v>2</v>
       </c>
@@ -24910,7 +24900,7 @@
       <c r="L732" s="6"/>
       <c r="M732" s="7"/>
     </row>
-    <row r="733" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="733" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B733" s="5" t="s">
         <v>5</v>
       </c>
@@ -24938,7 +24928,7 @@
       <c r="L733" s="6"/>
       <c r="M733" s="7"/>
     </row>
-    <row r="734" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="734" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B734" s="5" t="s">
         <v>2</v>
       </c>
@@ -24966,7 +24956,7 @@
       <c r="L734" s="6"/>
       <c r="M734" s="7"/>
     </row>
-    <row r="735" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="735" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B735" s="5" t="s">
         <v>5</v>
       </c>
@@ -24994,7 +24984,7 @@
       <c r="L735" s="6"/>
       <c r="M735" s="7"/>
     </row>
-    <row r="736" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="736" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B736" s="5" t="s">
         <v>2</v>
       </c>
@@ -25022,7 +25012,7 @@
       <c r="L736" s="6"/>
       <c r="M736" s="7"/>
     </row>
-    <row r="737" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="737" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B737" s="5" t="s">
         <v>5</v>
       </c>
@@ -25050,7 +25040,7 @@
       <c r="L737" s="6"/>
       <c r="M737" s="7"/>
     </row>
-    <row r="738" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="738" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B738" s="5" t="s">
         <v>2</v>
       </c>
@@ -25078,7 +25068,7 @@
       <c r="L738" s="6"/>
       <c r="M738" s="7"/>
     </row>
-    <row r="739" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="739" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B739" s="5" t="s">
         <v>5</v>
       </c>
@@ -25106,7 +25096,7 @@
       <c r="L739" s="6"/>
       <c r="M739" s="7"/>
     </row>
-    <row r="740" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="740" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B740" s="5" t="s">
         <v>5</v>
       </c>
@@ -25134,7 +25124,7 @@
       <c r="L740" s="6"/>
       <c r="M740" s="7"/>
     </row>
-    <row r="741" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="741" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B741" s="5" t="s">
         <v>2</v>
       </c>
@@ -25162,7 +25152,7 @@
       <c r="L741" s="6"/>
       <c r="M741" s="7"/>
     </row>
-    <row r="742" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="742" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B742" s="5" t="s">
         <v>5</v>
       </c>
@@ -25190,7 +25180,7 @@
       <c r="L742" s="6"/>
       <c r="M742" s="7"/>
     </row>
-    <row r="743" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="743" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B743" s="5" t="s">
         <v>5</v>
       </c>
@@ -25218,7 +25208,7 @@
       <c r="L743" s="6"/>
       <c r="M743" s="7"/>
     </row>
-    <row r="744" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="744" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B744" s="5" t="s">
         <v>5</v>
       </c>
@@ -25246,7 +25236,7 @@
       <c r="L744" s="6"/>
       <c r="M744" s="7"/>
     </row>
-    <row r="745" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="745" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B745" s="5" t="s">
         <v>2</v>
       </c>
@@ -25274,7 +25264,7 @@
       <c r="L745" s="6"/>
       <c r="M745" s="7"/>
     </row>
-    <row r="746" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="746" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B746" s="5" t="s">
         <v>2</v>
       </c>
@@ -25302,7 +25292,7 @@
       <c r="L746" s="6"/>
       <c r="M746" s="7"/>
     </row>
-    <row r="747" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="747" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B747" s="5" t="s">
         <v>2</v>
       </c>
@@ -25330,7 +25320,7 @@
       <c r="L747" s="6"/>
       <c r="M747" s="7"/>
     </row>
-    <row r="748" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="748" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B748" s="5" t="s">
         <v>5</v>
       </c>
@@ -25358,7 +25348,7 @@
       <c r="L748" s="6"/>
       <c r="M748" s="7"/>
     </row>
-    <row r="749" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="749" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B749" s="5" t="s">
         <v>5</v>
       </c>
@@ -25386,7 +25376,7 @@
       <c r="L749" s="6"/>
       <c r="M749" s="7"/>
     </row>
-    <row r="750" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="750" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B750" s="5" t="s">
         <v>5</v>
       </c>
@@ -25414,7 +25404,7 @@
       <c r="L750" s="6"/>
       <c r="M750" s="7"/>
     </row>
-    <row r="751" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="751" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B751" s="5" t="s">
         <v>5</v>
       </c>
@@ -25442,7 +25432,7 @@
       <c r="L751" s="6"/>
       <c r="M751" s="7"/>
     </row>
-    <row r="752" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="752" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B752" s="5" t="s">
         <v>2</v>
       </c>
@@ -25470,7 +25460,7 @@
       <c r="L752" s="6"/>
       <c r="M752" s="7"/>
     </row>
-    <row r="753" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="753" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B753" s="5" t="s">
         <v>5</v>
       </c>
@@ -25498,7 +25488,7 @@
       <c r="L753" s="6"/>
       <c r="M753" s="7"/>
     </row>
-    <row r="754" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="754" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B754" s="5" t="s">
         <v>5</v>
       </c>
@@ -25526,7 +25516,7 @@
       <c r="L754" s="6"/>
       <c r="M754" s="7"/>
     </row>
-    <row r="755" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="755" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B755" s="5" t="s">
         <v>5</v>
       </c>
@@ -25554,7 +25544,7 @@
       <c r="L755" s="6"/>
       <c r="M755" s="7"/>
     </row>
-    <row r="756" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="756" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B756" s="5" t="s">
         <v>5</v>
       </c>
@@ -25582,7 +25572,7 @@
       <c r="L756" s="6"/>
       <c r="M756" s="7"/>
     </row>
-    <row r="757" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="757" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B757" s="5" t="s">
         <v>2</v>
       </c>
@@ -25610,7 +25600,7 @@
       <c r="L757" s="6"/>
       <c r="M757" s="7"/>
     </row>
-    <row r="758" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="758" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B758" s="5" t="s">
         <v>5</v>
       </c>
@@ -25638,7 +25628,7 @@
       <c r="L758" s="6"/>
       <c r="M758" s="7"/>
     </row>
-    <row r="759" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="759" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B759" s="5" t="s">
         <v>2</v>
       </c>
@@ -25666,7 +25656,7 @@
       <c r="L759" s="6"/>
       <c r="M759" s="7"/>
     </row>
-    <row r="760" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="760" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B760" s="5" t="s">
         <v>5</v>
       </c>
@@ -25694,7 +25684,7 @@
       <c r="L760" s="6"/>
       <c r="M760" s="7"/>
     </row>
-    <row r="761" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="761" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B761" s="5" t="s">
         <v>5</v>
       </c>
@@ -25722,7 +25712,7 @@
       <c r="L761" s="6"/>
       <c r="M761" s="7"/>
     </row>
-    <row r="762" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="762" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B762" s="5" t="s">
         <v>2</v>
       </c>
@@ -25750,7 +25740,7 @@
       <c r="L762" s="6"/>
       <c r="M762" s="7"/>
     </row>
-    <row r="763" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="763" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B763" s="5" t="s">
         <v>5</v>
       </c>
@@ -25778,7 +25768,7 @@
       <c r="L763" s="6"/>
       <c r="M763" s="7"/>
     </row>
-    <row r="764" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="764" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B764" s="5" t="s">
         <v>2</v>
       </c>
@@ -25806,7 +25796,7 @@
       <c r="L764" s="6"/>
       <c r="M764" s="7"/>
     </row>
-    <row r="765" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="765" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B765" s="5" t="s">
         <v>2</v>
       </c>
@@ -25834,7 +25824,7 @@
       <c r="L765" s="6"/>
       <c r="M765" s="7"/>
     </row>
-    <row r="766" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="766" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B766" s="5" t="s">
         <v>5</v>
       </c>
@@ -25862,7 +25852,7 @@
       <c r="L766" s="6"/>
       <c r="M766" s="7"/>
     </row>
-    <row r="767" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="767" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B767" s="5" t="s">
         <v>2</v>
       </c>
@@ -25890,7 +25880,7 @@
       <c r="L767" s="6"/>
       <c r="M767" s="7"/>
     </row>
-    <row r="768" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="768" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B768" s="5" t="s">
         <v>5</v>
       </c>
@@ -25918,7 +25908,7 @@
       <c r="L768" s="6"/>
       <c r="M768" s="7"/>
     </row>
-    <row r="769" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="769" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B769" s="5" t="s">
         <v>2</v>
       </c>
@@ -25946,7 +25936,7 @@
       <c r="L769" s="6"/>
       <c r="M769" s="7"/>
     </row>
-    <row r="770" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="770" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B770" s="5" t="s">
         <v>2</v>
       </c>
@@ -25974,7 +25964,7 @@
       <c r="L770" s="6"/>
       <c r="M770" s="7"/>
     </row>
-    <row r="771" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="771" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B771" s="5" t="s">
         <v>5</v>
       </c>
@@ -26002,7 +25992,7 @@
       <c r="L771" s="6"/>
       <c r="M771" s="7"/>
     </row>
-    <row r="772" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="772" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B772" s="5" t="s">
         <v>2</v>
       </c>
@@ -26030,7 +26020,7 @@
       <c r="L772" s="6"/>
       <c r="M772" s="7"/>
     </row>
-    <row r="773" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="773" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B773" s="5" t="s">
         <v>5</v>
       </c>
@@ -26058,7 +26048,7 @@
       <c r="L773" s="6"/>
       <c r="M773" s="7"/>
     </row>
-    <row r="774" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="774" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B774" s="5" t="s">
         <v>5</v>
       </c>
@@ -26086,7 +26076,7 @@
       <c r="L774" s="6"/>
       <c r="M774" s="7"/>
     </row>
-    <row r="775" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="775" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B775" s="5" t="s">
         <v>5</v>
       </c>
@@ -26114,7 +26104,7 @@
       <c r="L775" s="6"/>
       <c r="M775" s="7"/>
     </row>
-    <row r="776" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="776" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B776" s="5" t="s">
         <v>2</v>
       </c>
@@ -26142,7 +26132,7 @@
       <c r="L776" s="6"/>
       <c r="M776" s="7"/>
     </row>
-    <row r="777" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="777" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B777" s="5" t="s">
         <v>2</v>
       </c>
@@ -26170,7 +26160,7 @@
       <c r="L777" s="6"/>
       <c r="M777" s="7"/>
     </row>
-    <row r="778" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="778" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B778" s="5" t="s">
         <v>5</v>
       </c>
@@ -26198,7 +26188,7 @@
       <c r="L778" s="6"/>
       <c r="M778" s="7"/>
     </row>
-    <row r="779" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="779" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B779" s="5" t="s">
         <v>2</v>
       </c>
@@ -26226,7 +26216,7 @@
       <c r="L779" s="6"/>
       <c r="M779" s="7"/>
     </row>
-    <row r="780" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="780" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B780" s="5" t="s">
         <v>2</v>
       </c>
@@ -26254,7 +26244,7 @@
       <c r="L780" s="6"/>
       <c r="M780" s="7"/>
     </row>
-    <row r="781" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="781" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B781" s="5" t="s">
         <v>2</v>
       </c>
@@ -26282,7 +26272,7 @@
       <c r="L781" s="6"/>
       <c r="M781" s="7"/>
     </row>
-    <row r="782" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="782" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B782" s="5" t="s">
         <v>2</v>
       </c>
@@ -26310,7 +26300,7 @@
       <c r="L782" s="6"/>
       <c r="M782" s="7"/>
     </row>
-    <row r="783" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="783" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B783" s="5" t="s">
         <v>5</v>
       </c>
@@ -26338,7 +26328,7 @@
       <c r="L783" s="6"/>
       <c r="M783" s="7"/>
     </row>
-    <row r="784" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="784" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B784" s="5" t="s">
         <v>2</v>
       </c>
@@ -26366,7 +26356,7 @@
       <c r="L784" s="6"/>
       <c r="M784" s="7"/>
     </row>
-    <row r="785" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="785" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B785" s="5" t="s">
         <v>2</v>
       </c>
@@ -26394,7 +26384,7 @@
       <c r="L785" s="6"/>
       <c r="M785" s="7"/>
     </row>
-    <row r="786" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="786" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B786" s="5" t="s">
         <v>2</v>
       </c>
@@ -26422,7 +26412,7 @@
       <c r="L786" s="6"/>
       <c r="M786" s="7"/>
     </row>
-    <row r="787" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="787" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B787" s="5" t="s">
         <v>2</v>
       </c>
@@ -26450,7 +26440,7 @@
       <c r="L787" s="6"/>
       <c r="M787" s="7"/>
     </row>
-    <row r="788" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="788" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B788" s="5" t="s">
         <v>5</v>
       </c>
@@ -26478,7 +26468,7 @@
       <c r="L788" s="6"/>
       <c r="M788" s="7"/>
     </row>
-    <row r="789" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="789" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B789" s="5" t="s">
         <v>2</v>
       </c>
@@ -26506,7 +26496,7 @@
       <c r="L789" s="6"/>
       <c r="M789" s="7"/>
     </row>
-    <row r="790" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="790" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B790" s="5" t="s">
         <v>2</v>
       </c>
@@ -26534,7 +26524,7 @@
       <c r="L790" s="6"/>
       <c r="M790" s="7"/>
     </row>
-    <row r="791" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="791" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B791" s="5" t="s">
         <v>2</v>
       </c>
@@ -26562,7 +26552,7 @@
       <c r="L791" s="6"/>
       <c r="M791" s="7"/>
     </row>
-    <row r="792" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="792" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B792" s="5" t="s">
         <v>5</v>
       </c>
@@ -26590,7 +26580,7 @@
       <c r="L792" s="6"/>
       <c r="M792" s="7"/>
     </row>
-    <row r="793" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="793" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B793" s="5" t="s">
         <v>2</v>
       </c>
@@ -26618,7 +26608,7 @@
       <c r="L793" s="6"/>
       <c r="M793" s="7"/>
     </row>
-    <row r="794" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="794" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B794" s="5" t="s">
         <v>2</v>
       </c>
@@ -26646,7 +26636,7 @@
       <c r="L794" s="6"/>
       <c r="M794" s="7"/>
     </row>
-    <row r="795" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="795" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B795" s="5" t="s">
         <v>2</v>
       </c>
@@ -26674,7 +26664,7 @@
       <c r="L795" s="6"/>
       <c r="M795" s="7"/>
     </row>
-    <row r="796" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="796" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B796" s="5" t="s">
         <v>5</v>
       </c>
@@ -26702,7 +26692,7 @@
       <c r="L796" s="6"/>
       <c r="M796" s="7"/>
     </row>
-    <row r="797" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="797" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B797" s="5" t="s">
         <v>5</v>
       </c>
@@ -26730,7 +26720,7 @@
       <c r="L797" s="6"/>
       <c r="M797" s="7"/>
     </row>
-    <row r="798" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="798" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B798" s="5" t="s">
         <v>2</v>
       </c>
@@ -26758,7 +26748,7 @@
       <c r="L798" s="6"/>
       <c r="M798" s="7"/>
     </row>
-    <row r="799" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="799" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B799" s="5" t="s">
         <v>2</v>
       </c>
@@ -26786,7 +26776,7 @@
       <c r="L799" s="6"/>
       <c r="M799" s="7"/>
     </row>
-    <row r="800" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="800" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B800" s="5" t="s">
         <v>5</v>
       </c>
@@ -26814,7 +26804,7 @@
       <c r="L800" s="6"/>
       <c r="M800" s="7"/>
     </row>
-    <row r="801" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="801" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B801" s="5" t="s">
         <v>2</v>
       </c>
@@ -26842,7 +26832,7 @@
       <c r="L801" s="6"/>
       <c r="M801" s="7"/>
     </row>
-    <row r="802" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="802" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B802" s="5" t="s">
         <v>5</v>
       </c>
@@ -26870,7 +26860,7 @@
       <c r="L802" s="6"/>
       <c r="M802" s="7"/>
     </row>
-    <row r="803" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="803" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B803" s="5" t="s">
         <v>2</v>
       </c>
@@ -26898,7 +26888,7 @@
       <c r="L803" s="6"/>
       <c r="M803" s="7"/>
     </row>
-    <row r="804" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="804" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B804" s="5" t="s">
         <v>5</v>
       </c>
@@ -26926,7 +26916,7 @@
       <c r="L804" s="6"/>
       <c r="M804" s="7"/>
     </row>
-    <row r="805" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="805" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B805" s="5" t="s">
         <v>5</v>
       </c>
@@ -26954,7 +26944,7 @@
       <c r="L805" s="6"/>
       <c r="M805" s="7"/>
     </row>
-    <row r="806" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="806" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B806" s="5" t="s">
         <v>2</v>
       </c>
@@ -26982,7 +26972,7 @@
       <c r="L806" s="6"/>
       <c r="M806" s="7"/>
     </row>
-    <row r="807" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="807" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B807" s="5" t="s">
         <v>2</v>
       </c>
@@ -27010,7 +27000,7 @@
       <c r="L807" s="6"/>
       <c r="M807" s="7"/>
     </row>
-    <row r="808" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="808" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B808" s="5" t="s">
         <v>2</v>
       </c>
@@ -27038,7 +27028,7 @@
       <c r="L808" s="6"/>
       <c r="M808" s="7"/>
     </row>
-    <row r="809" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="809" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B809" s="5" t="s">
         <v>5</v>
       </c>
@@ -27066,7 +27056,7 @@
       <c r="L809" s="6"/>
       <c r="M809" s="7"/>
     </row>
-    <row r="810" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="810" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B810" s="5" t="s">
         <v>2</v>
       </c>
@@ -27094,7 +27084,7 @@
       <c r="L810" s="6"/>
       <c r="M810" s="7"/>
     </row>
-    <row r="811" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="811" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B811" s="5" t="s">
         <v>2</v>
       </c>
@@ -27122,7 +27112,7 @@
       <c r="L811" s="6"/>
       <c r="M811" s="7"/>
     </row>
-    <row r="812" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="812" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B812" s="5" t="s">
         <v>5</v>
       </c>
@@ -27150,7 +27140,7 @@
       <c r="L812" s="6"/>
       <c r="M812" s="7"/>
     </row>
-    <row r="813" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="813" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B813" s="5" t="s">
         <v>5</v>
       </c>
@@ -27178,7 +27168,7 @@
       <c r="L813" s="6"/>
       <c r="M813" s="7"/>
     </row>
-    <row r="814" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="814" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B814" s="5" t="s">
         <v>5</v>
       </c>
@@ -27206,7 +27196,7 @@
       <c r="L814" s="6"/>
       <c r="M814" s="7"/>
     </row>
-    <row r="815" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="815" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B815" s="5" t="s">
         <v>5</v>
       </c>
@@ -27234,7 +27224,7 @@
       <c r="L815" s="6"/>
       <c r="M815" s="7"/>
     </row>
-    <row r="816" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="816" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B816" s="5" t="s">
         <v>2</v>
       </c>
@@ -27262,7 +27252,7 @@
       <c r="L816" s="6"/>
       <c r="M816" s="7"/>
     </row>
-    <row r="817" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="817" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B817" s="5" t="s">
         <v>5</v>
       </c>
@@ -27290,7 +27280,7 @@
       <c r="L817" s="6"/>
       <c r="M817" s="7"/>
     </row>
-    <row r="818" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="818" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B818" s="5" t="s">
         <v>2</v>
       </c>
@@ -27318,7 +27308,7 @@
       <c r="L818" s="6"/>
       <c r="M818" s="7"/>
     </row>
-    <row r="819" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="819" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B819" s="5" t="s">
         <v>5</v>
       </c>
@@ -27346,7 +27336,7 @@
       <c r="L819" s="6"/>
       <c r="M819" s="7"/>
     </row>
-    <row r="820" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="820" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B820" s="5" t="s">
         <v>2</v>
       </c>
@@ -27374,7 +27364,7 @@
       <c r="L820" s="6"/>
       <c r="M820" s="7"/>
     </row>
-    <row r="821" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="821" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B821" s="5" t="s">
         <v>5</v>
       </c>
@@ -27402,7 +27392,7 @@
       <c r="L821" s="6"/>
       <c r="M821" s="7"/>
     </row>
-    <row r="822" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="822" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B822" s="5" t="s">
         <v>2</v>
       </c>
@@ -27430,7 +27420,7 @@
       <c r="L822" s="6"/>
       <c r="M822" s="7"/>
     </row>
-    <row r="823" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="823" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B823" s="5" t="s">
         <v>2</v>
       </c>
@@ -27458,7 +27448,7 @@
       <c r="L823" s="6"/>
       <c r="M823" s="7"/>
     </row>
-    <row r="824" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="824" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B824" s="5" t="s">
         <v>2</v>
       </c>
@@ -27486,7 +27476,7 @@
       <c r="L824" s="6"/>
       <c r="M824" s="7"/>
     </row>
-    <row r="825" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="825" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B825" s="5" t="s">
         <v>2</v>
       </c>
@@ -27514,7 +27504,7 @@
       <c r="L825" s="6"/>
       <c r="M825" s="7"/>
     </row>
-    <row r="826" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="826" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B826" s="5" t="s">
         <v>5</v>
       </c>
@@ -27542,7 +27532,7 @@
       <c r="L826" s="6"/>
       <c r="M826" s="7"/>
     </row>
-    <row r="827" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="827" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B827" s="5" t="s">
         <v>2</v>
       </c>
@@ -27570,7 +27560,7 @@
       <c r="L827" s="6"/>
       <c r="M827" s="7"/>
     </row>
-    <row r="828" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="828" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B828" s="5" t="s">
         <v>2</v>
       </c>
@@ -27598,7 +27588,7 @@
       <c r="L828" s="6"/>
       <c r="M828" s="7"/>
     </row>
-    <row r="829" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="829" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B829" s="5" t="s">
         <v>5</v>
       </c>
@@ -27626,7 +27616,7 @@
       <c r="L829" s="6"/>
       <c r="M829" s="7"/>
     </row>
-    <row r="830" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="830" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B830" s="5" t="s">
         <v>2</v>
       </c>
@@ -27654,7 +27644,7 @@
       <c r="L830" s="6"/>
       <c r="M830" s="7"/>
     </row>
-    <row r="831" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="831" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B831" s="5" t="s">
         <v>2</v>
       </c>
@@ -27682,7 +27672,7 @@
       <c r="L831" s="6"/>
       <c r="M831" s="7"/>
     </row>
-    <row r="832" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="832" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B832" s="5" t="s">
         <v>2</v>
       </c>
@@ -27710,7 +27700,7 @@
       <c r="L832" s="6"/>
       <c r="M832" s="7"/>
     </row>
-    <row r="833" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="833" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B833" s="5" t="s">
         <v>5</v>
       </c>
@@ -27738,7 +27728,7 @@
       <c r="L833" s="6"/>
       <c r="M833" s="7"/>
     </row>
-    <row r="834" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="834" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B834" s="5" t="s">
         <v>2</v>
       </c>
@@ -27766,7 +27756,7 @@
       <c r="L834" s="6"/>
       <c r="M834" s="7"/>
     </row>
-    <row r="835" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="835" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B835" s="5" t="s">
         <v>2</v>
       </c>
@@ -27794,7 +27784,7 @@
       <c r="L835" s="6"/>
       <c r="M835" s="7"/>
     </row>
-    <row r="836" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="836" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B836" s="5" t="s">
         <v>5</v>
       </c>
@@ -27822,7 +27812,7 @@
       <c r="L836" s="6"/>
       <c r="M836" s="7"/>
     </row>
-    <row r="837" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="837" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B837" s="5" t="s">
         <v>2</v>
       </c>
@@ -27850,7 +27840,7 @@
       <c r="L837" s="6"/>
       <c r="M837" s="7"/>
     </row>
-    <row r="838" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="838" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B838" s="5" t="s">
         <v>5</v>
       </c>
@@ -27878,7 +27868,7 @@
       <c r="L838" s="6"/>
       <c r="M838" s="7"/>
     </row>
-    <row r="839" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="839" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B839" s="5" t="s">
         <v>2</v>
       </c>
@@ -27906,7 +27896,7 @@
       <c r="L839" s="6"/>
       <c r="M839" s="7"/>
     </row>
-    <row r="840" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="840" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B840" s="5" t="s">
         <v>5</v>
       </c>
@@ -27934,7 +27924,7 @@
       <c r="L840" s="6"/>
       <c r="M840" s="7"/>
     </row>
-    <row r="841" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="841" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B841" s="5" t="s">
         <v>2</v>
       </c>
@@ -27962,7 +27952,7 @@
       <c r="L841" s="6"/>
       <c r="M841" s="7"/>
     </row>
-    <row r="842" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="842" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B842" s="5" t="s">
         <v>5</v>
       </c>
@@ -27990,7 +27980,7 @@
       <c r="L842" s="6"/>
       <c r="M842" s="7"/>
     </row>
-    <row r="843" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="843" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B843" s="5" t="s">
         <v>2</v>
       </c>
@@ -28018,7 +28008,7 @@
       <c r="L843" s="6"/>
       <c r="M843" s="7"/>
     </row>
-    <row r="844" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="844" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B844" s="5" t="s">
         <v>2</v>
       </c>
@@ -28046,7 +28036,7 @@
       <c r="L844" s="6"/>
       <c r="M844" s="7"/>
     </row>
-    <row r="845" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="845" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B845" s="5" t="s">
         <v>5</v>
       </c>
@@ -28074,7 +28064,7 @@
       <c r="L845" s="6"/>
       <c r="M845" s="7"/>
     </row>
-    <row r="846" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="846" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B846" s="5" t="s">
         <v>2</v>
       </c>
@@ -28102,7 +28092,7 @@
       <c r="L846" s="6"/>
       <c r="M846" s="7"/>
     </row>
-    <row r="847" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="847" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B847" s="5" t="s">
         <v>5</v>
       </c>
@@ -28130,7 +28120,7 @@
       <c r="L847" s="6"/>
       <c r="M847" s="7"/>
     </row>
-    <row r="848" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="848" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B848" s="5" t="s">
         <v>2</v>
       </c>
@@ -28158,7 +28148,7 @@
       <c r="L848" s="6"/>
       <c r="M848" s="7"/>
     </row>
-    <row r="849" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="849" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B849" s="5" t="s">
         <v>5</v>
       </c>
@@ -28186,7 +28176,7 @@
       <c r="L849" s="6"/>
       <c r="M849" s="7"/>
     </row>
-    <row r="850" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="850" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B850" s="5" t="s">
         <v>5</v>
       </c>
@@ -28214,7 +28204,7 @@
       <c r="L850" s="6"/>
       <c r="M850" s="7"/>
     </row>
-    <row r="851" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="851" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B851" s="5" t="s">
         <v>5</v>
       </c>
@@ -28242,7 +28232,7 @@
       <c r="L851" s="6"/>
       <c r="M851" s="7"/>
     </row>
-    <row r="852" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="852" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B852" s="5" t="s">
         <v>2</v>
       </c>
@@ -28270,7 +28260,7 @@
       <c r="L852" s="6"/>
       <c r="M852" s="7"/>
     </row>
-    <row r="853" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="853" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B853" s="5" t="s">
         <v>5</v>
       </c>
@@ -28298,7 +28288,7 @@
       <c r="L853" s="6"/>
       <c r="M853" s="7"/>
     </row>
-    <row r="854" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="854" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B854" s="5" t="s">
         <v>5</v>
       </c>
@@ -28326,7 +28316,7 @@
       <c r="L854" s="6"/>
       <c r="M854" s="7"/>
     </row>
-    <row r="855" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="855" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B855" s="5" t="s">
         <v>2</v>
       </c>
@@ -28354,7 +28344,7 @@
       <c r="L855" s="6"/>
       <c r="M855" s="7"/>
     </row>
-    <row r="856" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="856" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B856" s="5" t="s">
         <v>2</v>
       </c>
@@ -28382,7 +28372,7 @@
       <c r="L856" s="6"/>
       <c r="M856" s="7"/>
     </row>
-    <row r="857" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="857" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B857" s="5" t="s">
         <v>5</v>
       </c>
@@ -28410,7 +28400,7 @@
       <c r="L857" s="6"/>
       <c r="M857" s="7"/>
     </row>
-    <row r="858" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="858" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B858" s="5" t="s">
         <v>5</v>
       </c>
@@ -28438,7 +28428,7 @@
       <c r="L858" s="6"/>
       <c r="M858" s="7"/>
     </row>
-    <row r="859" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="859" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B859" s="5" t="s">
         <v>2</v>
       </c>
@@ -28466,7 +28456,7 @@
       <c r="L859" s="6"/>
       <c r="M859" s="7"/>
     </row>
-    <row r="860" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="860" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B860" s="5" t="s">
         <v>5</v>
       </c>
@@ -28494,7 +28484,7 @@
       <c r="L860" s="6"/>
       <c r="M860" s="7"/>
     </row>
-    <row r="861" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="861" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B861" s="5" t="s">
         <v>2</v>
       </c>
@@ -28522,7 +28512,7 @@
       <c r="L861" s="6"/>
       <c r="M861" s="7"/>
     </row>
-    <row r="862" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="862" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B862" s="5" t="s">
         <v>5</v>
       </c>
@@ -28550,7 +28540,7 @@
       <c r="L862" s="6"/>
       <c r="M862" s="7"/>
     </row>
-    <row r="863" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="863" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B863" s="5" t="s">
         <v>5</v>
       </c>
@@ -28578,7 +28568,7 @@
       <c r="L863" s="6"/>
       <c r="M863" s="7"/>
     </row>
-    <row r="864" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="864" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B864" s="5" t="s">
         <v>2</v>
       </c>
@@ -28606,7 +28596,7 @@
       <c r="L864" s="6"/>
       <c r="M864" s="7"/>
     </row>
-    <row r="865" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="865" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B865" s="5" t="s">
         <v>2</v>
       </c>
@@ -28634,7 +28624,7 @@
       <c r="L865" s="6"/>
       <c r="M865" s="7"/>
     </row>
-    <row r="866" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="866" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B866" s="5" t="s">
         <v>5</v>
       </c>
@@ -28662,7 +28652,7 @@
       <c r="L866" s="6"/>
       <c r="M866" s="7"/>
     </row>
-    <row r="867" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="867" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B867" s="5" t="s">
         <v>2</v>
       </c>
@@ -28690,7 +28680,7 @@
       <c r="L867" s="6"/>
       <c r="M867" s="7"/>
     </row>
-    <row r="868" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="868" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B868" s="5" t="s">
         <v>5</v>
       </c>
@@ -28718,7 +28708,7 @@
       <c r="L868" s="6"/>
       <c r="M868" s="7"/>
     </row>
-    <row r="869" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="869" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B869" s="5" t="s">
         <v>5</v>
       </c>
@@ -28746,7 +28736,7 @@
       <c r="L869" s="6"/>
       <c r="M869" s="7"/>
     </row>
-    <row r="870" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="870" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B870" s="5" t="s">
         <v>5</v>
       </c>
@@ -28774,7 +28764,7 @@
       <c r="L870" s="6"/>
       <c r="M870" s="7"/>
     </row>
-    <row r="871" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="871" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B871" s="5" t="s">
         <v>5</v>
       </c>
@@ -28802,7 +28792,7 @@
       <c r="L871" s="6"/>
       <c r="M871" s="7"/>
     </row>
-    <row r="872" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="872" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B872" s="5" t="s">
         <v>5</v>
       </c>
@@ -28830,7 +28820,7 @@
       <c r="L872" s="6"/>
       <c r="M872" s="7"/>
     </row>
-    <row r="873" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="873" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B873" s="5" t="s">
         <v>5</v>
       </c>
@@ -28858,7 +28848,7 @@
       <c r="L873" s="6"/>
       <c r="M873" s="7"/>
     </row>
-    <row r="874" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="874" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B874" s="5" t="s">
         <v>5</v>
       </c>
@@ -28886,7 +28876,7 @@
       <c r="L874" s="6"/>
       <c r="M874" s="7"/>
     </row>
-    <row r="875" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="875" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B875" s="5" t="s">
         <v>2</v>
       </c>
@@ -28914,7 +28904,7 @@
       <c r="L875" s="6"/>
       <c r="M875" s="7"/>
     </row>
-    <row r="876" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="876" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B876" s="5" t="s">
         <v>5</v>
       </c>
@@ -28942,7 +28932,7 @@
       <c r="L876" s="6"/>
       <c r="M876" s="7"/>
     </row>
-    <row r="877" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="877" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B877" s="5" t="s">
         <v>5</v>
       </c>
@@ -28970,7 +28960,7 @@
       <c r="L877" s="6"/>
       <c r="M877" s="7"/>
     </row>
-    <row r="878" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="878" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B878" s="5" t="s">
         <v>2</v>
       </c>
@@ -28998,7 +28988,7 @@
       <c r="L878" s="6"/>
       <c r="M878" s="7"/>
     </row>
-    <row r="879" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="879" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B879" s="5" t="s">
         <v>5</v>
       </c>
@@ -29026,7 +29016,7 @@
       <c r="L879" s="6"/>
       <c r="M879" s="7"/>
     </row>
-    <row r="880" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="880" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B880" s="5" t="s">
         <v>5</v>
       </c>
@@ -29054,7 +29044,7 @@
       <c r="L880" s="6"/>
       <c r="M880" s="7"/>
     </row>
-    <row r="881" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="881" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B881" s="5" t="s">
         <v>5</v>
       </c>
@@ -29082,7 +29072,7 @@
       <c r="L881" s="6"/>
       <c r="M881" s="7"/>
     </row>
-    <row r="882" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="882" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B882" s="5" t="s">
         <v>2</v>
       </c>
@@ -29110,7 +29100,7 @@
       <c r="L882" s="6"/>
       <c r="M882" s="7"/>
     </row>
-    <row r="883" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="883" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B883" s="5" t="s">
         <v>2</v>
       </c>
@@ -29138,7 +29128,7 @@
       <c r="L883" s="6"/>
       <c r="M883" s="7"/>
     </row>
-    <row r="884" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="884" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B884" s="5" t="s">
         <v>5</v>
       </c>
@@ -29166,7 +29156,7 @@
       <c r="L884" s="6"/>
       <c r="M884" s="7"/>
     </row>
-    <row r="885" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="885" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B885" s="5" t="s">
         <v>2</v>
       </c>
@@ -29194,7 +29184,7 @@
       <c r="L885" s="6"/>
       <c r="M885" s="7"/>
     </row>
-    <row r="886" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="886" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B886" s="5" t="s">
         <v>2</v>
       </c>
@@ -29222,7 +29212,7 @@
       <c r="L886" s="6"/>
       <c r="M886" s="7"/>
     </row>
-    <row r="887" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="887" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B887" s="5" t="s">
         <v>5</v>
       </c>
@@ -29250,7 +29240,7 @@
       <c r="L887" s="6"/>
       <c r="M887" s="7"/>
     </row>
-    <row r="888" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="888" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B888" s="5" t="s">
         <v>2</v>
       </c>
@@ -29278,7 +29268,7 @@
       <c r="L888" s="6"/>
       <c r="M888" s="7"/>
     </row>
-    <row r="889" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="889" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B889" s="5" t="s">
         <v>2</v>
       </c>
@@ -29306,7 +29296,7 @@
       <c r="L889" s="6"/>
       <c r="M889" s="7"/>
     </row>
-    <row r="890" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="890" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B890" s="5" t="s">
         <v>2</v>
       </c>
@@ -29334,7 +29324,7 @@
       <c r="L890" s="6"/>
       <c r="M890" s="7"/>
     </row>
-    <row r="891" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="891" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B891" s="5" t="s">
         <v>5</v>
       </c>
@@ -29362,7 +29352,7 @@
       <c r="L891" s="6"/>
       <c r="M891" s="7"/>
     </row>
-    <row r="892" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="892" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B892" s="5" t="s">
         <v>2</v>
       </c>
@@ -29390,7 +29380,7 @@
       <c r="L892" s="6"/>
       <c r="M892" s="7"/>
     </row>
-    <row r="893" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="893" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B893" s="5" t="s">
         <v>5</v>
       </c>
@@ -29418,7 +29408,7 @@
       <c r="L893" s="6"/>
       <c r="M893" s="7"/>
     </row>
-    <row r="894" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="894" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B894" s="5" t="s">
         <v>2</v>
       </c>
@@ -29446,7 +29436,7 @@
       <c r="L894" s="6"/>
       <c r="M894" s="7"/>
     </row>
-    <row r="895" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="895" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B895" s="5" t="s">
         <v>2</v>
       </c>
@@ -29474,7 +29464,7 @@
       <c r="L895" s="6"/>
       <c r="M895" s="7"/>
     </row>
-    <row r="896" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="896" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B896" s="5" t="s">
         <v>2</v>
       </c>
@@ -29502,7 +29492,7 @@
       <c r="L896" s="6"/>
       <c r="M896" s="7"/>
     </row>
-    <row r="897" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="897" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B897" s="5" t="s">
         <v>5</v>
       </c>
@@ -29530,7 +29520,7 @@
       <c r="L897" s="6"/>
       <c r="M897" s="7"/>
     </row>
-    <row r="898" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="898" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B898" s="5" t="s">
         <v>2</v>
       </c>
@@ -29558,7 +29548,7 @@
       <c r="L898" s="6"/>
       <c r="M898" s="7"/>
     </row>
-    <row r="899" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="899" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B899" s="5" t="s">
         <v>2</v>
       </c>
@@ -29586,7 +29576,7 @@
       <c r="L899" s="6"/>
       <c r="M899" s="7"/>
     </row>
-    <row r="900" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="900" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B900" s="5" t="s">
         <v>5</v>
       </c>
@@ -29614,7 +29604,7 @@
       <c r="L900" s="6"/>
       <c r="M900" s="7"/>
     </row>
-    <row r="901" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="901" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B901" s="5" t="s">
         <v>2</v>
       </c>
@@ -29642,7 +29632,7 @@
       <c r="L901" s="6"/>
       <c r="M901" s="7"/>
     </row>
-    <row r="902" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="902" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B902" s="5" t="s">
         <v>5</v>
       </c>
@@ -29670,7 +29660,7 @@
       <c r="L902" s="6"/>
       <c r="M902" s="7"/>
     </row>
-    <row r="903" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="903" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B903" s="5" t="s">
         <v>2</v>
       </c>
@@ -29698,7 +29688,7 @@
       <c r="L903" s="6"/>
       <c r="M903" s="7"/>
     </row>
-    <row r="904" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="904" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B904" s="5" t="s">
         <v>5</v>
       </c>
@@ -29726,7 +29716,7 @@
       <c r="L904" s="6"/>
       <c r="M904" s="7"/>
     </row>
-    <row r="905" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="905" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B905" s="5" t="s">
         <v>2</v>
       </c>
@@ -29754,7 +29744,7 @@
       <c r="L905" s="6"/>
       <c r="M905" s="7"/>
     </row>
-    <row r="906" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="906" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B906" s="5" t="s">
         <v>2</v>
       </c>
@@ -29782,7 +29772,7 @@
       <c r="L906" s="6"/>
       <c r="M906" s="7"/>
     </row>
-    <row r="907" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="907" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B907" s="5" t="s">
         <v>2</v>
       </c>
@@ -29810,7 +29800,7 @@
       <c r="L907" s="6"/>
       <c r="M907" s="7"/>
     </row>
-    <row r="908" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="908" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B908" s="5" t="s">
         <v>2</v>
       </c>
@@ -29838,7 +29828,7 @@
       <c r="L908" s="6"/>
       <c r="M908" s="7"/>
     </row>
-    <row r="909" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="909" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B909" s="5" t="s">
         <v>5</v>
       </c>
@@ -29866,7 +29856,7 @@
       <c r="L909" s="6"/>
       <c r="M909" s="7"/>
     </row>
-    <row r="910" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="910" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B910" s="5" t="s">
         <v>5</v>
       </c>
@@ -29894,7 +29884,7 @@
       <c r="L910" s="6"/>
       <c r="M910" s="7"/>
     </row>
-    <row r="911" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="911" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B911" s="5" t="s">
         <v>2</v>
       </c>
@@ -29922,7 +29912,7 @@
       <c r="L911" s="6"/>
       <c r="M911" s="7"/>
     </row>
-    <row r="912" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="912" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B912" s="5" t="s">
         <v>2</v>
       </c>
@@ -29950,7 +29940,7 @@
       <c r="L912" s="6"/>
       <c r="M912" s="7"/>
     </row>
-    <row r="913" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="913" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B913" s="5" t="s">
         <v>5</v>
       </c>
@@ -29978,7 +29968,7 @@
       <c r="L913" s="6"/>
       <c r="M913" s="7"/>
     </row>
-    <row r="914" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="914" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B914" s="5" t="s">
         <v>5</v>
       </c>
@@ -30006,7 +29996,7 @@
       <c r="L914" s="6"/>
       <c r="M914" s="7"/>
     </row>
-    <row r="915" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="915" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B915" s="5" t="s">
         <v>2</v>
       </c>
@@ -30034,7 +30024,7 @@
       <c r="L915" s="6"/>
       <c r="M915" s="7"/>
     </row>
-    <row r="916" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="916" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B916" s="5" t="s">
         <v>2</v>
       </c>
@@ -30062,7 +30052,7 @@
       <c r="L916" s="6"/>
       <c r="M916" s="7"/>
     </row>
-    <row r="917" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="917" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B917" s="5" t="s">
         <v>2</v>
       </c>
@@ -30090,7 +30080,7 @@
       <c r="L917" s="6"/>
       <c r="M917" s="7"/>
     </row>
-    <row r="918" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="918" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B918" s="5" t="s">
         <v>2</v>
       </c>
@@ -30118,7 +30108,7 @@
       <c r="L918" s="6"/>
       <c r="M918" s="7"/>
     </row>
-    <row r="919" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="919" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B919" s="5" t="s">
         <v>2</v>
       </c>
@@ -30146,7 +30136,7 @@
       <c r="L919" s="6"/>
       <c r="M919" s="7"/>
     </row>
-    <row r="920" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="920" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B920" s="5" t="s">
         <v>5</v>
       </c>
@@ -30174,7 +30164,7 @@
       <c r="L920" s="6"/>
       <c r="M920" s="7"/>
     </row>
-    <row r="921" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="921" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B921" s="5" t="s">
         <v>2</v>
       </c>
@@ -30202,7 +30192,7 @@
       <c r="L921" s="6"/>
       <c r="M921" s="7"/>
     </row>
-    <row r="922" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="922" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B922" s="5" t="s">
         <v>2</v>
       </c>
@@ -30230,7 +30220,7 @@
       <c r="L922" s="6"/>
       <c r="M922" s="7"/>
     </row>
-    <row r="923" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="923" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B923" s="5" t="s">
         <v>5</v>
       </c>
@@ -30258,7 +30248,7 @@
       <c r="L923" s="6"/>
       <c r="M923" s="7"/>
     </row>
-    <row r="924" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="924" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B924" s="5" t="s">
         <v>5</v>
       </c>
@@ -30286,7 +30276,7 @@
       <c r="L924" s="6"/>
       <c r="M924" s="7"/>
     </row>
-    <row r="925" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="925" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B925" s="5" t="s">
         <v>2</v>
       </c>
@@ -30314,7 +30304,7 @@
       <c r="L925" s="6"/>
       <c r="M925" s="7"/>
     </row>
-    <row r="926" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="926" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B926" s="5" t="s">
         <v>5</v>
       </c>
@@ -30342,7 +30332,7 @@
       <c r="L926" s="6"/>
       <c r="M926" s="7"/>
     </row>
-    <row r="927" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="927" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B927" s="5" t="s">
         <v>2</v>
       </c>
@@ -30370,7 +30360,7 @@
       <c r="L927" s="6"/>
       <c r="M927" s="7"/>
     </row>
-    <row r="928" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="928" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B928" s="5" t="s">
         <v>5</v>
       </c>
@@ -30398,7 +30388,7 @@
       <c r="L928" s="6"/>
       <c r="M928" s="7"/>
     </row>
-    <row r="929" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="929" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B929" s="5" t="s">
         <v>5</v>
       </c>
@@ -30426,7 +30416,7 @@
       <c r="L929" s="6"/>
       <c r="M929" s="7"/>
     </row>
-    <row r="930" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="930" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B930" s="5" t="s">
         <v>5</v>
       </c>
@@ -30454,7 +30444,7 @@
       <c r="L930" s="6"/>
       <c r="M930" s="7"/>
     </row>
-    <row r="931" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="931" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B931" s="5" t="s">
         <v>2</v>
       </c>
@@ -30482,7 +30472,7 @@
       <c r="L931" s="6"/>
       <c r="M931" s="7"/>
     </row>
-    <row r="932" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="932" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B932" s="5" t="s">
         <v>5</v>
       </c>
@@ -30510,7 +30500,7 @@
       <c r="L932" s="6"/>
       <c r="M932" s="7"/>
     </row>
-    <row r="933" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="933" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B933" s="5" t="s">
         <v>2</v>
       </c>
@@ -30538,7 +30528,7 @@
       <c r="L933" s="6"/>
       <c r="M933" s="7"/>
     </row>
-    <row r="934" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="934" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B934" s="5" t="s">
         <v>5</v>
       </c>
@@ -30566,7 +30556,7 @@
       <c r="L934" s="6"/>
       <c r="M934" s="7"/>
     </row>
-    <row r="935" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="935" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B935" s="5" t="s">
         <v>5</v>
       </c>
@@ -30594,7 +30584,7 @@
       <c r="L935" s="6"/>
       <c r="M935" s="7"/>
     </row>
-    <row r="936" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="936" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B936" s="5" t="s">
         <v>5</v>
       </c>
@@ -30622,7 +30612,7 @@
       <c r="L936" s="6"/>
       <c r="M936" s="7"/>
     </row>
-    <row r="937" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="937" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B937" s="5" t="s">
         <v>5</v>
       </c>
@@ -30650,7 +30640,7 @@
       <c r="L937" s="6"/>
       <c r="M937" s="7"/>
     </row>
-    <row r="938" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="938" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B938" s="5" t="s">
         <v>5</v>
       </c>
@@ -30678,7 +30668,7 @@
       <c r="L938" s="6"/>
       <c r="M938" s="7"/>
     </row>
-    <row r="939" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="939" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B939" s="5" t="s">
         <v>5</v>
       </c>
@@ -30706,7 +30696,7 @@
       <c r="L939" s="6"/>
       <c r="M939" s="7"/>
     </row>
-    <row r="940" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="940" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B940" s="5" t="s">
         <v>5</v>
       </c>
@@ -30734,7 +30724,7 @@
       <c r="L940" s="6"/>
       <c r="M940" s="7"/>
     </row>
-    <row r="941" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="941" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B941" s="5" t="s">
         <v>2</v>
       </c>
@@ -30762,7 +30752,7 @@
       <c r="L941" s="6"/>
       <c r="M941" s="7"/>
     </row>
-    <row r="942" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="942" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B942" s="5" t="s">
         <v>5</v>
       </c>
@@ -30790,7 +30780,7 @@
       <c r="L942" s="6"/>
       <c r="M942" s="7"/>
     </row>
-    <row r="943" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="943" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B943" s="5" t="s">
         <v>5</v>
       </c>
@@ -30818,7 +30808,7 @@
       <c r="L943" s="6"/>
       <c r="M943" s="7"/>
     </row>
-    <row r="944" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="944" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B944" s="5" t="s">
         <v>5</v>
       </c>
@@ -30846,7 +30836,7 @@
       <c r="L944" s="6"/>
       <c r="M944" s="7"/>
     </row>
-    <row r="945" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="945" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B945" s="5" t="s">
         <v>2</v>
       </c>
@@ -30874,7 +30864,7 @@
       <c r="L945" s="6"/>
       <c r="M945" s="7"/>
     </row>
-    <row r="946" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="946" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B946" s="5" t="s">
         <v>5</v>
       </c>
@@ -30902,7 +30892,7 @@
       <c r="L946" s="6"/>
       <c r="M946" s="7"/>
     </row>
-    <row r="947" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="947" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B947" s="5" t="s">
         <v>5</v>
       </c>
@@ -30930,7 +30920,7 @@
       <c r="L947" s="6"/>
       <c r="M947" s="7"/>
     </row>
-    <row r="948" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="948" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B948" s="5" t="s">
         <v>2</v>
       </c>
@@ -30958,7 +30948,7 @@
       <c r="L948" s="6"/>
       <c r="M948" s="7"/>
     </row>
-    <row r="949" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="949" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B949" s="5" t="s">
         <v>2</v>
       </c>
@@ -30986,7 +30976,7 @@
       <c r="L949" s="6"/>
       <c r="M949" s="7"/>
     </row>
-    <row r="950" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="950" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B950" s="5" t="s">
         <v>5</v>
       </c>
@@ -31014,7 +31004,7 @@
       <c r="L950" s="6"/>
       <c r="M950" s="7"/>
     </row>
-    <row r="951" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="951" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B951" s="5" t="s">
         <v>2</v>
       </c>
@@ -31042,7 +31032,7 @@
       <c r="L951" s="6"/>
       <c r="M951" s="7"/>
     </row>
-    <row r="952" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="952" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B952" s="5" t="s">
         <v>5</v>
       </c>
@@ -31070,7 +31060,7 @@
       <c r="L952" s="6"/>
       <c r="M952" s="7"/>
     </row>
-    <row r="953" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="953" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B953" s="5" t="s">
         <v>2</v>
       </c>
@@ -31098,7 +31088,7 @@
       <c r="L953" s="6"/>
       <c r="M953" s="7"/>
     </row>
-    <row r="954" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="954" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B954" s="5" t="s">
         <v>5</v>
       </c>
@@ -31126,7 +31116,7 @@
       <c r="L954" s="6"/>
       <c r="M954" s="7"/>
     </row>
-    <row r="955" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="955" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B955" s="5" t="s">
         <v>2</v>
       </c>
@@ -31154,7 +31144,7 @@
       <c r="L955" s="6"/>
       <c r="M955" s="7"/>
     </row>
-    <row r="956" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="956" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B956" s="5" t="s">
         <v>2</v>
       </c>
@@ -31182,7 +31172,7 @@
       <c r="L956" s="6"/>
       <c r="M956" s="7"/>
     </row>
-    <row r="957" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="957" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B957" s="5" t="s">
         <v>5</v>
       </c>
@@ -31210,7 +31200,7 @@
       <c r="L957" s="6"/>
       <c r="M957" s="7"/>
     </row>
-    <row r="958" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="958" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B958" s="5" t="s">
         <v>2</v>
       </c>
@@ -31238,7 +31228,7 @@
       <c r="L958" s="6"/>
       <c r="M958" s="7"/>
     </row>
-    <row r="959" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="959" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B959" s="5" t="s">
         <v>5</v>
       </c>
@@ -31266,7 +31256,7 @@
       <c r="L959" s="6"/>
       <c r="M959" s="7"/>
     </row>
-    <row r="960" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="960" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B960" s="5" t="s">
         <v>5</v>
       </c>
@@ -31294,7 +31284,7 @@
       <c r="L960" s="6"/>
       <c r="M960" s="7"/>
     </row>
-    <row r="961" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="961" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B961" s="5" t="s">
         <v>2</v>
       </c>
@@ -31322,7 +31312,7 @@
       <c r="L961" s="6"/>
       <c r="M961" s="7"/>
     </row>
-    <row r="962" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="962" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B962" s="5" t="s">
         <v>2</v>
       </c>
@@ -31350,7 +31340,7 @@
       <c r="L962" s="6"/>
       <c r="M962" s="7"/>
     </row>
-    <row r="963" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="963" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B963" s="5" t="s">
         <v>5</v>
       </c>
@@ -31378,7 +31368,7 @@
       <c r="L963" s="6"/>
       <c r="M963" s="7"/>
     </row>
-    <row r="964" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="964" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B964" s="5" t="s">
         <v>2</v>
       </c>
@@ -31406,7 +31396,7 @@
       <c r="L964" s="6"/>
       <c r="M964" s="7"/>
     </row>
-    <row r="965" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="965" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B965" s="5" t="s">
         <v>2</v>
       </c>
@@ -31434,7 +31424,7 @@
       <c r="L965" s="6"/>
       <c r="M965" s="7"/>
     </row>
-    <row r="966" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="966" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B966" s="5" t="s">
         <v>2</v>
       </c>
@@ -31462,7 +31452,7 @@
       <c r="L966" s="6"/>
       <c r="M966" s="7"/>
     </row>
-    <row r="967" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="967" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B967" s="5" t="s">
         <v>2</v>
       </c>
@@ -31490,7 +31480,7 @@
       <c r="L967" s="6"/>
       <c r="M967" s="7"/>
     </row>
-    <row r="968" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="968" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B968" s="5" t="s">
         <v>5</v>
       </c>
@@ -31518,7 +31508,7 @@
       <c r="L968" s="6"/>
       <c r="M968" s="7"/>
     </row>
-    <row r="969" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="969" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B969" s="5" t="s">
         <v>2</v>
       </c>
@@ -31546,7 +31536,7 @@
       <c r="L969" s="6"/>
       <c r="M969" s="7"/>
     </row>
-    <row r="970" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="970" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B970" s="5" t="s">
         <v>5</v>
       </c>
@@ -31574,7 +31564,7 @@
       <c r="L970" s="6"/>
       <c r="M970" s="7"/>
     </row>
-    <row r="971" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="971" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B971" s="5" t="s">
         <v>5</v>
       </c>
@@ -31602,7 +31592,7 @@
       <c r="L971" s="6"/>
       <c r="M971" s="7"/>
     </row>
-    <row r="972" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="972" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B972" s="5" t="s">
         <v>2</v>
       </c>
@@ -31630,7 +31620,7 @@
       <c r="L972" s="6"/>
       <c r="M972" s="7"/>
     </row>
-    <row r="973" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="973" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B973" s="5" t="s">
         <v>2</v>
       </c>
@@ -31658,7 +31648,7 @@
       <c r="L973" s="6"/>
       <c r="M973" s="7"/>
     </row>
-    <row r="974" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="974" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B974" s="5" t="s">
         <v>2</v>
       </c>
@@ -31686,7 +31676,7 @@
       <c r="L974" s="6"/>
       <c r="M974" s="7"/>
     </row>
-    <row r="975" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="975" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B975" s="5" t="s">
         <v>5</v>
       </c>
@@ -31714,7 +31704,7 @@
       <c r="L975" s="6"/>
       <c r="M975" s="7"/>
     </row>
-    <row r="976" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="976" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B976" s="5" t="s">
         <v>2</v>
       </c>
@@ -31742,7 +31732,7 @@
       <c r="L976" s="6"/>
       <c r="M976" s="7"/>
     </row>
-    <row r="977" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="977" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B977" s="5" t="s">
         <v>2</v>
       </c>
@@ -31770,7 +31760,7 @@
       <c r="L977" s="6"/>
       <c r="M977" s="7"/>
     </row>
-    <row r="978" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="978" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B978" s="5" t="s">
         <v>2</v>
       </c>
@@ -31798,7 +31788,7 @@
       <c r="L978" s="6"/>
       <c r="M978" s="7"/>
     </row>
-    <row r="979" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="979" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B979" s="5" t="s">
         <v>2</v>
       </c>
@@ -31826,7 +31816,7 @@
       <c r="L979" s="6"/>
       <c r="M979" s="7"/>
     </row>
-    <row r="980" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="980" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B980" s="5" t="s">
         <v>5</v>
       </c>
@@ -31854,7 +31844,7 @@
       <c r="L980" s="6"/>
       <c r="M980" s="7"/>
     </row>
-    <row r="981" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="981" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B981" s="5" t="s">
         <v>5</v>
       </c>
@@ -31882,7 +31872,7 @@
       <c r="L981" s="6"/>
       <c r="M981" s="7"/>
     </row>
-    <row r="982" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="982" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B982" s="5" t="s">
         <v>5</v>
       </c>
@@ -31910,7 +31900,7 @@
       <c r="L982" s="6"/>
       <c r="M982" s="7"/>
     </row>
-    <row r="983" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="983" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B983" s="5" t="s">
         <v>2</v>
       </c>
@@ -31938,7 +31928,7 @@
       <c r="L983" s="6"/>
       <c r="M983" s="7"/>
     </row>
-    <row r="984" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="984" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B984" s="5" t="s">
         <v>2</v>
       </c>
@@ -31966,7 +31956,7 @@
       <c r="L984" s="6"/>
       <c r="M984" s="7"/>
     </row>
-    <row r="985" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="985" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B985" s="5" t="s">
         <v>5</v>
       </c>
@@ -31994,7 +31984,7 @@
       <c r="L985" s="6"/>
       <c r="M985" s="7"/>
     </row>
-    <row r="986" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="986" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B986" s="5" t="s">
         <v>5</v>
       </c>
@@ -32022,7 +32012,7 @@
       <c r="L986" s="6"/>
       <c r="M986" s="7"/>
     </row>
-    <row r="987" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="987" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B987" s="5" t="s">
         <v>2</v>
       </c>
@@ -32050,7 +32040,7 @@
       <c r="L987" s="6"/>
       <c r="M987" s="7"/>
     </row>
-    <row r="988" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="988" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B988" s="5" t="s">
         <v>2</v>
       </c>
@@ -32078,7 +32068,7 @@
       <c r="L988" s="6"/>
       <c r="M988" s="7"/>
     </row>
-    <row r="989" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="989" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B989" s="5" t="s">
         <v>5</v>
       </c>
@@ -32106,7 +32096,7 @@
       <c r="L989" s="6"/>
       <c r="M989" s="7"/>
     </row>
-    <row r="990" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="990" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B990" s="5" t="s">
         <v>2</v>
       </c>
@@ -32134,7 +32124,7 @@
       <c r="L990" s="6"/>
       <c r="M990" s="7"/>
     </row>
-    <row r="991" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="991" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B991" s="5" t="s">
         <v>5</v>
       </c>
@@ -32162,7 +32152,7 @@
       <c r="L991" s="6"/>
       <c r="M991" s="7"/>
     </row>
-    <row r="992" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="992" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B992" s="5" t="s">
         <v>2</v>
       </c>
@@ -32190,7 +32180,7 @@
       <c r="L992" s="6"/>
       <c r="M992" s="7"/>
     </row>
-    <row r="993" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="993" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B993" s="5" t="s">
         <v>2</v>
       </c>
@@ -32218,7 +32208,7 @@
       <c r="L993" s="6"/>
       <c r="M993" s="7"/>
     </row>
-    <row r="994" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="994" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B994" s="5" t="s">
         <v>5</v>
       </c>
@@ -32246,7 +32236,7 @@
       <c r="L994" s="6"/>
       <c r="M994" s="7"/>
     </row>
-    <row r="995" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="995" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B995" s="5" t="s">
         <v>2</v>
       </c>
@@ -32274,7 +32264,7 @@
       <c r="L995" s="6"/>
       <c r="M995" s="7"/>
     </row>
-    <row r="996" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="996" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B996" s="5" t="s">
         <v>2</v>
       </c>
@@ -32302,7 +32292,7 @@
       <c r="L996" s="6"/>
       <c r="M996" s="7"/>
     </row>
-    <row r="997" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="997" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B997" s="5" t="s">
         <v>2</v>
       </c>
@@ -32330,7 +32320,7 @@
       <c r="L997" s="6"/>
       <c r="M997" s="7"/>
     </row>
-    <row r="998" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="998" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B998" s="5" t="s">
         <v>5</v>
       </c>
@@ -32358,7 +32348,7 @@
       <c r="L998" s="6"/>
       <c r="M998" s="7"/>
     </row>
-    <row r="999" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="999" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B999" s="5" t="s">
         <v>2</v>
       </c>
@@ -32386,7 +32376,7 @@
       <c r="L999" s="6"/>
       <c r="M999" s="7"/>
     </row>
-    <row r="1000" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1000" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B1000" s="5" t="s">
         <v>5</v>
       </c>
@@ -32414,7 +32404,7 @@
       <c r="L1000" s="6"/>
       <c r="M1000" s="7"/>
     </row>
-    <row r="1001" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1001" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B1001" s="5" t="s">
         <v>2</v>
       </c>
@@ -32442,7 +32432,7 @@
       <c r="L1001" s="6"/>
       <c r="M1001" s="7"/>
     </row>
-    <row r="1002" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1002" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B1002" s="5" t="s">
         <v>2</v>
       </c>
@@ -32470,7 +32460,7 @@
       <c r="L1002" s="6"/>
       <c r="M1002" s="7"/>
     </row>
-    <row r="1003" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1003" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B1003" s="8" t="s">
         <v>2</v>
       </c>
